--- a/assets/templates/New Template BOQ Sept 2026 All Charger.xlsx
+++ b/assets/templates/New Template BOQ Sept 2026 All Charger.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Hartono\Master BOQ VGreen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F8A3CE-A1DF-4E88-8057-ECBD2332312E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC04B5E6-FBF1-4EA5-9CDF-C15FFD60E8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="2" activeTab="6" xr2:uid="{84A2494B-0B6E-4413-A838-7E05AF24F7FD}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="157">
   <si>
     <t xml:space="preserve">CHARGING WORK </t>
   </si>
@@ -1080,7 +1080,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1282,9 +1282,6 @@
     <xf numFmtId="168" fontId="26" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="21" fillId="6" borderId="3" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="16" fillId="0" borderId="3" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1512,33 +1509,6 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="5" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1568,6 +1538,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="18" fillId="7" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1662,13 +1659,13 @@
             <v>Excavation of foundation soil by machine combined with manual repair</v>
           </cell>
           <cell r="J15">
-            <v>126100</v>
+            <v>138710</v>
           </cell>
           <cell r="K15">
-            <v>126100</v>
+            <v>138710</v>
           </cell>
           <cell r="L15">
-            <v>126100</v>
+            <v>138710</v>
           </cell>
         </row>
         <row r="18">
@@ -1676,13 +1673,13 @@
             <v>Transporting soil to gather internally within the project</v>
           </cell>
           <cell r="J18">
-            <v>120000</v>
+            <v>132000</v>
           </cell>
           <cell r="K18">
-            <v>120000</v>
+            <v>132000</v>
           </cell>
           <cell r="L18">
-            <v>120000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="19">
@@ -1690,13 +1687,13 @@
             <v xml:space="preserve">Plastic </v>
           </cell>
           <cell r="J19">
-            <v>14550</v>
+            <v>16005.000000000002</v>
           </cell>
           <cell r="K19">
-            <v>14550</v>
+            <v>16005.000000000002</v>
           </cell>
           <cell r="L19">
-            <v>14550</v>
+            <v>16005.000000000002</v>
           </cell>
         </row>
         <row r="20">
@@ -1704,13 +1701,13 @@
             <v>Concrete foundation lining, foundation bracing, foundation lining</v>
           </cell>
           <cell r="J20">
-            <v>1212500</v>
+            <v>1333750</v>
           </cell>
           <cell r="K20">
-            <v>1212500</v>
+            <v>1333750</v>
           </cell>
           <cell r="L20">
-            <v>1212500</v>
+            <v>1333750</v>
           </cell>
         </row>
         <row r="21">
@@ -1718,13 +1715,13 @@
             <v>Concrete foundation, foundation bracing, foundation</v>
           </cell>
           <cell r="J21">
-            <v>1746000</v>
+            <v>1920600.0000000002</v>
           </cell>
           <cell r="K21">
-            <v>1746000</v>
+            <v>1920600.0000000002</v>
           </cell>
           <cell r="L21">
-            <v>1746000</v>
+            <v>1920600.0000000002</v>
           </cell>
         </row>
         <row r="22">
@@ -1732,13 +1729,13 @@
             <v>Formwork of all kinds</v>
           </cell>
           <cell r="J22">
-            <v>294000</v>
+            <v>323400</v>
           </cell>
           <cell r="K22">
-            <v>294000</v>
+            <v>323400</v>
           </cell>
           <cell r="L22">
-            <v>294000</v>
+            <v>323400</v>
           </cell>
         </row>
         <row r="23">
@@ -1746,13 +1743,13 @@
             <v>Concrete formwork for foundation, foundation bracing, foundation, wall bracing, foundation wall, lobby, steps</v>
           </cell>
           <cell r="J23">
-            <v>302640</v>
+            <v>332904</v>
           </cell>
           <cell r="K23">
-            <v>302640</v>
+            <v>332904</v>
           </cell>
           <cell r="L23">
-            <v>302640</v>
+            <v>332904</v>
           </cell>
         </row>
         <row r="24">
@@ -1760,13 +1757,13 @@
             <v>Supply and install anchor bolts</v>
           </cell>
           <cell r="J24">
-            <v>33950</v>
+            <v>37345</v>
           </cell>
           <cell r="K24">
-            <v>33950</v>
+            <v>37345</v>
           </cell>
           <cell r="L24">
-            <v>33950</v>
+            <v>37345</v>
           </cell>
         </row>
         <row r="25">
@@ -1774,13 +1771,13 @@
             <v>Plastering outdoor</v>
           </cell>
           <cell r="J25">
-            <v>82450</v>
+            <v>90695.000000000015</v>
           </cell>
           <cell r="K25">
-            <v>82450</v>
+            <v>90695.000000000015</v>
           </cell>
           <cell r="L25">
-            <v>82450</v>
+            <v>90695.000000000015</v>
           </cell>
         </row>
         <row r="26">
@@ -1788,13 +1785,13 @@
             <v>External wall painting, foundation of cabinet, substation…</v>
           </cell>
           <cell r="J26">
-            <v>92000</v>
+            <v>101200.00000000001</v>
           </cell>
           <cell r="K26">
-            <v>92000</v>
+            <v>101200.00000000001</v>
           </cell>
           <cell r="L26">
-            <v>92000</v>
+            <v>101200.00000000001</v>
           </cell>
         </row>
         <row r="28">
@@ -1802,13 +1799,13 @@
             <v>Excavation of foundation soil by machine combined with manual repair</v>
           </cell>
           <cell r="J28">
-            <v>126100</v>
+            <v>138710</v>
           </cell>
           <cell r="K28">
-            <v>126100</v>
+            <v>138710</v>
           </cell>
           <cell r="L28">
-            <v>126100</v>
+            <v>138710</v>
           </cell>
         </row>
         <row r="31">
@@ -1816,13 +1813,13 @@
             <v>Transporting soil to gather internally within the project</v>
           </cell>
           <cell r="J31">
-            <v>120000</v>
+            <v>132000</v>
           </cell>
           <cell r="K31">
-            <v>120000</v>
+            <v>132000</v>
           </cell>
           <cell r="L31">
-            <v>120000</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="32">
@@ -1830,13 +1827,13 @@
             <v>Concrete foundation lining, foundation bracing, foundation lining</v>
           </cell>
           <cell r="J32">
-            <v>1212500</v>
+            <v>1333750</v>
           </cell>
           <cell r="K32">
-            <v>1212500</v>
+            <v>1333750</v>
           </cell>
           <cell r="L32">
-            <v>1212500</v>
+            <v>1333750</v>
           </cell>
         </row>
         <row r="33">
@@ -1844,13 +1841,13 @@
             <v>Concrete foundation, foundation bracing, foundation</v>
           </cell>
           <cell r="J33">
-            <v>1746000</v>
+            <v>1920600.0000000002</v>
           </cell>
           <cell r="K33">
-            <v>1746000</v>
+            <v>1920600.0000000002</v>
           </cell>
           <cell r="L33">
-            <v>1746000</v>
+            <v>1920600.0000000002</v>
           </cell>
         </row>
         <row r="34">
@@ -1858,13 +1855,13 @@
             <v>Formwork of all kinds</v>
           </cell>
           <cell r="J34">
-            <v>294000</v>
+            <v>323400</v>
           </cell>
           <cell r="K34">
-            <v>294000</v>
+            <v>323400</v>
           </cell>
           <cell r="L34">
-            <v>294000</v>
+            <v>323400</v>
           </cell>
         </row>
         <row r="35">
@@ -1872,13 +1869,13 @@
             <v>Concrete formwork for foundation, foundation bracing, foundation, wall bracing, foundation wall, lobby, steps</v>
           </cell>
           <cell r="J35">
-            <v>302640</v>
+            <v>332904</v>
           </cell>
           <cell r="K35">
-            <v>302640</v>
+            <v>332904</v>
           </cell>
           <cell r="L35">
-            <v>302640</v>
+            <v>332904</v>
           </cell>
         </row>
         <row r="36">
@@ -1886,13 +1883,13 @@
             <v>Supply and install anchor bolts</v>
           </cell>
           <cell r="J36">
-            <v>33950</v>
+            <v>37345</v>
           </cell>
           <cell r="K36">
-            <v>33950</v>
+            <v>37345</v>
           </cell>
           <cell r="L36">
-            <v>33950</v>
+            <v>37345</v>
           </cell>
         </row>
         <row r="37">
@@ -1900,13 +1897,13 @@
             <v>Plastering outdoor</v>
           </cell>
           <cell r="J37">
-            <v>82450</v>
+            <v>90695.000000000015</v>
           </cell>
           <cell r="K37">
-            <v>82450</v>
+            <v>90695.000000000015</v>
           </cell>
           <cell r="L37">
-            <v>82450</v>
+            <v>90695.000000000015</v>
           </cell>
         </row>
         <row r="38">
@@ -1914,13 +1911,13 @@
             <v>External wall painting, foundation of cabinet, substation…</v>
           </cell>
           <cell r="J38">
-            <v>92000</v>
+            <v>101200.00000000001</v>
           </cell>
           <cell r="K38">
-            <v>92000</v>
+            <v>101200.00000000001</v>
           </cell>
           <cell r="L38">
-            <v>92000</v>
+            <v>101200.00000000001</v>
           </cell>
         </row>
         <row r="40">
@@ -1928,13 +1925,13 @@
             <v>Line marking</v>
           </cell>
           <cell r="J40">
-            <v>48500</v>
+            <v>53350.000000000007</v>
           </cell>
           <cell r="K40">
-            <v>48500</v>
+            <v>53350.000000000007</v>
           </cell>
           <cell r="L40">
-            <v>48500</v>
+            <v>53350.000000000007</v>
           </cell>
         </row>
         <row r="41">
@@ -1942,13 +1939,13 @@
             <v>Car stops</v>
           </cell>
           <cell r="J41">
-            <v>213400</v>
+            <v>234740.00000000003</v>
           </cell>
           <cell r="K41">
-            <v>213400</v>
+            <v>234740.00000000003</v>
           </cell>
           <cell r="L41">
-            <v>213400</v>
+            <v>234740.00000000003</v>
           </cell>
         </row>
         <row r="43">
@@ -1956,13 +1953,13 @@
             <v>3kg CO2 portable fire extinguisher</v>
           </cell>
           <cell r="J43">
-            <v>1420000</v>
+            <v>1562000.0000000002</v>
           </cell>
           <cell r="K43">
-            <v>1420000</v>
+            <v>1562000.0000000002</v>
           </cell>
           <cell r="L43">
-            <v>1420000</v>
+            <v>1562000.0000000002</v>
           </cell>
         </row>
         <row r="44">
@@ -1970,13 +1967,13 @@
             <v>Fire extinguisher rack (Dimensions: 500x200x200mm, 1.2mm thick sheet metal, powder coated), 100mm high legs</v>
           </cell>
           <cell r="J44">
-            <v>913594.49999999988</v>
+            <v>1004953.95</v>
           </cell>
           <cell r="K44">
-            <v>913594.49999999988</v>
+            <v>1004953.95</v>
           </cell>
           <cell r="L44">
-            <v>913594.49999999988</v>
+            <v>1004953.95</v>
           </cell>
         </row>
         <row r="47">
@@ -1984,7 +1981,7 @@
             <v>LT-PANEL electrical cabinet - 1x 20kW poles  3P</v>
           </cell>
           <cell r="J47">
-            <v>5044000</v>
+            <v>5548400</v>
           </cell>
         </row>
         <row r="48">
@@ -1992,7 +1989,7 @@
             <v>LT-PANEL electrical cabinet - 1x 30kW poles  3P</v>
           </cell>
           <cell r="K48">
-            <v>6305000</v>
+            <v>6935500.0000000009</v>
           </cell>
         </row>
         <row r="49">
@@ -2000,7 +1997,7 @@
             <v>LT-PANEL electrical cabinet - 1x 60kW poles  3P</v>
           </cell>
           <cell r="L49">
-            <v>10670000</v>
+            <v>11737000.000000002</v>
           </cell>
         </row>
         <row r="55">
@@ -2008,7 +2005,7 @@
             <v>60kW Charging Pole</v>
           </cell>
           <cell r="L55">
-            <v>5820000</v>
+            <v>6402000.0000000009</v>
           </cell>
         </row>
         <row r="56">
@@ -2016,7 +2013,7 @@
             <v>Charging Pole 30KW</v>
           </cell>
           <cell r="K56">
-            <v>4365000</v>
+            <v>4801500</v>
           </cell>
         </row>
         <row r="57">
@@ -2024,7 +2021,7 @@
             <v>20KW Charging Tower</v>
           </cell>
           <cell r="J57">
-            <v>2910000</v>
+            <v>3201000.0000000005</v>
           </cell>
         </row>
         <row r="58">
@@ -2032,13 +2029,13 @@
             <v>Sticker EV Charger (DTF type)</v>
           </cell>
           <cell r="J58">
-            <v>100000</v>
+            <v>110000.00000000001</v>
           </cell>
           <cell r="K58">
-            <v>100000</v>
+            <v>110000.00000000001</v>
           </cell>
           <cell r="L58">
-            <v>100000</v>
+            <v>110000.00000000001</v>
           </cell>
         </row>
         <row r="60">
@@ -2046,7 +2043,7 @@
             <v>NA2XY (4Cx16)mm2 + E-NAYA (1Cx16)mm2 (from KWH to AC Panel)</v>
           </cell>
           <cell r="J60">
-            <v>78648.569999999992</v>
+            <v>86513.426999999996</v>
           </cell>
         </row>
         <row r="61">
@@ -2054,7 +2051,7 @@
             <v>NA2XY (4Cx16)mm2 + E-NAYA (1Cx16)mm2 (from AC Panel to Charger)</v>
           </cell>
           <cell r="J61">
-            <v>78648.569999999992</v>
+            <v>86513.426999999996</v>
           </cell>
         </row>
         <row r="62">
@@ -2062,7 +2059,7 @@
             <v>Cable Ground NYA 6mm with rod and grounding clamp</v>
           </cell>
           <cell r="J62">
-            <v>18000</v>
+            <v>19800</v>
           </cell>
         </row>
         <row r="63">
@@ -2070,7 +2067,7 @@
             <v>nA2Xy (3Cx25+1CX16) mm2 +e-nAya (1x16)mm2 (from KWH to AC Panel)</v>
           </cell>
           <cell r="K63">
-            <v>160667.79299999998</v>
+            <v>176734.5723</v>
           </cell>
         </row>
         <row r="64">
@@ -2078,7 +2075,7 @@
             <v>nA2Xy (3Cx25+1CX16) mm2 +e-nAya (1x16)mm2 (from AC Panel to Charger)</v>
           </cell>
           <cell r="K64">
-            <v>160667.79299999998</v>
+            <v>176734.5723</v>
           </cell>
         </row>
         <row r="65">
@@ -2086,7 +2083,7 @@
             <v>Cable Ground NYA 10mm with rod and grounding clamp</v>
           </cell>
           <cell r="K65">
-            <v>31000</v>
+            <v>34100</v>
           </cell>
         </row>
         <row r="66">
@@ -2094,7 +2091,7 @@
             <v>nA2Xy 3Cx95+N.(1X50)mm2+e-nAya (1x50)mm2 (from KWH to AC Panel)</v>
           </cell>
           <cell r="L66">
-            <v>265438.92375000002</v>
+            <v>291982.81612500007</v>
           </cell>
         </row>
         <row r="67">
@@ -2102,7 +2099,7 @@
             <v>nA2Xy 3Cx95+N.(1X50)mm2+e-nAya (1x50)mm2 (from AC Panel to Charger)</v>
           </cell>
           <cell r="L67">
-            <v>265438.92375000002</v>
+            <v>291982.81612500007</v>
           </cell>
         </row>
         <row r="68">
@@ -2110,7 +2107,7 @@
             <v>Cable Ground NYA 16mm with rod and grounding clamp</v>
           </cell>
           <cell r="L68">
-            <v>55500</v>
+            <v>61050.000000000007</v>
           </cell>
         </row>
         <row r="76">
@@ -2118,13 +2115,13 @@
             <v>Excavation of foundation pits and trenches by machine</v>
           </cell>
           <cell r="J76">
-            <v>116400</v>
+            <v>128040.00000000001</v>
           </cell>
           <cell r="K76">
-            <v>116400</v>
+            <v>128040.00000000001</v>
           </cell>
           <cell r="L76">
-            <v>116400</v>
+            <v>128040.00000000001</v>
           </cell>
         </row>
         <row r="77">
@@ -2132,13 +2129,13 @@
             <v>Backfilling with vibratory compactors</v>
           </cell>
           <cell r="J77">
-            <v>140650</v>
+            <v>154715</v>
           </cell>
           <cell r="K77">
-            <v>140650</v>
+            <v>154715</v>
           </cell>
           <cell r="L77">
-            <v>140650</v>
+            <v>154715</v>
           </cell>
         </row>
         <row r="78">
@@ -2146,13 +2143,13 @@
             <v>D300 warning tape</v>
           </cell>
           <cell r="J78">
-            <v>14550</v>
+            <v>16005.000000000002</v>
           </cell>
           <cell r="K78">
-            <v>14550</v>
+            <v>16005.000000000002</v>
           </cell>
           <cell r="L78">
-            <v>14550</v>
+            <v>16005.000000000002</v>
           </cell>
         </row>
         <row r="79">
@@ -2160,13 +2157,13 @@
             <v>Other materials: Adhesives, tapes, plastic cable ties, fire starters, bolts, nuts, tie rod connectors, washers, expansion anchors, pipe clamps, rods Welding, Teflon tape, rubber-cushioned jute rope, rags, foam glue, gaskets, marking, labeling. Elbows, tees, pipe connectors, plastic pipe clamps, end caps (for conduit), conduit connectors, ladder connectors, grounding, terminal lugs &lt;50mm2, etc.</v>
           </cell>
           <cell r="J79">
-            <v>339500</v>
+            <v>373450.00000000006</v>
           </cell>
           <cell r="K79">
-            <v>339500</v>
+            <v>373450.00000000006</v>
           </cell>
           <cell r="L79">
-            <v>339500</v>
+            <v>373450.00000000006</v>
           </cell>
         </row>
         <row r="80">
@@ -2174,13 +2171,13 @@
             <v>Biaya transport dan Survey (JAVA)</v>
           </cell>
           <cell r="J80">
-            <v>1000000</v>
+            <v>1100000</v>
           </cell>
           <cell r="K80">
-            <v>1000000</v>
+            <v>1100000</v>
           </cell>
           <cell r="L80">
-            <v>1000000</v>
+            <v>1100000</v>
           </cell>
         </row>
       </sheetData>
@@ -2254,13 +2251,13 @@
             <v>Excavation of foundation soil by machine combined with manual repair</v>
           </cell>
           <cell r="J15">
-            <v>138710</v>
+            <v>126100</v>
           </cell>
           <cell r="K15">
-            <v>138710</v>
+            <v>126100</v>
           </cell>
           <cell r="L15">
-            <v>138710</v>
+            <v>126100</v>
           </cell>
         </row>
         <row r="18">
@@ -2268,13 +2265,13 @@
             <v>Transporting soil to gather internally within the project</v>
           </cell>
           <cell r="J18">
-            <v>132000</v>
+            <v>120000</v>
           </cell>
           <cell r="K18">
-            <v>132000</v>
+            <v>120000</v>
           </cell>
           <cell r="L18">
-            <v>132000</v>
+            <v>120000</v>
           </cell>
         </row>
         <row r="19">
@@ -2282,13 +2279,13 @@
             <v xml:space="preserve">Plastic </v>
           </cell>
           <cell r="J19">
-            <v>16005.000000000002</v>
+            <v>14550</v>
           </cell>
           <cell r="K19">
-            <v>16005.000000000002</v>
+            <v>14550</v>
           </cell>
           <cell r="L19">
-            <v>16005.000000000002</v>
+            <v>14550</v>
           </cell>
         </row>
         <row r="20">
@@ -2296,13 +2293,13 @@
             <v>Concrete foundation lining, foundation bracing, foundation lining</v>
           </cell>
           <cell r="J20">
-            <v>1333750</v>
+            <v>1212500</v>
           </cell>
           <cell r="K20">
-            <v>1333750</v>
+            <v>1212500</v>
           </cell>
           <cell r="L20">
-            <v>1333750</v>
+            <v>1212500</v>
           </cell>
         </row>
         <row r="21">
@@ -2310,13 +2307,13 @@
             <v>Concrete foundation, foundation bracing, foundation</v>
           </cell>
           <cell r="J21">
-            <v>1920600.0000000002</v>
+            <v>1746000</v>
           </cell>
           <cell r="K21">
-            <v>1920600.0000000002</v>
+            <v>1746000</v>
           </cell>
           <cell r="L21">
-            <v>1920600.0000000002</v>
+            <v>1746000</v>
           </cell>
         </row>
         <row r="22">
@@ -2324,13 +2321,13 @@
             <v>Formwork of all kinds</v>
           </cell>
           <cell r="J22">
-            <v>323400</v>
+            <v>294000</v>
           </cell>
           <cell r="K22">
-            <v>323400</v>
+            <v>294000</v>
           </cell>
           <cell r="L22">
-            <v>323400</v>
+            <v>294000</v>
           </cell>
         </row>
         <row r="23">
@@ -2338,13 +2335,13 @@
             <v>Concrete formwork for foundation, foundation bracing, foundation, wall bracing, foundation wall, lobby, steps</v>
           </cell>
           <cell r="J23">
-            <v>332904</v>
+            <v>302640</v>
           </cell>
           <cell r="K23">
-            <v>332904</v>
+            <v>302640</v>
           </cell>
           <cell r="L23">
-            <v>332904</v>
+            <v>302640</v>
           </cell>
         </row>
         <row r="24">
@@ -2352,13 +2349,13 @@
             <v>Supply and install anchor bolts</v>
           </cell>
           <cell r="J24">
-            <v>37345</v>
+            <v>33950</v>
           </cell>
           <cell r="K24">
-            <v>37345</v>
+            <v>33950</v>
           </cell>
           <cell r="L24">
-            <v>37345</v>
+            <v>33950</v>
           </cell>
         </row>
         <row r="25">
@@ -2366,13 +2363,13 @@
             <v>Plastering outdoor</v>
           </cell>
           <cell r="J25">
-            <v>90695.000000000015</v>
+            <v>82450</v>
           </cell>
           <cell r="K25">
-            <v>90695.000000000015</v>
+            <v>82450</v>
           </cell>
           <cell r="L25">
-            <v>90695.000000000015</v>
+            <v>82450</v>
           </cell>
         </row>
         <row r="26">
@@ -2380,13 +2377,13 @@
             <v>External wall painting, foundation of cabinet, substation…</v>
           </cell>
           <cell r="J26">
-            <v>101200.00000000001</v>
+            <v>92000</v>
           </cell>
           <cell r="K26">
-            <v>101200.00000000001</v>
+            <v>92000</v>
           </cell>
           <cell r="L26">
-            <v>101200.00000000001</v>
+            <v>92000</v>
           </cell>
         </row>
         <row r="28">
@@ -2394,13 +2391,13 @@
             <v>Excavation of foundation soil by machine combined with manual repair</v>
           </cell>
           <cell r="J28">
-            <v>138710</v>
+            <v>126100</v>
           </cell>
           <cell r="K28">
-            <v>138710</v>
+            <v>126100</v>
           </cell>
           <cell r="L28">
-            <v>138710</v>
+            <v>126100</v>
           </cell>
         </row>
         <row r="31">
@@ -2408,13 +2405,13 @@
             <v>Transporting soil to gather internally within the project</v>
           </cell>
           <cell r="J31">
-            <v>132000</v>
+            <v>120000</v>
           </cell>
           <cell r="K31">
-            <v>132000</v>
+            <v>120000</v>
           </cell>
           <cell r="L31">
-            <v>132000</v>
+            <v>120000</v>
           </cell>
         </row>
         <row r="32">
@@ -2422,13 +2419,13 @@
             <v>Concrete foundation lining, foundation bracing, foundation lining</v>
           </cell>
           <cell r="J32">
-            <v>1333750</v>
+            <v>1212500</v>
           </cell>
           <cell r="K32">
-            <v>1333750</v>
+            <v>1212500</v>
           </cell>
           <cell r="L32">
-            <v>1333750</v>
+            <v>1212500</v>
           </cell>
         </row>
         <row r="33">
@@ -2436,13 +2433,13 @@
             <v>Concrete foundation, foundation bracing, foundation</v>
           </cell>
           <cell r="J33">
-            <v>1920600.0000000002</v>
+            <v>1746000</v>
           </cell>
           <cell r="K33">
-            <v>1920600.0000000002</v>
+            <v>1746000</v>
           </cell>
           <cell r="L33">
-            <v>1920600.0000000002</v>
+            <v>1746000</v>
           </cell>
         </row>
         <row r="34">
@@ -2450,13 +2447,13 @@
             <v>Formwork of all kinds</v>
           </cell>
           <cell r="J34">
-            <v>323400</v>
+            <v>294000</v>
           </cell>
           <cell r="K34">
-            <v>323400</v>
+            <v>294000</v>
           </cell>
           <cell r="L34">
-            <v>323400</v>
+            <v>294000</v>
           </cell>
         </row>
         <row r="35">
@@ -2464,13 +2461,13 @@
             <v>Concrete formwork for foundation, foundation bracing, foundation, wall bracing, foundation wall, lobby, steps</v>
           </cell>
           <cell r="J35">
-            <v>332904</v>
+            <v>302640</v>
           </cell>
           <cell r="K35">
-            <v>332904</v>
+            <v>302640</v>
           </cell>
           <cell r="L35">
-            <v>332904</v>
+            <v>302640</v>
           </cell>
         </row>
         <row r="36">
@@ -2478,13 +2475,13 @@
             <v>Supply and install anchor bolts</v>
           </cell>
           <cell r="J36">
-            <v>37345</v>
+            <v>33950</v>
           </cell>
           <cell r="K36">
-            <v>37345</v>
+            <v>33950</v>
           </cell>
           <cell r="L36">
-            <v>37345</v>
+            <v>33950</v>
           </cell>
         </row>
         <row r="37">
@@ -2492,13 +2489,13 @@
             <v>Plastering outdoor</v>
           </cell>
           <cell r="J37">
-            <v>90695.000000000015</v>
+            <v>82450</v>
           </cell>
           <cell r="K37">
-            <v>90695.000000000015</v>
+            <v>82450</v>
           </cell>
           <cell r="L37">
-            <v>90695.000000000015</v>
+            <v>82450</v>
           </cell>
         </row>
         <row r="38">
@@ -2506,13 +2503,13 @@
             <v>External wall painting, foundation of cabinet, substation…</v>
           </cell>
           <cell r="J38">
-            <v>101200.00000000001</v>
+            <v>92000</v>
           </cell>
           <cell r="K38">
-            <v>101200.00000000001</v>
+            <v>92000</v>
           </cell>
           <cell r="L38">
-            <v>101200.00000000001</v>
+            <v>92000</v>
           </cell>
         </row>
         <row r="40">
@@ -2520,13 +2517,13 @@
             <v>Line marking</v>
           </cell>
           <cell r="J40">
-            <v>53350.000000000007</v>
+            <v>48500</v>
           </cell>
           <cell r="K40">
-            <v>53350.000000000007</v>
+            <v>48500</v>
           </cell>
           <cell r="L40">
-            <v>53350.000000000007</v>
+            <v>48500</v>
           </cell>
         </row>
         <row r="41">
@@ -2534,13 +2531,13 @@
             <v>Car stops</v>
           </cell>
           <cell r="J41">
-            <v>234740.00000000003</v>
+            <v>213400</v>
           </cell>
           <cell r="K41">
-            <v>234740.00000000003</v>
+            <v>213400</v>
           </cell>
           <cell r="L41">
-            <v>234740.00000000003</v>
+            <v>213400</v>
           </cell>
         </row>
         <row r="43">
@@ -2548,13 +2545,13 @@
             <v>3kg CO2 portable fire extinguisher</v>
           </cell>
           <cell r="J43">
-            <v>1562000.0000000002</v>
+            <v>1420000</v>
           </cell>
           <cell r="K43">
-            <v>1562000.0000000002</v>
+            <v>1420000</v>
           </cell>
           <cell r="L43">
-            <v>1562000.0000000002</v>
+            <v>1420000</v>
           </cell>
         </row>
         <row r="44">
@@ -2562,13 +2559,13 @@
             <v>Fire extinguisher rack (Dimensions: 500x200x200mm, 1.2mm thick sheet metal, powder coated), 100mm high legs</v>
           </cell>
           <cell r="J44">
-            <v>1004953.95</v>
+            <v>913594.49999999988</v>
           </cell>
           <cell r="K44">
-            <v>1004953.95</v>
+            <v>913594.49999999988</v>
           </cell>
           <cell r="L44">
-            <v>1004953.95</v>
+            <v>913594.49999999988</v>
           </cell>
         </row>
         <row r="47">
@@ -2576,7 +2573,7 @@
             <v>LT-PANEL electrical cabinet - 1x 20kW poles  3P</v>
           </cell>
           <cell r="J47">
-            <v>5548400</v>
+            <v>5044000</v>
           </cell>
         </row>
         <row r="48">
@@ -2584,7 +2581,7 @@
             <v>LT-PANEL electrical cabinet - 1x 30kW poles  3P</v>
           </cell>
           <cell r="K48">
-            <v>6935500.0000000009</v>
+            <v>6305000</v>
           </cell>
         </row>
         <row r="49">
@@ -2592,7 +2589,7 @@
             <v>LT-PANEL electrical cabinet - 1x 60kW poles  3P</v>
           </cell>
           <cell r="L49">
-            <v>11737000.000000002</v>
+            <v>10670000</v>
           </cell>
         </row>
         <row r="55">
@@ -2600,7 +2597,7 @@
             <v>60kW Charging Pole</v>
           </cell>
           <cell r="L55">
-            <v>6402000.0000000009</v>
+            <v>5820000</v>
           </cell>
         </row>
         <row r="56">
@@ -2608,7 +2605,7 @@
             <v>Charging Pole 30KW</v>
           </cell>
           <cell r="K56">
-            <v>4801500</v>
+            <v>4365000</v>
           </cell>
         </row>
         <row r="57">
@@ -2616,7 +2613,7 @@
             <v>20KW Charging Tower</v>
           </cell>
           <cell r="J57">
-            <v>3201000.0000000005</v>
+            <v>2910000</v>
           </cell>
         </row>
         <row r="58">
@@ -2624,13 +2621,13 @@
             <v>Sticker EV Charger (DTF type)</v>
           </cell>
           <cell r="J58">
-            <v>110000.00000000001</v>
+            <v>100000</v>
           </cell>
           <cell r="K58">
-            <v>110000.00000000001</v>
+            <v>100000</v>
           </cell>
           <cell r="L58">
-            <v>110000.00000000001</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="60">
@@ -2638,7 +2635,7 @@
             <v>NA2XY (4Cx16)mm2 + E-NAYA (1Cx16)mm2 (from KWH to AC Panel)</v>
           </cell>
           <cell r="J60">
-            <v>86513.426999999996</v>
+            <v>78648.569999999992</v>
           </cell>
         </row>
         <row r="61">
@@ -2646,7 +2643,7 @@
             <v>NA2XY (4Cx16)mm2 + E-NAYA (1Cx16)mm2 (from AC Panel to Charger)</v>
           </cell>
           <cell r="J61">
-            <v>86513.426999999996</v>
+            <v>78648.569999999992</v>
           </cell>
         </row>
         <row r="62">
@@ -2654,7 +2651,7 @@
             <v>Cable Ground NYA 6mm with rod and grounding clamp</v>
           </cell>
           <cell r="J62">
-            <v>19800</v>
+            <v>18000</v>
           </cell>
         </row>
         <row r="63">
@@ -2662,7 +2659,7 @@
             <v>nA2Xy (3Cx25+1CX16) mm2 +e-nAya (1x16)mm2 (from KWH to AC Panel)</v>
           </cell>
           <cell r="K63">
-            <v>176734.5723</v>
+            <v>160667.79299999998</v>
           </cell>
         </row>
         <row r="64">
@@ -2670,7 +2667,7 @@
             <v>nA2Xy (3Cx25+1CX16) mm2 +e-nAya (1x16)mm2 (from AC Panel to Charger)</v>
           </cell>
           <cell r="K64">
-            <v>176734.5723</v>
+            <v>160667.79299999998</v>
           </cell>
         </row>
         <row r="65">
@@ -2678,7 +2675,7 @@
             <v>Cable Ground NYA 10mm with rod and grounding clamp</v>
           </cell>
           <cell r="K65">
-            <v>34100</v>
+            <v>31000</v>
           </cell>
         </row>
         <row r="66">
@@ -2686,7 +2683,7 @@
             <v>nA2Xy 3Cx95+N.(1X50)mm2+e-nAya (1x50)mm2 (from KWH to AC Panel)</v>
           </cell>
           <cell r="L66">
-            <v>291982.81612500007</v>
+            <v>265438.92375000002</v>
           </cell>
         </row>
         <row r="67">
@@ -2694,7 +2691,7 @@
             <v>nA2Xy 3Cx95+N.(1X50)mm2+e-nAya (1x50)mm2 (from AC Panel to Charger)</v>
           </cell>
           <cell r="L67">
-            <v>291982.81612500007</v>
+            <v>265438.92375000002</v>
           </cell>
         </row>
         <row r="68">
@@ -2702,7 +2699,7 @@
             <v>Cable Ground NYA 16mm with rod and grounding clamp</v>
           </cell>
           <cell r="L68">
-            <v>61050.000000000007</v>
+            <v>55500</v>
           </cell>
         </row>
         <row r="76">
@@ -2710,13 +2707,13 @@
             <v>Excavation of foundation pits and trenches by machine</v>
           </cell>
           <cell r="J76">
-            <v>128040.00000000001</v>
+            <v>116400</v>
           </cell>
           <cell r="K76">
-            <v>128040.00000000001</v>
+            <v>116400</v>
           </cell>
           <cell r="L76">
-            <v>128040.00000000001</v>
+            <v>116400</v>
           </cell>
         </row>
         <row r="77">
@@ -2724,13 +2721,13 @@
             <v>Backfilling with vibratory compactors</v>
           </cell>
           <cell r="J77">
-            <v>154715</v>
+            <v>140650</v>
           </cell>
           <cell r="K77">
-            <v>154715</v>
+            <v>140650</v>
           </cell>
           <cell r="L77">
-            <v>154715</v>
+            <v>140650</v>
           </cell>
         </row>
         <row r="78">
@@ -2738,13 +2735,13 @@
             <v>D300 warning tape</v>
           </cell>
           <cell r="J78">
-            <v>16005.000000000002</v>
+            <v>14550</v>
           </cell>
           <cell r="K78">
-            <v>16005.000000000002</v>
+            <v>14550</v>
           </cell>
           <cell r="L78">
-            <v>16005.000000000002</v>
+            <v>14550</v>
           </cell>
         </row>
         <row r="79">
@@ -2752,13 +2749,13 @@
             <v>Other materials: Adhesives, tapes, plastic cable ties, fire starters, bolts, nuts, tie rod connectors, washers, expansion anchors, pipe clamps, rods Welding, Teflon tape, rubber-cushioned jute rope, rags, foam glue, gaskets, marking, labeling. Elbows, tees, pipe connectors, plastic pipe clamps, end caps (for conduit), conduit connectors, ladder connectors, grounding, terminal lugs &lt;50mm2, etc.</v>
           </cell>
           <cell r="J79">
-            <v>373450.00000000006</v>
+            <v>339500</v>
           </cell>
           <cell r="K79">
-            <v>373450.00000000006</v>
+            <v>339500</v>
           </cell>
           <cell r="L79">
-            <v>373450.00000000006</v>
+            <v>339500</v>
           </cell>
         </row>
         <row r="80">
@@ -2766,13 +2763,13 @@
             <v>Biaya transport dan Survey (JAVA)</v>
           </cell>
           <cell r="J80">
-            <v>1100000</v>
+            <v>1000000</v>
           </cell>
           <cell r="K80">
-            <v>1100000</v>
+            <v>1000000</v>
           </cell>
           <cell r="L80">
-            <v>1100000</v>
+            <v>1000000</v>
           </cell>
         </row>
       </sheetData>
@@ -3121,10 +3118,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="152"/>
+      <c r="B1" s="162"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:10">
@@ -3135,13 +3132,13 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="13.15" customHeight="1">
-      <c r="A3" s="153" t="s">
+      <c r="A3" s="163" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="153"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="153"/>
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:10" ht="13.15" customHeight="1">
@@ -3151,10 +3148,10 @@
     <row r="5" spans="1:10" ht="25.5" customHeight="1">
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="G5" s="156" t="s">
+      <c r="G5" s="165" t="s">
         <v>153</v>
       </c>
-      <c r="H5" s="155"/>
+      <c r="H5" s="166"/>
     </row>
     <row r="6" spans="1:10" s="47" customFormat="1" ht="16.5" thickBot="1">
       <c r="A6" s="43" t="s">
@@ -3166,10 +3163,10 @@
       <c r="C6" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="154" t="s">
+      <c r="D6" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="154"/>
+      <c r="E6" s="164"/>
       <c r="F6" s="43" t="s">
         <v>7</v>
       </c>
@@ -3181,11 +3178,11 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="151"/>
-      <c r="E7" s="151"/>
+      <c r="A7" s="159"/>
+      <c r="B7" s="160"/>
+      <c r="C7" s="161"/>
+      <c r="D7" s="161"/>
+      <c r="E7" s="161"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:10" ht="16">
@@ -3227,7 +3224,7 @@
         <v>16</v>
       </c>
       <c r="G9" s="10">
-        <f>IF(B9='[2]Breakdown from VHM BOQ'!B9,'[2]Breakdown from VHM BOQ'!J9,"")*1.1</f>
+        <f>IF(B9='[1]Breakdown from VHM BOQ'!B9,'[1]Breakdown from VHM BOQ'!J9,"")*1.1</f>
         <v>94.600000000000009</v>
       </c>
       <c r="H9" s="11">
@@ -3253,7 +3250,7 @@
         <v>16</v>
       </c>
       <c r="G10" s="10">
-        <f>IF(B10='[2]Breakdown from VHM BOQ'!B10,'[2]Breakdown from VHM BOQ'!J10,"")*1.1</f>
+        <f>IF(B10='[1]Breakdown from VHM BOQ'!B10,'[1]Breakdown from VHM BOQ'!J10,"")*1.1</f>
         <v>94.600000000000009</v>
       </c>
       <c r="H10" s="11">
@@ -3279,7 +3276,7 @@
         <v>16</v>
       </c>
       <c r="G11" s="10">
-        <f>IF(B11='[2]Breakdown from VHM BOQ'!B11,'[2]Breakdown from VHM BOQ'!J11,"")*1.1</f>
+        <f>IF(B11='[1]Breakdown from VHM BOQ'!B11,'[1]Breakdown from VHM BOQ'!J11,"")*1.1</f>
         <v>3348400.0000000005</v>
       </c>
       <c r="H11" s="11">
@@ -3360,7 +3357,7 @@
         <v>16</v>
       </c>
       <c r="G15" s="10">
-        <f>IF(B15='[2]Breakdown from VHM BOQ'!B15,'[2]Breakdown from VHM BOQ'!J15,"")</f>
+        <f>IF(B15='[1]Breakdown from VHM BOQ'!B15,'[1]Breakdown from VHM BOQ'!J15,"")</f>
         <v>138710</v>
       </c>
       <c r="H15" s="11">
@@ -3390,7 +3387,7 @@
         <v>16</v>
       </c>
       <c r="G16" s="10">
-        <f>IF(B16='[2]Breakdown from VHM BOQ'!B18,'[2]Breakdown from VHM BOQ'!J18,"")</f>
+        <f>IF(B16='[1]Breakdown from VHM BOQ'!B18,'[1]Breakdown from VHM BOQ'!J18,"")</f>
         <v>132000</v>
       </c>
       <c r="H16" s="11">
@@ -3418,7 +3415,7 @@
         <v>16</v>
       </c>
       <c r="G17" s="10">
-        <f>IF(B17='[2]Breakdown from VHM BOQ'!B19,'[2]Breakdown from VHM BOQ'!J19,"")</f>
+        <f>IF(B17='[1]Breakdown from VHM BOQ'!B19,'[1]Breakdown from VHM BOQ'!J19,"")</f>
         <v>16005.000000000002</v>
       </c>
       <c r="H17" s="11">
@@ -3449,7 +3446,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="10">
-        <f>IF(B18='[2]Breakdown from VHM BOQ'!B20,'[2]Breakdown from VHM BOQ'!J20,"")</f>
+        <f>IF(B18='[1]Breakdown from VHM BOQ'!B20,'[1]Breakdown from VHM BOQ'!J20,"")</f>
         <v>1333750</v>
       </c>
       <c r="H18" s="11">
@@ -3479,7 +3476,7 @@
         <v>16</v>
       </c>
       <c r="G19" s="10">
-        <f>IF(B19='[2]Breakdown from VHM BOQ'!B21,'[2]Breakdown from VHM BOQ'!J21,"")</f>
+        <f>IF(B19='[1]Breakdown from VHM BOQ'!B21,'[1]Breakdown from VHM BOQ'!J21,"")</f>
         <v>1920600.0000000002</v>
       </c>
       <c r="H19" s="11">
@@ -3509,7 +3506,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="10">
-        <f>IF(B20='[2]Breakdown from VHM BOQ'!B22,'[2]Breakdown from VHM BOQ'!J22,"")</f>
+        <f>IF(B20='[1]Breakdown from VHM BOQ'!B22,'[1]Breakdown from VHM BOQ'!J22,"")</f>
         <v>323400</v>
       </c>
       <c r="H20" s="11">
@@ -3539,7 +3536,7 @@
         <v>16</v>
       </c>
       <c r="G21" s="10">
-        <f>IF(B21='[2]Breakdown from VHM BOQ'!B23,'[2]Breakdown from VHM BOQ'!J23,"")</f>
+        <f>IF(B21='[1]Breakdown from VHM BOQ'!B23,'[1]Breakdown from VHM BOQ'!J23,"")</f>
         <v>332904</v>
       </c>
       <c r="H21" s="11">
@@ -3569,7 +3566,7 @@
         <v>16</v>
       </c>
       <c r="G22" s="10">
-        <f>IF(B22='[2]Breakdown from VHM BOQ'!B24,'[2]Breakdown from VHM BOQ'!J24,"")</f>
+        <f>IF(B22='[1]Breakdown from VHM BOQ'!B24,'[1]Breakdown from VHM BOQ'!J24,"")</f>
         <v>37345</v>
       </c>
       <c r="H22" s="11">
@@ -3599,7 +3596,7 @@
         <v>16</v>
       </c>
       <c r="G23" s="10">
-        <f>IF(B23='[2]Breakdown from VHM BOQ'!B25,'[2]Breakdown from VHM BOQ'!J25,"")</f>
+        <f>IF(B23='[1]Breakdown from VHM BOQ'!B25,'[1]Breakdown from VHM BOQ'!J25,"")</f>
         <v>90695.000000000015</v>
       </c>
       <c r="H23" s="11">
@@ -3629,7 +3626,7 @@
         <v>16</v>
       </c>
       <c r="G24" s="10">
-        <f>IF(B24='[2]Breakdown from VHM BOQ'!B26,'[2]Breakdown from VHM BOQ'!J26,"")</f>
+        <f>IF(B24='[1]Breakdown from VHM BOQ'!B26,'[1]Breakdown from VHM BOQ'!J26,"")</f>
         <v>101200.00000000001</v>
       </c>
       <c r="H24" s="11">
@@ -3678,7 +3675,7 @@
         <v>16</v>
       </c>
       <c r="G26" s="10">
-        <f>IF(B26='[2]Breakdown from VHM BOQ'!B28,'[2]Breakdown from VHM BOQ'!J28,"")</f>
+        <f>IF(B26='[1]Breakdown from VHM BOQ'!B28,'[1]Breakdown from VHM BOQ'!J28,"")</f>
         <v>138710</v>
       </c>
       <c r="H26" s="11">
@@ -3708,7 +3705,7 @@
         <v>16</v>
       </c>
       <c r="G27" s="10">
-        <f>IF(B27='[2]Breakdown from VHM BOQ'!B31,'[2]Breakdown from VHM BOQ'!J31,"")</f>
+        <f>IF(B27='[1]Breakdown from VHM BOQ'!B31,'[1]Breakdown from VHM BOQ'!J31,"")</f>
         <v>132000</v>
       </c>
       <c r="H27" s="11">
@@ -3738,7 +3735,7 @@
         <v>16</v>
       </c>
       <c r="G28" s="10">
-        <f>IF(B28='[2]Breakdown from VHM BOQ'!B32,'[2]Breakdown from VHM BOQ'!J32,"")</f>
+        <f>IF(B28='[1]Breakdown from VHM BOQ'!B32,'[1]Breakdown from VHM BOQ'!J32,"")</f>
         <v>1333750</v>
       </c>
       <c r="H28" s="11">
@@ -3768,7 +3765,7 @@
         <v>16</v>
       </c>
       <c r="G29" s="10">
-        <f>IF(B29='[2]Breakdown from VHM BOQ'!B33,'[2]Breakdown from VHM BOQ'!J33,"")</f>
+        <f>IF(B29='[1]Breakdown from VHM BOQ'!B33,'[1]Breakdown from VHM BOQ'!J33,"")</f>
         <v>1920600.0000000002</v>
       </c>
       <c r="H29" s="11">
@@ -3798,7 +3795,7 @@
         <v>16</v>
       </c>
       <c r="G30" s="10">
-        <f>IF(B30='[2]Breakdown from VHM BOQ'!B34,'[2]Breakdown from VHM BOQ'!J34,"")</f>
+        <f>IF(B30='[1]Breakdown from VHM BOQ'!B34,'[1]Breakdown from VHM BOQ'!J34,"")</f>
         <v>323400</v>
       </c>
       <c r="H30" s="11">
@@ -3828,7 +3825,7 @@
         <v>16</v>
       </c>
       <c r="G31" s="10">
-        <f>IF(B31='[2]Breakdown from VHM BOQ'!B35,'[2]Breakdown from VHM BOQ'!J35,"")</f>
+        <f>IF(B31='[1]Breakdown from VHM BOQ'!B35,'[1]Breakdown from VHM BOQ'!J35,"")</f>
         <v>332904</v>
       </c>
       <c r="H31" s="11">
@@ -3858,7 +3855,7 @@
         <v>16</v>
       </c>
       <c r="G32" s="10">
-        <f>IF(B32='[2]Breakdown from VHM BOQ'!B36,'[2]Breakdown from VHM BOQ'!J36,"")</f>
+        <f>IF(B32='[1]Breakdown from VHM BOQ'!B36,'[1]Breakdown from VHM BOQ'!J36,"")</f>
         <v>37345</v>
       </c>
       <c r="H32" s="11">
@@ -3888,7 +3885,7 @@
         <v>16</v>
       </c>
       <c r="G33" s="10">
-        <f>IF(B33='[2]Breakdown from VHM BOQ'!B37,'[2]Breakdown from VHM BOQ'!J37,"")</f>
+        <f>IF(B33='[1]Breakdown from VHM BOQ'!B37,'[1]Breakdown from VHM BOQ'!J37,"")</f>
         <v>90695.000000000015</v>
       </c>
       <c r="H33" s="11">
@@ -3918,7 +3915,7 @@
         <v>16</v>
       </c>
       <c r="G34" s="10">
-        <f>IF(B34='[2]Breakdown from VHM BOQ'!B38,'[2]Breakdown from VHM BOQ'!J38,"")</f>
+        <f>IF(B34='[1]Breakdown from VHM BOQ'!B38,'[1]Breakdown from VHM BOQ'!J38,"")</f>
         <v>101200.00000000001</v>
       </c>
       <c r="H34" s="11">
@@ -3968,7 +3965,7 @@
         <v>16</v>
       </c>
       <c r="G36" s="10">
-        <f>IF(B36='[2]Breakdown from VHM BOQ'!B40,'[2]Breakdown from VHM BOQ'!J40,"")</f>
+        <f>IF(B36='[1]Breakdown from VHM BOQ'!B40,'[1]Breakdown from VHM BOQ'!J40,"")</f>
         <v>53350.000000000007</v>
       </c>
       <c r="H36" s="11">
@@ -3998,7 +3995,7 @@
         <v>16</v>
       </c>
       <c r="G37" s="10">
-        <f>IF(B37='[2]Breakdown from VHM BOQ'!B41,'[2]Breakdown from VHM BOQ'!J41,"")</f>
+        <f>IF(B37='[1]Breakdown from VHM BOQ'!B41,'[1]Breakdown from VHM BOQ'!J41,"")</f>
         <v>234740.00000000003</v>
       </c>
       <c r="H37" s="11">
@@ -4045,7 +4042,7 @@
         <v>16</v>
       </c>
       <c r="G39" s="10">
-        <f>IF(B39='[2]Breakdown from VHM BOQ'!B43,'[2]Breakdown from VHM BOQ'!J43,"")</f>
+        <f>IF(B39='[1]Breakdown from VHM BOQ'!B43,'[1]Breakdown from VHM BOQ'!J43,"")</f>
         <v>1562000.0000000002</v>
       </c>
       <c r="H39" s="11">
@@ -4075,7 +4072,7 @@
         <v>16</v>
       </c>
       <c r="G40" s="10">
-        <f>IF(B40='[2]Breakdown from VHM BOQ'!B44,'[2]Breakdown from VHM BOQ'!J44,"")</f>
+        <f>IF(B40='[1]Breakdown from VHM BOQ'!B44,'[1]Breakdown from VHM BOQ'!J44,"")</f>
         <v>1004953.95</v>
       </c>
       <c r="H40" s="11">
@@ -4121,7 +4118,7 @@
         <v>64</v>
       </c>
       <c r="G42" s="10">
-        <f>IF(B42='[2]Breakdown from VHM BOQ'!B47,'[2]Breakdown from VHM BOQ'!J47,"")</f>
+        <f>IF(B42='[1]Breakdown from VHM BOQ'!B47,'[1]Breakdown from VHM BOQ'!J47,"")</f>
         <v>5548400</v>
       </c>
       <c r="H42" s="11">
@@ -4215,7 +4212,7 @@
         <v>16</v>
       </c>
       <c r="G46" s="10">
-        <f>IF(B46='[2]Breakdown from VHM BOQ'!B57,'[2]Breakdown from VHM BOQ'!J57,"")</f>
+        <f>IF(B46='[1]Breakdown from VHM BOQ'!B57,'[1]Breakdown from VHM BOQ'!J57,"")</f>
         <v>3201000.0000000005</v>
       </c>
       <c r="H46" s="11">
@@ -4243,7 +4240,7 @@
         <v>16</v>
       </c>
       <c r="G47" s="10">
-        <f>IF(B47='[2]Breakdown from VHM BOQ'!B58,'[2]Breakdown from VHM BOQ'!J58,"")</f>
+        <f>IF(B47='[1]Breakdown from VHM BOQ'!B58,'[1]Breakdown from VHM BOQ'!J58,"")</f>
         <v>110000.00000000001</v>
       </c>
       <c r="H47" s="11">
@@ -4290,7 +4287,7 @@
         <v>76</v>
       </c>
       <c r="G49" s="10">
-        <f>IF(B49='[2]Breakdown from VHM BOQ'!B60,'[2]Breakdown from VHM BOQ'!J60,"")</f>
+        <f>IF(B49='[1]Breakdown from VHM BOQ'!B60,'[1]Breakdown from VHM BOQ'!J60,"")</f>
         <v>86513.426999999996</v>
       </c>
       <c r="H49" s="11">
@@ -4318,7 +4315,7 @@
         <v>76</v>
       </c>
       <c r="G50" s="10">
-        <f>IF(B50='[2]Breakdown from VHM BOQ'!B61,'[2]Breakdown from VHM BOQ'!J61,"")</f>
+        <f>IF(B50='[1]Breakdown from VHM BOQ'!B61,'[1]Breakdown from VHM BOQ'!J61,"")</f>
         <v>86513.426999999996</v>
       </c>
       <c r="H50" s="11">
@@ -4346,7 +4343,7 @@
         <v>76</v>
       </c>
       <c r="G51" s="10">
-        <f>IF(B51='[2]Breakdown from VHM BOQ'!B62,'[2]Breakdown from VHM BOQ'!J62,"")</f>
+        <f>IF(B51='[1]Breakdown from VHM BOQ'!B62,'[1]Breakdown from VHM BOQ'!J62,"")</f>
         <v>19800</v>
       </c>
       <c r="H51" s="11">
@@ -4403,7 +4400,7 @@
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="10">
-        <f>IF(B53='[2]Breakdown from VHM BOQ'!B76,'[2]Breakdown from VHM BOQ'!J76,"")</f>
+        <f>IF(B53='[1]Breakdown from VHM BOQ'!B76,'[1]Breakdown from VHM BOQ'!J76,"")</f>
         <v>128040.00000000001</v>
       </c>
       <c r="H53" s="11">
@@ -4432,7 +4429,7 @@
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="10">
-        <f>IF(B54='[2]Breakdown from VHM BOQ'!B77,'[2]Breakdown from VHM BOQ'!J77,"")</f>
+        <f>IF(B54='[1]Breakdown from VHM BOQ'!B77,'[1]Breakdown from VHM BOQ'!J77,"")</f>
         <v>154715</v>
       </c>
       <c r="H54" s="11">
@@ -4459,7 +4456,7 @@
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="10">
-        <f>IF(B55='[2]Breakdown from VHM BOQ'!B78,'[2]Breakdown from VHM BOQ'!J78,"")</f>
+        <f>IF(B55='[1]Breakdown from VHM BOQ'!B78,'[1]Breakdown from VHM BOQ'!J78,"")</f>
         <v>16005.000000000002</v>
       </c>
       <c r="H55" s="11">
@@ -4487,7 +4484,7 @@
         <v>16</v>
       </c>
       <c r="G56" s="10">
-        <f>IF(B56='[2]Breakdown from VHM BOQ'!B79,'[2]Breakdown from VHM BOQ'!J79,"")</f>
+        <f>IF(B56='[1]Breakdown from VHM BOQ'!B79,'[1]Breakdown from VHM BOQ'!J79,"")</f>
         <v>373450.00000000006</v>
       </c>
       <c r="H56" s="11">
@@ -4511,7 +4508,7 @@
       <c r="E57" s="52"/>
       <c r="F57" s="53"/>
       <c r="G57" s="58">
-        <f>IF(B57='[2]Breakdown from VHM BOQ'!B80,'[2]Breakdown from VHM BOQ'!J80,"")</f>
+        <f>IF(B57='[1]Breakdown from VHM BOQ'!B80,'[1]Breakdown from VHM BOQ'!J80,"")</f>
         <v>1100000</v>
       </c>
       <c r="H57" s="51">
@@ -4573,117 +4570,117 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="18.5">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="162"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
     </row>
     <row r="3" spans="1:9" ht="14.5">
-      <c r="A3" s="109" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
+      <c r="A3" s="108" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
     </row>
     <row r="4" spans="1:9" ht="14.5">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="162"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
+      <c r="B4" s="152"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
     </row>
     <row r="5" spans="1:9" ht="14.5">
-      <c r="A5" s="111"/>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
+      <c r="A5" s="110"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A6" s="110"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="164" t="s">
+      <c r="A6" s="109"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="F6" s="165"/>
-      <c r="G6" s="166"/>
+      <c r="F6" s="155"/>
+      <c r="G6" s="156"/>
     </row>
     <row r="7" spans="1:9" ht="14.5">
-      <c r="A7" s="107" t="s">
+      <c r="A7" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="107" t="s">
+      <c r="B7" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="167" t="s">
+      <c r="C7" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="168"/>
-      <c r="E7" s="107" t="s">
+      <c r="D7" s="158"/>
+      <c r="E7" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="106" t="s">
+      <c r="F7" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="106" t="s">
+      <c r="G7" s="105" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.5">
-      <c r="A8" s="100" t="s">
+      <c r="A8" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="99" t="s">
+      <c r="B8" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="100">
-        <v>1</v>
-      </c>
-      <c r="D8" s="100" t="s">
+      <c r="C8" s="99">
+        <v>1</v>
+      </c>
+      <c r="D8" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="100"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96">
+      <c r="E8" s="99"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95">
         <f>SUM(G9:G12)</f>
         <v>3630000</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.5">
-      <c r="A9" s="76">
-        <v>1</v>
-      </c>
-      <c r="B9" s="79" t="s">
+      <c r="A9" s="75">
+        <v>1</v>
+      </c>
+      <c r="B9" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="76">
+      <c r="C9" s="75">
         <v>7700</v>
       </c>
-      <c r="D9" s="76" t="s">
+      <c r="D9" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="76"/>
-      <c r="F9" s="72">
+      <c r="E9" s="75"/>
+      <c r="F9" s="71">
         <v>94.600000000000009</v>
       </c>
-      <c r="G9" s="72">
+      <c r="G9" s="71">
         <f>C9*F9</f>
         <v>728420.00000000012</v>
       </c>
@@ -4691,23 +4688,23 @@
       <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9" ht="14.5">
-      <c r="A10" s="76">
+      <c r="A10" s="75">
         <v>2</v>
       </c>
-      <c r="B10" s="79" t="s">
+      <c r="B10" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="76">
+      <c r="C10" s="75">
         <v>7700</v>
       </c>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="76"/>
-      <c r="F10" s="72">
+      <c r="E10" s="75"/>
+      <c r="F10" s="71">
         <v>94.600000000000009</v>
       </c>
-      <c r="G10" s="72">
+      <c r="G10" s="71">
         <f>C10*F10</f>
         <v>728420.00000000012</v>
       </c>
@@ -4715,23 +4712,23 @@
       <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9" ht="14.5">
-      <c r="A11" s="76">
+      <c r="A11" s="75">
         <v>3</v>
       </c>
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="76">
-        <v>1</v>
-      </c>
-      <c r="D11" s="76" t="s">
+      <c r="C11" s="75">
+        <v>1</v>
+      </c>
+      <c r="D11" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="76"/>
-      <c r="F11" s="72">
+      <c r="E11" s="75"/>
+      <c r="F11" s="71">
         <v>2530000</v>
       </c>
-      <c r="G11" s="72">
+      <c r="G11" s="71">
         <f>C11*F11</f>
         <v>2530000</v>
       </c>
@@ -4739,19 +4736,19 @@
       <c r="I11" s="27"/>
     </row>
     <row r="12" spans="1:9" ht="14.5">
-      <c r="A12" s="76"/>
-      <c r="B12" s="105" t="s">
+      <c r="A12" s="75"/>
+      <c r="B12" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="104">
-        <v>1</v>
-      </c>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="103">
+      <c r="C12" s="103">
+        <v>1</v>
+      </c>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="102">
         <v>-356840</v>
       </c>
-      <c r="G12" s="103">
+      <c r="G12" s="102">
         <f>F12*C12</f>
         <v>-356840</v>
       </c>
@@ -4759,21 +4756,21 @@
       <c r="I12" s="27"/>
     </row>
     <row r="13" spans="1:9" ht="14.5">
-      <c r="A13" s="100" t="s">
+      <c r="A13" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="99" t="s">
+      <c r="B13" s="98" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="98">
-        <v>1</v>
-      </c>
-      <c r="D13" s="98" t="s">
+      <c r="C13" s="97">
+        <v>1</v>
+      </c>
+      <c r="D13" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="98"/>
-      <c r="F13" s="97"/>
-      <c r="G13" s="96">
+      <c r="E13" s="97"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="95">
         <f>SUM(G14:G15)</f>
         <v>1155000</v>
       </c>
@@ -4781,25 +4778,25 @@
       <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9" ht="14.5">
-      <c r="A14" s="76">
-        <v>1</v>
-      </c>
-      <c r="B14" s="77" t="s">
+      <c r="A14" s="75">
+        <v>1</v>
+      </c>
+      <c r="B14" s="76" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="76">
-        <v>1</v>
-      </c>
-      <c r="D14" s="76" t="s">
+      <c r="C14" s="75">
+        <v>1</v>
+      </c>
+      <c r="D14" s="75" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="76" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="72">
+      <c r="E14" s="75" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="71">
         <v>275000</v>
       </c>
-      <c r="G14" s="72">
+      <c r="G14" s="71">
         <f>C14*F14</f>
         <v>275000</v>
       </c>
@@ -4807,25 +4804,25 @@
       <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9" ht="14.5">
-      <c r="A15" s="76">
+      <c r="A15" s="75">
         <v>2</v>
       </c>
-      <c r="B15" s="79" t="s">
+      <c r="B15" s="78" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="76">
-        <v>1</v>
-      </c>
-      <c r="D15" s="76" t="s">
+      <c r="C15" s="75">
+        <v>1</v>
+      </c>
+      <c r="D15" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="76" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="72">
+      <c r="E15" s="75" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="71">
         <v>880000.00000000012</v>
       </c>
-      <c r="G15" s="72">
+      <c r="G15" s="71">
         <f>C15*F15</f>
         <v>880000.00000000012</v>
       </c>
@@ -4833,28 +4830,28 @@
       <c r="I15" s="27"/>
     </row>
     <row r="16" spans="1:9" ht="14.5">
-      <c r="A16" s="76"/>
-      <c r="B16" s="79"/>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="72"/>
+      <c r="A16" s="75"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
       <c r="H16" s="68"/>
       <c r="I16" s="27"/>
     </row>
     <row r="17" spans="1:9" ht="14.5">
-      <c r="A17" s="100" t="s">
+      <c r="A17" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="99" t="s">
+      <c r="B17" s="98" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="97"/>
-      <c r="G17" s="96">
+      <c r="C17" s="97"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="97"/>
+      <c r="F17" s="96"/>
+      <c r="G17" s="95">
         <f>SUM(G18)</f>
         <v>1650000.0000000002</v>
       </c>
@@ -4862,25 +4859,25 @@
       <c r="I17" s="27"/>
     </row>
     <row r="18" spans="1:9" ht="14.5">
-      <c r="A18" s="76">
-        <v>1</v>
-      </c>
-      <c r="B18" s="79" t="s">
+      <c r="A18" s="75">
+        <v>1</v>
+      </c>
+      <c r="B18" s="78" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="76">
-        <v>1</v>
-      </c>
-      <c r="D18" s="76" t="s">
+      <c r="C18" s="75">
+        <v>1</v>
+      </c>
+      <c r="D18" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="F18" s="72">
+      <c r="F18" s="71">
         <v>1650000.0000000002</v>
       </c>
-      <c r="G18" s="72">
+      <c r="G18" s="71">
         <f>C18*F18</f>
         <v>1650000.0000000002</v>
       </c>
@@ -4888,28 +4885,28 @@
       <c r="I18" s="27"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A19" s="102"/>
-      <c r="B19" s="101"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
       <c r="H19" s="68"/>
       <c r="I19" s="27"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="99" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="99" t="s">
+      <c r="B20" s="98" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="98"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="96">
+      <c r="C20" s="97"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="95">
         <f>SUM(G21:G25)</f>
         <v>4922500</v>
       </c>
@@ -4917,25 +4914,25 @@
       <c r="I20" s="27"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A21" s="76">
-        <v>1</v>
-      </c>
-      <c r="B21" s="81" t="s">
+      <c r="A21" s="75">
+        <v>1</v>
+      </c>
+      <c r="B21" s="80" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="76">
+      <c r="C21" s="75">
         <v>15</v>
       </c>
-      <c r="D21" s="76" t="s">
+      <c r="D21" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="94" t="s">
+      <c r="E21" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="94">
         <v>165000</v>
       </c>
-      <c r="G21" s="72">
+      <c r="G21" s="71">
         <f>C21*F21</f>
         <v>2475000</v>
       </c>
@@ -4943,25 +4940,25 @@
       <c r="I21" s="27"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A22" s="76">
+      <c r="A22" s="75">
         <v>2</v>
       </c>
-      <c r="B22" s="79" t="s">
+      <c r="B22" s="78" t="s">
         <v>126</v>
       </c>
-      <c r="C22" s="76">
+      <c r="C22" s="75">
         <v>5</v>
       </c>
-      <c r="D22" s="76" t="s">
+      <c r="D22" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="E22" s="94" t="s">
+      <c r="E22" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="94">
         <v>55000.000000000007</v>
       </c>
-      <c r="G22" s="72">
+      <c r="G22" s="71">
         <f>C22*F22</f>
         <v>275000.00000000006</v>
       </c>
@@ -4969,25 +4966,25 @@
       <c r="I22" s="27"/>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A23" s="76">
+      <c r="A23" s="75">
         <v>3</v>
       </c>
-      <c r="B23" s="79" t="s">
+      <c r="B23" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="76">
+      <c r="C23" s="75">
         <v>15</v>
       </c>
-      <c r="D23" s="76" t="s">
+      <c r="D23" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="94" t="s">
+      <c r="E23" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="F23" s="72">
+      <c r="F23" s="71">
         <v>38500</v>
       </c>
-      <c r="G23" s="72">
+      <c r="G23" s="71">
         <f>C23*F23</f>
         <v>577500</v>
       </c>
@@ -4995,23 +4992,23 @@
       <c r="I23" s="27"/>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A24" s="76">
+      <c r="A24" s="75">
         <v>4</v>
       </c>
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="76">
-        <v>1</v>
-      </c>
-      <c r="D24" s="76" t="s">
+      <c r="C24" s="75">
+        <v>1</v>
+      </c>
+      <c r="D24" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="76"/>
-      <c r="F24" s="72">
+      <c r="E24" s="75"/>
+      <c r="F24" s="71">
         <v>1100000</v>
       </c>
-      <c r="G24" s="72">
+      <c r="G24" s="71">
         <f>C24*F24</f>
         <v>1100000</v>
       </c>
@@ -5019,25 +5016,25 @@
       <c r="I24" s="27"/>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A25" s="76">
+      <c r="A25" s="75">
         <v>5</v>
       </c>
-      <c r="B25" s="79" t="s">
+      <c r="B25" s="78" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="76">
+      <c r="C25" s="75">
         <v>15</v>
       </c>
-      <c r="D25" s="76" t="s">
+      <c r="D25" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="76" t="s">
+      <c r="E25" s="75" t="s">
         <v>129</v>
       </c>
-      <c r="F25" s="72">
+      <c r="F25" s="71">
         <v>33000</v>
       </c>
-      <c r="G25" s="72">
+      <c r="G25" s="71">
         <f>C25*F25</f>
         <v>495000</v>
       </c>
@@ -5045,34 +5042,34 @@
       <c r="I25" s="27"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A26" s="79"/>
-      <c r="B26" s="93"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="72"/>
+      <c r="A26" s="78"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="71"/>
       <c r="H26" s="68"/>
       <c r="I26" s="27"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="90" t="s">
+      <c r="B27" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="86">
-        <v>1</v>
-      </c>
-      <c r="D27" s="86" t="s">
+      <c r="C27" s="85">
+        <v>1</v>
+      </c>
+      <c r="D27" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="86"/>
-      <c r="F27" s="89">
+      <c r="E27" s="85"/>
+      <c r="F27" s="88">
         <v>550000</v>
       </c>
-      <c r="G27" s="83">
+      <c r="G27" s="82">
         <f>C27*F27</f>
         <v>550000</v>
       </c>
@@ -5080,17 +5077,17 @@
       <c r="I27" s="27"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A28" s="88" t="s">
+      <c r="A28" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="87" t="s">
+      <c r="B28" s="86" t="s">
         <v>130</v>
       </c>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="83">
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="82">
         <f>SUM(G29:G34)</f>
         <v>520025</v>
       </c>
@@ -5098,150 +5095,150 @@
       <c r="I28" s="27"/>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A29" s="76">
-        <v>1</v>
-      </c>
-      <c r="B29" s="82" t="s">
+      <c r="A29" s="75">
+        <v>1</v>
+      </c>
+      <c r="B29" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="C29" s="81" t="s">
+      <c r="C29" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="D29" s="80" t="s">
+      <c r="D29" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="E29" s="80" t="s">
+      <c r="E29" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="F29" s="72">
+      <c r="F29" s="71">
         <v>76450</v>
       </c>
-      <c r="G29" s="72">
+      <c r="G29" s="71">
         <v>48125.000000000007</v>
       </c>
       <c r="H29" s="68"/>
       <c r="I29" s="27"/>
     </row>
     <row r="30" spans="1:9" ht="37.5" customHeight="1">
-      <c r="A30" s="76">
+      <c r="A30" s="75">
         <v>2</v>
       </c>
-      <c r="B30" s="77" t="s">
+      <c r="B30" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="D30" s="76" t="s">
+      <c r="D30" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="76" t="s">
+      <c r="E30" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="72">
+      <c r="F30" s="71">
         <v>1870000.0000000002</v>
       </c>
-      <c r="G30" s="72">
+      <c r="G30" s="71">
         <v>149600</v>
       </c>
       <c r="H30" s="68"/>
       <c r="I30" s="27"/>
     </row>
     <row r="31" spans="1:9" ht="41.5" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="75">
         <v>3</v>
       </c>
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="D31" s="76" t="s">
+      <c r="D31" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="E31" s="76" t="s">
+      <c r="E31" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F31" s="72">
+      <c r="F31" s="71">
         <v>321310</v>
       </c>
-      <c r="G31" s="72">
+      <c r="G31" s="71">
         <v>122100.00000000001</v>
       </c>
       <c r="H31" s="68"/>
       <c r="I31" s="27"/>
     </row>
     <row r="32" spans="1:9" ht="40.5" customHeight="1">
-      <c r="A32" s="76">
+      <c r="A32" s="75">
         <v>4</v>
       </c>
-      <c r="B32" s="77" t="s">
+      <c r="B32" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="C32" s="79" t="s">
+      <c r="C32" s="78" t="s">
         <v>139</v>
       </c>
-      <c r="D32" s="78" t="s">
+      <c r="D32" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="78" t="s">
+      <c r="E32" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="F32" s="72">
+      <c r="F32" s="71">
         <v>25740.000000000004</v>
       </c>
-      <c r="G32" s="72">
+      <c r="G32" s="71">
         <v>40700</v>
       </c>
       <c r="H32" s="68"/>
       <c r="I32" s="27"/>
     </row>
     <row r="33" spans="1:9" ht="21" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="75">
         <v>5</v>
       </c>
-      <c r="B33" s="77" t="s">
+      <c r="B33" s="76" t="s">
         <v>140</v>
       </c>
-      <c r="C33" s="76">
-        <v>1</v>
-      </c>
-      <c r="D33" s="76" t="s">
+      <c r="C33" s="75">
+        <v>1</v>
+      </c>
+      <c r="D33" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="76" t="s">
+      <c r="E33" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F33" s="72">
+      <c r="F33" s="71">
         <v>69300</v>
       </c>
-      <c r="G33" s="72">
+      <c r="G33" s="71">
         <v>69300</v>
       </c>
       <c r="H33" s="68"/>
       <c r="I33" s="27"/>
     </row>
     <row r="34" spans="1:9" ht="35.5" customHeight="1">
-      <c r="A34" s="75">
+      <c r="A34" s="74">
         <v>6</v>
       </c>
-      <c r="B34" s="74" t="s">
+      <c r="B34" s="73" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="73">
-        <v>1</v>
-      </c>
-      <c r="D34" s="73" t="s">
+      <c r="C34" s="72">
+        <v>1</v>
+      </c>
+      <c r="D34" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="73" t="s">
+      <c r="E34" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="F34" s="72">
+      <c r="F34" s="71">
         <v>90200.000000000015</v>
       </c>
-      <c r="G34" s="72">
+      <c r="G34" s="71">
         <v>90200.000000000015</v>
       </c>
       <c r="H34" s="68"/>
@@ -5251,11 +5248,11 @@
       <c r="A35" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="158"/>
-      <c r="C35" s="159"/>
-      <c r="D35" s="159"/>
-      <c r="E35" s="159"/>
-      <c r="F35" s="160"/>
+      <c r="B35" s="148"/>
+      <c r="C35" s="149"/>
+      <c r="D35" s="149"/>
+      <c r="E35" s="149"/>
+      <c r="F35" s="150"/>
       <c r="G35" s="69">
         <f>SUM(G8,G13,G17,G20,G27,G28)</f>
         <v>12427525</v>
@@ -5344,672 +5341,672 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="14.5">
-      <c r="A1" s="140"/>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
+      <c r="A1" s="139"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
     </row>
     <row r="2" spans="1:13" ht="18.5">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="151" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="162"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1">
-      <c r="A3" s="109" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
+      <c r="A3" s="108" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="162"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
+      <c r="B4" s="152"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
     </row>
     <row r="5" spans="1:13" ht="14.5">
-      <c r="A5" s="111"/>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
+      <c r="A5" s="110"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
     </row>
     <row r="6" spans="1:13" ht="16.5" thickBot="1">
-      <c r="A6" s="110"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="169" t="s">
+      <c r="A6" s="109"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="168" t="s">
         <v>143</v>
       </c>
-      <c r="F6" s="162"/>
-      <c r="G6" s="170"/>
+      <c r="F6" s="152"/>
+      <c r="G6" s="169"/>
     </row>
     <row r="7" spans="1:13" ht="14.5">
-      <c r="A7" s="139" t="s">
+      <c r="A7" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="138" t="s">
+      <c r="B7" s="137" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="171" t="s">
+      <c r="C7" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="172"/>
-      <c r="E7" s="137" t="s">
+      <c r="D7" s="171"/>
+      <c r="E7" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="136" t="s">
+      <c r="F7" s="135" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="135" t="s">
+      <c r="G7" s="134" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="14.5">
-      <c r="A8" s="133" t="s">
+      <c r="A8" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="134" t="s">
+      <c r="B8" s="133" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="133">
-        <v>1</v>
-      </c>
-      <c r="D8" s="133" t="s">
+      <c r="C8" s="132">
+        <v>1</v>
+      </c>
+      <c r="D8" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="133"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132">
+      <c r="E8" s="132"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="131">
         <f>SUM(G9:G12)</f>
         <v>3630000</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="14.5">
-      <c r="A9" s="80">
-        <v>1</v>
-      </c>
-      <c r="B9" s="81" t="s">
+      <c r="A9" s="79">
+        <v>1</v>
+      </c>
+      <c r="B9" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="80">
+      <c r="C9" s="79">
         <v>11000</v>
       </c>
-      <c r="D9" s="80" t="s">
+      <c r="D9" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="80"/>
-      <c r="F9" s="95">
+      <c r="E9" s="79"/>
+      <c r="F9" s="94">
         <v>80.300000000000011</v>
       </c>
-      <c r="G9" s="95">
+      <c r="G9" s="94">
         <f>C9*F9</f>
         <v>883300.00000000012</v>
       </c>
       <c r="H9" s="68"/>
     </row>
     <row r="10" spans="1:13" ht="14.5">
-      <c r="A10" s="80">
+      <c r="A10" s="79">
         <v>2</v>
       </c>
-      <c r="B10" s="81" t="s">
+      <c r="B10" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="80">
+      <c r="C10" s="79">
         <v>11000</v>
       </c>
-      <c r="D10" s="80" t="s">
+      <c r="D10" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="80"/>
-      <c r="F10" s="95">
+      <c r="E10" s="79"/>
+      <c r="F10" s="94">
         <v>80.300000000000011</v>
       </c>
-      <c r="G10" s="95">
+      <c r="G10" s="94">
         <f>C10*F10</f>
         <v>883300.00000000012</v>
       </c>
       <c r="H10" s="68"/>
     </row>
     <row r="11" spans="1:13" ht="14.5">
-      <c r="A11" s="80">
+      <c r="A11" s="79">
         <v>3</v>
       </c>
-      <c r="B11" s="81" t="s">
+      <c r="B11" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="80">
-        <v>1</v>
-      </c>
-      <c r="D11" s="80" t="s">
+      <c r="C11" s="79">
+        <v>1</v>
+      </c>
+      <c r="D11" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="95">
+      <c r="E11" s="79"/>
+      <c r="F11" s="94">
         <v>2530000</v>
       </c>
-      <c r="G11" s="95">
+      <c r="G11" s="94">
         <f>C11*F11</f>
         <v>2530000</v>
       </c>
       <c r="H11" s="68"/>
     </row>
     <row r="12" spans="1:13" ht="14.5">
-      <c r="A12" s="80"/>
-      <c r="B12" s="105" t="s">
+      <c r="A12" s="79"/>
+      <c r="B12" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="104">
-        <v>1</v>
-      </c>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="103">
+      <c r="C12" s="103">
+        <v>1</v>
+      </c>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="102">
         <v>-666600</v>
       </c>
-      <c r="G12" s="103">
+      <c r="G12" s="102">
         <f>F12*C12</f>
         <v>-666600</v>
       </c>
       <c r="H12" s="68"/>
     </row>
     <row r="13" spans="1:13" ht="14.5">
-      <c r="A13" s="127" t="s">
+      <c r="A13" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="130" t="s">
+      <c r="B13" s="129" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="125">
-        <v>1</v>
-      </c>
-      <c r="D13" s="125" t="s">
+      <c r="C13" s="124">
+        <v>1</v>
+      </c>
+      <c r="D13" s="124" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="125"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="123">
+      <c r="E13" s="124"/>
+      <c r="F13" s="123"/>
+      <c r="G13" s="122">
         <f>SUM(G14:G15)</f>
         <v>1265000</v>
       </c>
       <c r="H13" s="68"/>
     </row>
     <row r="14" spans="1:13" ht="14.5">
-      <c r="A14" s="80">
-        <v>1</v>
-      </c>
-      <c r="B14" s="82" t="s">
+      <c r="A14" s="79">
+        <v>1</v>
+      </c>
+      <c r="B14" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="80">
-        <v>1</v>
-      </c>
-      <c r="D14" s="80" t="s">
+      <c r="C14" s="79">
+        <v>1</v>
+      </c>
+      <c r="D14" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="80" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="95">
+      <c r="E14" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="94">
         <v>275000</v>
       </c>
-      <c r="G14" s="95">
+      <c r="G14" s="94">
         <f>C14*F14</f>
         <v>275000</v>
       </c>
       <c r="H14" s="68"/>
-      <c r="M14" s="131"/>
+      <c r="M14" s="130"/>
     </row>
     <row r="15" spans="1:13" ht="14.5">
-      <c r="A15" s="80">
+      <c r="A15" s="79">
         <v>2</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="80">
-        <v>1</v>
-      </c>
-      <c r="D15" s="80" t="s">
+      <c r="C15" s="79">
+        <v>1</v>
+      </c>
+      <c r="D15" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="80" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="95">
+      <c r="E15" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="94">
         <v>990000.00000000012</v>
       </c>
-      <c r="G15" s="95">
+      <c r="G15" s="94">
         <f>C15*F15</f>
         <v>990000.00000000012</v>
       </c>
       <c r="H15" s="68"/>
-      <c r="M15" s="131"/>
+      <c r="M15" s="130"/>
     </row>
     <row r="16" spans="1:13" ht="14.5">
-      <c r="A16" s="80"/>
-      <c r="B16" s="81"/>
-      <c r="C16" s="80" t="s">
+      <c r="A16" s="79"/>
+      <c r="B16" s="80"/>
+      <c r="C16" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="94"/>
       <c r="H16" s="68"/>
-      <c r="M16" s="131"/>
+      <c r="M16" s="130"/>
     </row>
     <row r="17" spans="1:8" ht="14.5">
-      <c r="A17" s="127" t="s">
+      <c r="A17" s="126" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="130" t="s">
+      <c r="B17" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="125" t="s">
+      <c r="C17" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="125"/>
-      <c r="E17" s="125"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="123">
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="123"/>
+      <c r="G17" s="122">
         <f>SUM(G18)</f>
         <v>1870000.0000000002</v>
       </c>
       <c r="H17" s="68"/>
     </row>
     <row r="18" spans="1:8" ht="14.5">
-      <c r="A18" s="80">
-        <v>1</v>
-      </c>
-      <c r="B18" s="81" t="s">
+      <c r="A18" s="79">
+        <v>1</v>
+      </c>
+      <c r="B18" s="80" t="s">
         <v>145</v>
       </c>
-      <c r="C18" s="80">
-        <v>1</v>
-      </c>
-      <c r="D18" s="80" t="s">
+      <c r="C18" s="79">
+        <v>1</v>
+      </c>
+      <c r="D18" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="80" t="s">
+      <c r="E18" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="94">
         <v>1870000.0000000002</v>
       </c>
-      <c r="G18" s="95">
+      <c r="G18" s="94">
         <f>C18*F18</f>
         <v>1870000.0000000002</v>
       </c>
       <c r="H18" s="68"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="129"/>
-      <c r="B19" s="128"/>
-      <c r="C19" s="80" t="s">
+      <c r="A19" s="128"/>
+      <c r="B19" s="127"/>
+      <c r="C19" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
       <c r="H19" s="68"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A20" s="127" t="s">
+      <c r="A20" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="126" t="s">
+      <c r="B20" s="125" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="125" t="s">
+      <c r="C20" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="124"/>
-      <c r="G20" s="123">
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="122">
         <f>SUM(G21:G25)</f>
         <v>5362500</v>
       </c>
       <c r="H20" s="68"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" s="80">
-        <v>1</v>
-      </c>
-      <c r="B21" s="81" t="s">
+      <c r="A21" s="79">
+        <v>1</v>
+      </c>
+      <c r="B21" s="80" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="80">
+      <c r="C21" s="79">
         <v>15</v>
       </c>
-      <c r="D21" s="80" t="s">
+      <c r="D21" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="122" t="s">
+      <c r="E21" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="94">
         <v>192500.00000000003</v>
       </c>
-      <c r="G21" s="95">
+      <c r="G21" s="94">
         <f>C21*F21</f>
         <v>2887500.0000000005</v>
       </c>
       <c r="H21" s="68"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="80">
+      <c r="A22" s="79">
         <v>2</v>
       </c>
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="80">
+      <c r="C22" s="79">
         <v>5</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E22" s="122" t="s">
+      <c r="E22" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="94">
         <v>60500.000000000007</v>
       </c>
-      <c r="G22" s="95">
+      <c r="G22" s="94">
         <f>C22*F22</f>
         <v>302500.00000000006</v>
       </c>
       <c r="H22" s="68"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="80">
+      <c r="A23" s="79">
         <v>3</v>
       </c>
-      <c r="B23" s="79" t="s">
+      <c r="B23" s="78" t="s">
         <v>148</v>
       </c>
-      <c r="C23" s="76">
+      <c r="C23" s="75">
         <v>15</v>
       </c>
-      <c r="D23" s="76" t="s">
+      <c r="D23" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="94" t="s">
+      <c r="E23" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="F23" s="72">
+      <c r="F23" s="71">
         <v>38500</v>
       </c>
-      <c r="G23" s="95">
+      <c r="G23" s="94">
         <f>C23*F23</f>
         <v>577500</v>
       </c>
       <c r="H23" s="68"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A24" s="80">
+      <c r="A24" s="79">
         <v>4</v>
       </c>
-      <c r="B24" s="81" t="s">
+      <c r="B24" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="76">
-        <v>1</v>
-      </c>
-      <c r="D24" s="76" t="s">
+      <c r="C24" s="75">
+        <v>1</v>
+      </c>
+      <c r="D24" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="76"/>
-      <c r="F24" s="72">
+      <c r="E24" s="75"/>
+      <c r="F24" s="71">
         <v>1100000</v>
       </c>
-      <c r="G24" s="95">
+      <c r="G24" s="94">
         <f>C24*F24</f>
         <v>1100000</v>
       </c>
       <c r="H24" s="68"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" s="80">
+      <c r="A25" s="79">
         <v>5</v>
       </c>
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="80" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="80">
+      <c r="C25" s="79">
         <v>15</v>
       </c>
-      <c r="D25" s="80" t="s">
+      <c r="D25" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="80" t="s">
+      <c r="E25" s="79" t="s">
         <v>129</v>
       </c>
-      <c r="F25" s="95">
+      <c r="F25" s="94">
         <v>33000</v>
       </c>
-      <c r="G25" s="95">
+      <c r="G25" s="94">
         <f>C25*F25</f>
         <v>495000</v>
       </c>
       <c r="H25" s="68"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A26" s="110"/>
-      <c r="B26" s="121"/>
-      <c r="C26" s="120" t="s">
+      <c r="A26" s="109"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="119" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="120"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="118"/>
       <c r="H26" s="68"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="118" t="s">
+      <c r="A27" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="117" t="s">
+      <c r="B27" s="116" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="116">
-        <v>1</v>
-      </c>
-      <c r="D27" s="116" t="s">
+      <c r="C27" s="115">
+        <v>1</v>
+      </c>
+      <c r="D27" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="116"/>
-      <c r="F27" s="115">
+      <c r="E27" s="115"/>
+      <c r="F27" s="114">
         <v>550000</v>
       </c>
-      <c r="G27" s="114">
+      <c r="G27" s="113">
         <f>C27*F27</f>
         <v>550000</v>
       </c>
       <c r="H27" s="68"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A28" s="88" t="s">
+      <c r="A28" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="87" t="s">
+      <c r="B28" s="86" t="s">
         <v>130</v>
       </c>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="83">
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="82">
         <f>SUM(G29:G34)</f>
         <v>520025</v>
       </c>
       <c r="H28" s="68"/>
     </row>
     <row r="29" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A29" s="76">
-        <v>1</v>
-      </c>
-      <c r="B29" s="82" t="s">
+      <c r="A29" s="75">
+        <v>1</v>
+      </c>
+      <c r="B29" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="C29" s="81" t="s">
+      <c r="C29" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="D29" s="81" t="s">
+      <c r="D29" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="E29" s="80" t="s">
+      <c r="E29" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="F29" s="72">
+      <c r="F29" s="71">
         <v>76450</v>
       </c>
-      <c r="G29" s="72">
+      <c r="G29" s="71">
         <v>48125.000000000007</v>
       </c>
       <c r="H29" s="68"/>
     </row>
     <row r="30" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A30" s="76">
+      <c r="A30" s="75">
         <v>2</v>
       </c>
-      <c r="B30" s="77" t="s">
+      <c r="B30" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="D30" s="79" t="s">
+      <c r="D30" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="76" t="s">
+      <c r="E30" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="72">
+      <c r="F30" s="71">
         <v>1870000.0000000002</v>
       </c>
-      <c r="G30" s="72">
+      <c r="G30" s="71">
         <v>149600</v>
       </c>
       <c r="H30" s="68"/>
     </row>
     <row r="31" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="75">
         <v>3</v>
       </c>
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="D31" s="79" t="s">
+      <c r="D31" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="E31" s="76" t="s">
+      <c r="E31" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F31" s="72">
+      <c r="F31" s="71">
         <v>321310</v>
       </c>
-      <c r="G31" s="72">
+      <c r="G31" s="71">
         <v>122100.00000000001</v>
       </c>
       <c r="H31" s="68"/>
     </row>
     <row r="32" spans="1:8" ht="26.5" customHeight="1">
-      <c r="A32" s="76">
+      <c r="A32" s="75">
         <v>4</v>
       </c>
-      <c r="B32" s="77" t="s">
+      <c r="B32" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="C32" s="79" t="s">
+      <c r="C32" s="78" t="s">
         <v>139</v>
       </c>
-      <c r="D32" s="113" t="s">
+      <c r="D32" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="78" t="s">
+      <c r="E32" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="F32" s="72">
+      <c r="F32" s="71">
         <v>25740.000000000004</v>
       </c>
-      <c r="G32" s="72">
+      <c r="G32" s="71">
         <v>40700</v>
       </c>
       <c r="H32" s="68"/>
     </row>
     <row r="33" spans="1:8" ht="32.5" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="75">
         <v>5</v>
       </c>
-      <c r="B33" s="77" t="s">
+      <c r="B33" s="76" t="s">
         <v>140</v>
       </c>
-      <c r="C33" s="76">
-        <v>1</v>
-      </c>
-      <c r="D33" s="79" t="s">
+      <c r="C33" s="75">
+        <v>1</v>
+      </c>
+      <c r="D33" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="76" t="s">
+      <c r="E33" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F33" s="72">
+      <c r="F33" s="71">
         <v>69300</v>
       </c>
-      <c r="G33" s="72">
+      <c r="G33" s="71">
         <v>69300</v>
       </c>
       <c r="H33" s="68"/>
     </row>
     <row r="34" spans="1:8" ht="36" customHeight="1">
-      <c r="A34" s="76">
+      <c r="A34" s="75">
         <v>6</v>
       </c>
-      <c r="B34" s="77" t="s">
+      <c r="B34" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="76">
-        <v>1</v>
-      </c>
-      <c r="D34" s="79" t="s">
+      <c r="C34" s="75">
+        <v>1</v>
+      </c>
+      <c r="D34" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="76" t="s">
+      <c r="E34" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F34" s="72">
+      <c r="F34" s="71">
         <v>90200.000000000015</v>
       </c>
-      <c r="G34" s="72">
+      <c r="G34" s="71">
         <v>90200.000000000015</v>
       </c>
       <c r="H34" s="68"/>
@@ -6018,11 +6015,11 @@
       <c r="A35" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="158"/>
-      <c r="C35" s="159"/>
-      <c r="D35" s="159"/>
-      <c r="E35" s="159"/>
-      <c r="F35" s="160"/>
+      <c r="B35" s="148"/>
+      <c r="C35" s="149"/>
+      <c r="D35" s="149"/>
+      <c r="E35" s="149"/>
+      <c r="F35" s="150"/>
       <c r="G35" s="69">
         <f>SUM(G8,G13,G17,G20,G27,G28)</f>
         <v>13197525</v>
@@ -6106,658 +6103,658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.5">
-      <c r="A1" s="140"/>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
+      <c r="A1" s="139"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
     </row>
     <row r="2" spans="1:7" ht="18.5">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="162"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1">
-      <c r="A3" s="109" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
+      <c r="A3" s="108" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="162"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110">
+      <c r="B4" s="152"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109">
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.5">
-      <c r="A5" s="111"/>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
+      <c r="A5" s="110"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
     </row>
     <row r="6" spans="1:7" ht="16.5" thickBot="1">
-      <c r="A6" s="110"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="169" t="s">
+      <c r="A6" s="109"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="168" t="s">
         <v>150</v>
       </c>
-      <c r="F6" s="162"/>
-      <c r="G6" s="170"/>
+      <c r="F6" s="152"/>
+      <c r="G6" s="169"/>
     </row>
     <row r="7" spans="1:7" ht="14.5">
-      <c r="A7" s="139" t="s">
+      <c r="A7" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="138" t="s">
+      <c r="B7" s="137" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="171" t="s">
+      <c r="C7" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="172"/>
-      <c r="E7" s="137" t="s">
+      <c r="D7" s="171"/>
+      <c r="E7" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="136" t="s">
+      <c r="F7" s="135" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="135" t="s">
+      <c r="G7" s="134" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.5">
-      <c r="A8" s="133" t="s">
+      <c r="A8" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="134" t="s">
+      <c r="B8" s="133" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="133">
-        <v>1</v>
-      </c>
-      <c r="D8" s="133" t="s">
+      <c r="C8" s="132">
+        <v>1</v>
+      </c>
+      <c r="D8" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="133"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132">
+      <c r="E8" s="132"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="131">
         <f>SUM(G9:G12)</f>
         <v>4400000</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.5">
-      <c r="A9" s="80">
-        <v>1</v>
-      </c>
-      <c r="B9" s="81" t="s">
+      <c r="A9" s="79">
+        <v>1</v>
+      </c>
+      <c r="B9" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="80">
+      <c r="C9" s="79">
         <v>13200</v>
       </c>
-      <c r="D9" s="80" t="s">
+      <c r="D9" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="80"/>
-      <c r="F9" s="95">
+      <c r="E9" s="79"/>
+      <c r="F9" s="94">
         <v>80.300000000000011</v>
       </c>
-      <c r="G9" s="95">
+      <c r="G9" s="94">
         <f>F9*C9</f>
         <v>1059960.0000000002</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.5">
-      <c r="A10" s="80">
+      <c r="A10" s="79">
         <v>2</v>
       </c>
-      <c r="B10" s="81" t="s">
+      <c r="B10" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="80">
+      <c r="C10" s="79">
         <v>13200</v>
       </c>
-      <c r="D10" s="80" t="s">
+      <c r="D10" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="80"/>
-      <c r="F10" s="95">
+      <c r="E10" s="79"/>
+      <c r="F10" s="94">
         <v>80.300000000000011</v>
       </c>
-      <c r="G10" s="95">
+      <c r="G10" s="94">
         <f>F10*C10</f>
         <v>1059960.0000000002</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.5">
-      <c r="A11" s="80">
+      <c r="A11" s="79">
         <v>3</v>
       </c>
-      <c r="B11" s="81" t="s">
+      <c r="B11" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="80">
-        <v>1</v>
-      </c>
-      <c r="D11" s="80" t="s">
+      <c r="C11" s="79">
+        <v>1</v>
+      </c>
+      <c r="D11" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="95">
+      <c r="E11" s="79"/>
+      <c r="F11" s="94">
         <v>2750000</v>
       </c>
-      <c r="G11" s="95">
+      <c r="G11" s="94">
         <f>F11*C11</f>
         <v>2750000</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.5">
-      <c r="A12" s="80"/>
-      <c r="B12" s="105" t="s">
+      <c r="A12" s="79"/>
+      <c r="B12" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="104">
-        <v>1</v>
-      </c>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="103">
+      <c r="C12" s="103">
+        <v>1</v>
+      </c>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="102">
         <v>-469920.00000000006</v>
       </c>
-      <c r="G12" s="103">
+      <c r="G12" s="102">
         <f>F12*C12</f>
         <v>-469920.00000000006</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.5">
-      <c r="A13" s="127" t="s">
+      <c r="A13" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="130" t="s">
+      <c r="B13" s="129" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="125">
-        <v>1</v>
-      </c>
-      <c r="D13" s="125" t="s">
+      <c r="C13" s="124">
+        <v>1</v>
+      </c>
+      <c r="D13" s="124" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="125"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="123">
+      <c r="E13" s="124"/>
+      <c r="F13" s="123"/>
+      <c r="G13" s="122">
         <f>SUM(G14:G15)</f>
         <v>1265000</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.5">
-      <c r="A14" s="80">
-        <v>1</v>
-      </c>
-      <c r="B14" s="82" t="s">
+      <c r="A14" s="79">
+        <v>1</v>
+      </c>
+      <c r="B14" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="80">
-        <v>1</v>
-      </c>
-      <c r="D14" s="80" t="s">
+      <c r="C14" s="79">
+        <v>1</v>
+      </c>
+      <c r="D14" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="80" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="95">
+      <c r="E14" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="94">
         <v>275000</v>
       </c>
-      <c r="G14" s="95">
+      <c r="G14" s="94">
         <f>F14*C14</f>
         <v>275000</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.5">
-      <c r="A15" s="80">
+      <c r="A15" s="79">
         <v>2</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="80">
-        <v>1</v>
-      </c>
-      <c r="D15" s="80" t="s">
+      <c r="C15" s="79">
+        <v>1</v>
+      </c>
+      <c r="D15" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="80" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="95">
+      <c r="E15" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="94">
         <v>990000.00000000012</v>
       </c>
-      <c r="G15" s="95">
+      <c r="G15" s="94">
         <f>F15*C15</f>
         <v>990000.00000000012</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.5">
-      <c r="A16" s="80"/>
-      <c r="B16" s="81"/>
-      <c r="C16" s="80" t="s">
+      <c r="A16" s="79"/>
+      <c r="B16" s="80"/>
+      <c r="C16" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="94"/>
     </row>
     <row r="17" spans="1:8" ht="14.5">
-      <c r="A17" s="127" t="s">
+      <c r="A17" s="126" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="130" t="s">
+      <c r="B17" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="125" t="s">
+      <c r="C17" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="125"/>
-      <c r="E17" s="125"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="123">
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="123"/>
+      <c r="G17" s="122">
         <f>SUM(G18)</f>
         <v>2200000</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="14.5">
-      <c r="A18" s="80">
-        <v>1</v>
-      </c>
-      <c r="B18" s="81" t="s">
+      <c r="A18" s="79">
+        <v>1</v>
+      </c>
+      <c r="B18" s="80" t="s">
         <v>151</v>
       </c>
-      <c r="C18" s="80">
-        <v>1</v>
-      </c>
-      <c r="D18" s="80" t="s">
+      <c r="C18" s="79">
+        <v>1</v>
+      </c>
+      <c r="D18" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="80" t="s">
+      <c r="E18" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="94">
         <v>2200000</v>
       </c>
-      <c r="G18" s="95">
+      <c r="G18" s="94">
         <f>F18*C18</f>
         <v>2200000</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="129"/>
-      <c r="B19" s="128"/>
-      <c r="C19" s="80" t="s">
+      <c r="A19" s="128"/>
+      <c r="B19" s="127"/>
+      <c r="C19" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A20" s="127" t="s">
+      <c r="A20" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="126" t="s">
+      <c r="B20" s="125" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="125" t="s">
+      <c r="C20" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="124"/>
-      <c r="G20" s="123">
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="122">
         <f>SUM(G21:G25)</f>
         <v>4705250</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="14.5">
-      <c r="A21" s="80">
-        <v>1</v>
-      </c>
-      <c r="B21" s="81" t="s">
+      <c r="A21" s="79">
+        <v>1</v>
+      </c>
+      <c r="B21" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="C21" s="80">
+      <c r="C21" s="79">
         <v>15</v>
       </c>
-      <c r="D21" s="80" t="s">
+      <c r="D21" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="122" t="s">
+      <c r="E21" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="94">
         <v>143000</v>
       </c>
-      <c r="G21" s="95">
+      <c r="G21" s="94">
         <f>F21*C21</f>
         <v>2145000</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="23.5" customHeight="1">
-      <c r="A22" s="80">
+      <c r="A22" s="79">
         <v>2</v>
       </c>
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="80">
+      <c r="C22" s="79">
         <v>5</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E22" s="122" t="s">
+      <c r="E22" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="94">
         <v>67650</v>
       </c>
-      <c r="G22" s="95">
+      <c r="G22" s="94">
         <f>F22*C22</f>
         <v>338250</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="34.5" customHeight="1">
-      <c r="A23" s="80">
+      <c r="A23" s="79">
         <v>3</v>
       </c>
-      <c r="B23" s="79" t="s">
+      <c r="B23" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="80">
+      <c r="C23" s="79">
         <v>15</v>
       </c>
-      <c r="D23" s="80" t="s">
+      <c r="D23" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="122" t="s">
+      <c r="E23" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="F23" s="72">
+      <c r="F23" s="71">
         <v>41800</v>
       </c>
-      <c r="G23" s="95">
+      <c r="G23" s="94">
         <f>F23*C23</f>
         <v>627000</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A24" s="80">
+      <c r="A24" s="79">
         <v>4</v>
       </c>
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="76">
-        <v>1</v>
-      </c>
-      <c r="D24" s="76" t="s">
+      <c r="C24" s="75">
+        <v>1</v>
+      </c>
+      <c r="D24" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="76"/>
-      <c r="F24" s="72">
+      <c r="E24" s="75"/>
+      <c r="F24" s="71">
         <v>1100000</v>
       </c>
-      <c r="G24" s="95">
+      <c r="G24" s="94">
         <f>F24*C24</f>
         <v>1100000</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" s="80">
+      <c r="A25" s="79">
         <v>5</v>
       </c>
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="80" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="80">
+      <c r="C25" s="79">
         <v>15</v>
       </c>
-      <c r="D25" s="80" t="s">
+      <c r="D25" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="80" t="s">
+      <c r="E25" s="79" t="s">
         <v>129</v>
       </c>
-      <c r="F25" s="95">
+      <c r="F25" s="94">
         <v>33000</v>
       </c>
-      <c r="G25" s="95">
+      <c r="G25" s="94">
         <f>F25*C25</f>
         <v>495000</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A26" s="110"/>
-      <c r="B26" s="121"/>
-      <c r="C26" s="120" t="s">
+      <c r="A26" s="109"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="119" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="120"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="118"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="148" t="s">
+      <c r="A27" s="147" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="147" t="s">
+      <c r="B27" s="146" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="146">
-        <v>1</v>
-      </c>
-      <c r="D27" s="146" t="s">
+      <c r="C27" s="145">
+        <v>1</v>
+      </c>
+      <c r="D27" s="145" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="146"/>
-      <c r="F27" s="145">
+      <c r="E27" s="145"/>
+      <c r="F27" s="144">
         <v>550000</v>
       </c>
-      <c r="G27" s="144">
+      <c r="G27" s="143">
         <f>F27*C27</f>
         <v>550000</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A28" s="143"/>
-      <c r="B28" s="142"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
+      <c r="A28" s="142"/>
+      <c r="B28" s="141"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A29" s="88" t="s">
+      <c r="A29" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="87" t="s">
+      <c r="B29" s="86" t="s">
         <v>130</v>
       </c>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="84"/>
-      <c r="G29" s="83">
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="82">
         <f>SUM(G30:G35)</f>
         <v>520025</v>
       </c>
-      <c r="H29" s="110"/>
+      <c r="H29" s="109"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A30" s="76">
-        <v>1</v>
-      </c>
-      <c r="B30" s="82" t="s">
+      <c r="A30" s="75">
+        <v>1</v>
+      </c>
+      <c r="B30" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="80" t="s">
+      <c r="C30" s="79" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="80" t="s">
+      <c r="D30" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="E30" s="80" t="s">
+      <c r="E30" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="72">
+      <c r="F30" s="71">
         <v>76450</v>
       </c>
-      <c r="G30" s="72">
+      <c r="G30" s="71">
         <v>48125.000000000007</v>
       </c>
-      <c r="H30" s="110"/>
+      <c r="H30" s="109"/>
     </row>
     <row r="31" spans="1:8" ht="33.75" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="75">
         <v>2</v>
       </c>
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="C31" s="76" t="s">
+      <c r="C31" s="75" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="76" t="s">
+      <c r="D31" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="76" t="s">
+      <c r="E31" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F31" s="72">
+      <c r="F31" s="71">
         <v>1870000.0000000002</v>
       </c>
-      <c r="G31" s="72">
+      <c r="G31" s="71">
         <v>149600</v>
       </c>
-      <c r="H31" s="110"/>
+      <c r="H31" s="109"/>
     </row>
     <row r="32" spans="1:8" ht="46.75" customHeight="1">
-      <c r="A32" s="76">
+      <c r="A32" s="75">
         <v>3</v>
       </c>
-      <c r="B32" s="77" t="s">
+      <c r="B32" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="C32" s="76" t="s">
+      <c r="C32" s="75" t="s">
         <v>137</v>
       </c>
-      <c r="D32" s="76" t="s">
+      <c r="D32" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="76" t="s">
+      <c r="E32" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F32" s="72">
+      <c r="F32" s="71">
         <v>321310</v>
       </c>
-      <c r="G32" s="72">
+      <c r="G32" s="71">
         <v>122100.00000000001</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="43.75" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="75">
         <v>4</v>
       </c>
-      <c r="B33" s="77" t="s">
+      <c r="B33" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="C33" s="76" t="s">
+      <c r="C33" s="75" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="78" t="s">
+      <c r="D33" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="78" t="s">
+      <c r="E33" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="F33" s="72">
+      <c r="F33" s="71">
         <v>25740.000000000004</v>
       </c>
-      <c r="G33" s="72">
+      <c r="G33" s="71">
         <v>40700</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A34" s="76">
+      <c r="A34" s="75">
         <v>5</v>
       </c>
-      <c r="B34" s="77" t="s">
+      <c r="B34" s="76" t="s">
         <v>140</v>
       </c>
-      <c r="C34" s="76">
-        <v>1</v>
-      </c>
-      <c r="D34" s="76" t="s">
+      <c r="C34" s="75">
+        <v>1</v>
+      </c>
+      <c r="D34" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="76" t="s">
+      <c r="E34" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F34" s="72">
+      <c r="F34" s="71">
         <v>69300</v>
       </c>
-      <c r="G34" s="72">
+      <c r="G34" s="71">
         <v>69300</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
-      <c r="A35" s="76">
+      <c r="A35" s="75">
         <v>6</v>
       </c>
-      <c r="B35" s="77" t="s">
+      <c r="B35" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="C35" s="76">
-        <v>1</v>
-      </c>
-      <c r="D35" s="76" t="s">
+      <c r="C35" s="75">
+        <v>1</v>
+      </c>
+      <c r="D35" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="76" t="s">
+      <c r="E35" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F35" s="72">
+      <c r="F35" s="71">
         <v>90200.000000000015</v>
       </c>
-      <c r="G35" s="72">
+      <c r="G35" s="71">
         <v>90200.000000000015</v>
       </c>
     </row>
@@ -6765,11 +6762,11 @@
       <c r="A36" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="158"/>
-      <c r="C36" s="159"/>
-      <c r="D36" s="159"/>
-      <c r="E36" s="159"/>
-      <c r="F36" s="160"/>
+      <c r="B36" s="148"/>
+      <c r="C36" s="149"/>
+      <c r="D36" s="149"/>
+      <c r="E36" s="149"/>
+      <c r="F36" s="150"/>
       <c r="G36" s="69">
         <f>SUM(G8,G13,G17,G20,G27,G29)</f>
         <v>13640275</v>
@@ -6861,10 +6858,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="152"/>
+      <c r="B1" s="162"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:10">
@@ -6875,13 +6872,13 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="13.15" customHeight="1">
-      <c r="A3" s="153" t="s">
+      <c r="A3" s="163" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="153"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="153"/>
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:10" ht="13.15" customHeight="1">
@@ -6891,10 +6888,10 @@
     <row r="5" spans="1:10" ht="25.5" customHeight="1">
       <c r="B5" s="29"/>
       <c r="C5" s="4"/>
-      <c r="G5" s="156" t="s">
+      <c r="G5" s="165" t="s">
         <v>153</v>
       </c>
-      <c r="H5" s="155"/>
+      <c r="H5" s="166"/>
     </row>
     <row r="6" spans="1:10" s="7" customFormat="1" ht="16.5" thickBot="1">
       <c r="A6" s="43" t="s">
@@ -6906,8 +6903,8 @@
       <c r="C6" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="154"/>
-      <c r="E6" s="154"/>
+      <c r="D6" s="164"/>
+      <c r="E6" s="164"/>
       <c r="F6" s="43" t="s">
         <v>7</v>
       </c>
@@ -6919,11 +6916,11 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="151"/>
-      <c r="E7" s="151"/>
+      <c r="A7" s="159"/>
+      <c r="B7" s="160"/>
+      <c r="C7" s="161"/>
+      <c r="D7" s="161"/>
+      <c r="E7" s="161"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:10" ht="32">
@@ -6965,7 +6962,7 @@
         <v>16</v>
       </c>
       <c r="G9" s="10">
-        <f>IF(B9='[2]Breakdown from VHM BOQ'!B9,'[2]Breakdown from VHM BOQ'!K9,"")*1.1</f>
+        <f>IF(B9='[1]Breakdown from VHM BOQ'!B9,'[1]Breakdown from VHM BOQ'!K9,"")*1.1</f>
         <v>94.600000000000009</v>
       </c>
       <c r="H9" s="11">
@@ -6991,7 +6988,7 @@
         <v>16</v>
       </c>
       <c r="G10" s="10">
-        <f>IF(B10='[2]Breakdown from VHM BOQ'!B10,'[2]Breakdown from VHM BOQ'!K10,"")*1.1</f>
+        <f>IF(B10='[1]Breakdown from VHM BOQ'!B10,'[1]Breakdown from VHM BOQ'!K10,"")*1.1</f>
         <v>94.600000000000009</v>
       </c>
       <c r="H10" s="11">
@@ -7017,7 +7014,7 @@
         <v>16</v>
       </c>
       <c r="G11" s="10">
-        <f>IF(B11='[2]Breakdown from VHM BOQ'!B11,'[2]Breakdown from VHM BOQ'!K11,"")*1.1</f>
+        <f>IF(B11='[1]Breakdown from VHM BOQ'!B11,'[1]Breakdown from VHM BOQ'!K11,"")*1.1</f>
         <v>3656400.0000000005</v>
       </c>
       <c r="H11" s="11">
@@ -7097,7 +7094,7 @@
         <v>16</v>
       </c>
       <c r="G15" s="10">
-        <f>IF(B15='[2]Breakdown from VHM BOQ'!B15,'[2]Breakdown from VHM BOQ'!K15,"")</f>
+        <f>IF(B15='[1]Breakdown from VHM BOQ'!B15,'[1]Breakdown from VHM BOQ'!K15,"")</f>
         <v>138710</v>
       </c>
       <c r="H15" s="11">
@@ -7128,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="G16" s="10">
-        <f>IF(B16='[2]Breakdown from VHM BOQ'!B18,'[2]Breakdown from VHM BOQ'!K18,"")</f>
+        <f>IF(B16='[1]Breakdown from VHM BOQ'!B18,'[1]Breakdown from VHM BOQ'!K18,"")</f>
         <v>132000</v>
       </c>
       <c r="H16" s="11">
@@ -7157,7 +7154,7 @@
         <v>16</v>
       </c>
       <c r="G17" s="10">
-        <f>IF(B17='[2]Breakdown from VHM BOQ'!B19,'[2]Breakdown from VHM BOQ'!K19,"")</f>
+        <f>IF(B17='[1]Breakdown from VHM BOQ'!B19,'[1]Breakdown from VHM BOQ'!K19,"")</f>
         <v>16005.000000000002</v>
       </c>
       <c r="H17" s="11">
@@ -7187,7 +7184,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="10">
-        <f>IF(B18='[2]Breakdown from VHM BOQ'!B20,'[2]Breakdown from VHM BOQ'!K20,"")</f>
+        <f>IF(B18='[1]Breakdown from VHM BOQ'!B20,'[1]Breakdown from VHM BOQ'!K20,"")</f>
         <v>1333750</v>
       </c>
       <c r="H18" s="11">
@@ -7217,7 +7214,7 @@
         <v>16</v>
       </c>
       <c r="G19" s="10">
-        <f>IF(B19='[2]Breakdown from VHM BOQ'!B21,'[2]Breakdown from VHM BOQ'!K21,"")</f>
+        <f>IF(B19='[1]Breakdown from VHM BOQ'!B21,'[1]Breakdown from VHM BOQ'!K21,"")</f>
         <v>1920600.0000000002</v>
       </c>
       <c r="H19" s="11">
@@ -7248,7 +7245,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="10">
-        <f>IF(B20='[2]Breakdown from VHM BOQ'!B22,'[2]Breakdown from VHM BOQ'!K22,"")</f>
+        <f>IF(B20='[1]Breakdown from VHM BOQ'!B22,'[1]Breakdown from VHM BOQ'!K22,"")</f>
         <v>323400</v>
       </c>
       <c r="H20" s="11">
@@ -7278,7 +7275,7 @@
         <v>16</v>
       </c>
       <c r="G21" s="10">
-        <f>IF(B21='[2]Breakdown from VHM BOQ'!B23,'[2]Breakdown from VHM BOQ'!K23,"")</f>
+        <f>IF(B21='[1]Breakdown from VHM BOQ'!B23,'[1]Breakdown from VHM BOQ'!K23,"")</f>
         <v>332904</v>
       </c>
       <c r="H21" s="11">
@@ -7308,7 +7305,7 @@
         <v>16</v>
       </c>
       <c r="G22" s="10">
-        <f>IF(B22='[2]Breakdown from VHM BOQ'!B24,'[2]Breakdown from VHM BOQ'!K24,"")</f>
+        <f>IF(B22='[1]Breakdown from VHM BOQ'!B24,'[1]Breakdown from VHM BOQ'!K24,"")</f>
         <v>37345</v>
       </c>
       <c r="H22" s="11">
@@ -7339,7 +7336,7 @@
         <v>16</v>
       </c>
       <c r="G23" s="10">
-        <f>IF(B23='[2]Breakdown from VHM BOQ'!B25,'[2]Breakdown from VHM BOQ'!K25,"")</f>
+        <f>IF(B23='[1]Breakdown from VHM BOQ'!B25,'[1]Breakdown from VHM BOQ'!K25,"")</f>
         <v>90695.000000000015</v>
       </c>
       <c r="H23" s="11">
@@ -7370,7 +7367,7 @@
         <v>16</v>
       </c>
       <c r="G24" s="10">
-        <f>IF(B24='[2]Breakdown from VHM BOQ'!B26,'[2]Breakdown from VHM BOQ'!K26,"")</f>
+        <f>IF(B24='[1]Breakdown from VHM BOQ'!B26,'[1]Breakdown from VHM BOQ'!K26,"")</f>
         <v>101200.00000000001</v>
       </c>
       <c r="H24" s="11">
@@ -7419,7 +7416,7 @@
         <v>16</v>
       </c>
       <c r="G26" s="10">
-        <f>IF(B26='[2]Breakdown from VHM BOQ'!B28,'[2]Breakdown from VHM BOQ'!K28,"")</f>
+        <f>IF(B26='[1]Breakdown from VHM BOQ'!B28,'[1]Breakdown from VHM BOQ'!K28,"")</f>
         <v>138710</v>
       </c>
       <c r="H26" s="11">
@@ -7449,7 +7446,7 @@
         <v>16</v>
       </c>
       <c r="G27" s="10">
-        <f>IF(B27='[2]Breakdown from VHM BOQ'!B31,'[2]Breakdown from VHM BOQ'!K31,"")</f>
+        <f>IF(B27='[1]Breakdown from VHM BOQ'!B31,'[1]Breakdown from VHM BOQ'!K31,"")</f>
         <v>132000</v>
       </c>
       <c r="H27" s="11">
@@ -7479,7 +7476,7 @@
         <v>16</v>
       </c>
       <c r="G28" s="10">
-        <f>IF(B28='[2]Breakdown from VHM BOQ'!B32,'[2]Breakdown from VHM BOQ'!K32,"")</f>
+        <f>IF(B28='[1]Breakdown from VHM BOQ'!B32,'[1]Breakdown from VHM BOQ'!K32,"")</f>
         <v>1333750</v>
       </c>
       <c r="H28" s="11">
@@ -7509,7 +7506,7 @@
         <v>16</v>
       </c>
       <c r="G29" s="10">
-        <f>IF(B29='[2]Breakdown from VHM BOQ'!B33,'[2]Breakdown from VHM BOQ'!K33,"")</f>
+        <f>IF(B29='[1]Breakdown from VHM BOQ'!B33,'[1]Breakdown from VHM BOQ'!K33,"")</f>
         <v>1920600.0000000002</v>
       </c>
       <c r="H29" s="11">
@@ -7539,7 +7536,7 @@
         <v>16</v>
       </c>
       <c r="G30" s="10">
-        <f>IF(B30='[2]Breakdown from VHM BOQ'!B34,'[2]Breakdown from VHM BOQ'!K34,"")</f>
+        <f>IF(B30='[1]Breakdown from VHM BOQ'!B34,'[1]Breakdown from VHM BOQ'!K34,"")</f>
         <v>323400</v>
       </c>
       <c r="H30" s="11">
@@ -7569,7 +7566,7 @@
         <v>16</v>
       </c>
       <c r="G31" s="10">
-        <f>IF(B31='[2]Breakdown from VHM BOQ'!B35,'[2]Breakdown from VHM BOQ'!K35,"")</f>
+        <f>IF(B31='[1]Breakdown from VHM BOQ'!B35,'[1]Breakdown from VHM BOQ'!K35,"")</f>
         <v>332904</v>
       </c>
       <c r="H31" s="11">
@@ -7599,7 +7596,7 @@
         <v>16</v>
       </c>
       <c r="G32" s="10">
-        <f>IF(B32='[2]Breakdown from VHM BOQ'!B36,'[2]Breakdown from VHM BOQ'!K36,"")</f>
+        <f>IF(B32='[1]Breakdown from VHM BOQ'!B36,'[1]Breakdown from VHM BOQ'!K36,"")</f>
         <v>37345</v>
       </c>
       <c r="H32" s="11">
@@ -7629,7 +7626,7 @@
         <v>16</v>
       </c>
       <c r="G33" s="10">
-        <f>IF(B33='[2]Breakdown from VHM BOQ'!B37,'[2]Breakdown from VHM BOQ'!K37,"")</f>
+        <f>IF(B33='[1]Breakdown from VHM BOQ'!B37,'[1]Breakdown from VHM BOQ'!K37,"")</f>
         <v>90695.000000000015</v>
       </c>
       <c r="H33" s="11">
@@ -7659,7 +7656,7 @@
         <v>16</v>
       </c>
       <c r="G34" s="10">
-        <f>IF(B34='[2]Breakdown from VHM BOQ'!B38,'[2]Breakdown from VHM BOQ'!K38,"")</f>
+        <f>IF(B34='[1]Breakdown from VHM BOQ'!B38,'[1]Breakdown from VHM BOQ'!K38,"")</f>
         <v>101200.00000000001</v>
       </c>
       <c r="H34" s="11">
@@ -7708,7 +7705,7 @@
         <v>16</v>
       </c>
       <c r="G36" s="10">
-        <f>IF(B36='[2]Breakdown from VHM BOQ'!B40,'[2]Breakdown from VHM BOQ'!K40,"")</f>
+        <f>IF(B36='[1]Breakdown from VHM BOQ'!B40,'[1]Breakdown from VHM BOQ'!K40,"")</f>
         <v>53350.000000000007</v>
       </c>
       <c r="H36" s="11">
@@ -7738,7 +7735,7 @@
         <v>16</v>
       </c>
       <c r="G37" s="10">
-        <f>IF(B37='[2]Breakdown from VHM BOQ'!B41,'[2]Breakdown from VHM BOQ'!K41,"")</f>
+        <f>IF(B37='[1]Breakdown from VHM BOQ'!B41,'[1]Breakdown from VHM BOQ'!K41,"")</f>
         <v>234740.00000000003</v>
       </c>
       <c r="H37" s="11">
@@ -7785,7 +7782,7 @@
         <v>16</v>
       </c>
       <c r="G39" s="10">
-        <f>IF(B39='[2]Breakdown from VHM BOQ'!B43,'[2]Breakdown from VHM BOQ'!K43,"")</f>
+        <f>IF(B39='[1]Breakdown from VHM BOQ'!B43,'[1]Breakdown from VHM BOQ'!K43,"")</f>
         <v>1562000.0000000002</v>
       </c>
       <c r="H39" s="11">
@@ -7815,7 +7812,7 @@
         <v>16</v>
       </c>
       <c r="G40" s="10">
-        <f>IF(B40='[2]Breakdown from VHM BOQ'!B44,'[2]Breakdown from VHM BOQ'!K44,"")</f>
+        <f>IF(B40='[1]Breakdown from VHM BOQ'!B44,'[1]Breakdown from VHM BOQ'!K44,"")</f>
         <v>1004953.95</v>
       </c>
       <c r="H40" s="11">
@@ -7862,7 +7859,7 @@
         <v>64</v>
       </c>
       <c r="G42" s="10">
-        <f>IF(B42='[2]Breakdown from VHM BOQ'!B48,'[2]Breakdown from VHM BOQ'!K48,"")</f>
+        <f>IF(B42='[1]Breakdown from VHM BOQ'!B48,'[1]Breakdown from VHM BOQ'!K48,"")</f>
         <v>6935500.0000000009</v>
       </c>
       <c r="H42" s="11">
@@ -7956,7 +7953,7 @@
         <v>16</v>
       </c>
       <c r="G46" s="10">
-        <f>IF(B46='[2]Breakdown from VHM BOQ'!B56,'[2]Breakdown from VHM BOQ'!K56,"")</f>
+        <f>IF(B46='[1]Breakdown from VHM BOQ'!B56,'[1]Breakdown from VHM BOQ'!K56,"")</f>
         <v>4801500</v>
       </c>
       <c r="H46" s="11">
@@ -7984,7 +7981,7 @@
         <v>16</v>
       </c>
       <c r="G47" s="10">
-        <f>IF(B47='[2]Breakdown from VHM BOQ'!B58,'[2]Breakdown from VHM BOQ'!K58,"")</f>
+        <f>IF(B47='[1]Breakdown from VHM BOQ'!B58,'[1]Breakdown from VHM BOQ'!K58,"")</f>
         <v>110000.00000000001</v>
       </c>
       <c r="H47" s="11">
@@ -8031,7 +8028,7 @@
         <v>76</v>
       </c>
       <c r="G49" s="10">
-        <f>IF(B49='[2]Breakdown from VHM BOQ'!B63,'[2]Breakdown from VHM BOQ'!K63,"")</f>
+        <f>IF(B49='[1]Breakdown from VHM BOQ'!B63,'[1]Breakdown from VHM BOQ'!K63,"")</f>
         <v>176734.5723</v>
       </c>
       <c r="H49" s="11">
@@ -8059,7 +8056,7 @@
         <v>76</v>
       </c>
       <c r="G50" s="10">
-        <f>IF(B50='[2]Breakdown from VHM BOQ'!B64,'[2]Breakdown from VHM BOQ'!K64,"")</f>
+        <f>IF(B50='[1]Breakdown from VHM BOQ'!B64,'[1]Breakdown from VHM BOQ'!K64,"")</f>
         <v>176734.5723</v>
       </c>
       <c r="H50" s="11">
@@ -8087,7 +8084,7 @@
         <v>76</v>
       </c>
       <c r="G51" s="10">
-        <f>IF(B51='[2]Breakdown from VHM BOQ'!B65,'[2]Breakdown from VHM BOQ'!K65,"")</f>
+        <f>IF(B51='[1]Breakdown from VHM BOQ'!B65,'[1]Breakdown from VHM BOQ'!K65,"")</f>
         <v>34100</v>
       </c>
       <c r="H51" s="11">
@@ -8144,7 +8141,7 @@
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="10">
-        <f>IF(B53='[2]Breakdown from VHM BOQ'!B76,'[2]Breakdown from VHM BOQ'!K76,"")</f>
+        <f>IF(B53='[1]Breakdown from VHM BOQ'!B76,'[1]Breakdown from VHM BOQ'!K76,"")</f>
         <v>128040.00000000001</v>
       </c>
       <c r="H53" s="11">
@@ -8173,7 +8170,7 @@
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="10">
-        <f>IF(B54='[2]Breakdown from VHM BOQ'!B77,'[2]Breakdown from VHM BOQ'!K77,"")</f>
+        <f>IF(B54='[1]Breakdown from VHM BOQ'!B77,'[1]Breakdown from VHM BOQ'!K77,"")</f>
         <v>154715</v>
       </c>
       <c r="H54" s="11">
@@ -8200,7 +8197,7 @@
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="10">
-        <f>IF(B55='[2]Breakdown from VHM BOQ'!B78,'[2]Breakdown from VHM BOQ'!K78,"")</f>
+        <f>IF(B55='[1]Breakdown from VHM BOQ'!B78,'[1]Breakdown from VHM BOQ'!K78,"")</f>
         <v>16005.000000000002</v>
       </c>
       <c r="H55" s="11">
@@ -8228,7 +8225,7 @@
         <v>16</v>
       </c>
       <c r="G56" s="10">
-        <f>IF(B56='[2]Breakdown from VHM BOQ'!B79,'[2]Breakdown from VHM BOQ'!K79,"")</f>
+        <f>IF(B56='[1]Breakdown from VHM BOQ'!B79,'[1]Breakdown from VHM BOQ'!K79,"")</f>
         <v>373450.00000000006</v>
       </c>
       <c r="H56" s="11">
@@ -8254,7 +8251,7 @@
       </c>
       <c r="F57" s="53"/>
       <c r="G57" s="58">
-        <f>IF(B57='[2]Breakdown from VHM BOQ'!B80,'[2]Breakdown from VHM BOQ'!K80,"")</f>
+        <f>IF(B57='[1]Breakdown from VHM BOQ'!B80,'[1]Breakdown from VHM BOQ'!K80,"")</f>
         <v>1100000</v>
       </c>
       <c r="H57" s="51">
@@ -8316,10 +8313,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="152"/>
+      <c r="B1" s="162"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:10">
@@ -8330,13 +8327,13 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="13.15" customHeight="1">
-      <c r="A3" s="153" t="s">
+      <c r="A3" s="163" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="153"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="153"/>
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:10" ht="14.25" customHeight="1">
@@ -8346,10 +8343,10 @@
     <row r="5" spans="1:10" ht="25.5" customHeight="1">
       <c r="B5" s="29"/>
       <c r="C5" s="4"/>
-      <c r="G5" s="156" t="s">
+      <c r="G5" s="165" t="s">
         <v>153</v>
       </c>
-      <c r="H5" s="155"/>
+      <c r="H5" s="166"/>
     </row>
     <row r="6" spans="1:10" s="7" customFormat="1" ht="16.5" thickBot="1">
       <c r="A6" s="43" t="s">
@@ -8361,8 +8358,8 @@
       <c r="C6" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="154"/>
-      <c r="E6" s="154"/>
+      <c r="D6" s="164"/>
+      <c r="E6" s="164"/>
       <c r="F6" s="43" t="s">
         <v>7</v>
       </c>
@@ -8412,7 +8409,7 @@
         <v>16</v>
       </c>
       <c r="G8" s="10">
-        <f>IF(B8='[2]Breakdown from VHM BOQ'!B9,'[2]Breakdown from VHM BOQ'!L9,"")*1.1</f>
+        <f>IF(B8='[1]Breakdown from VHM BOQ'!B9,'[1]Breakdown from VHM BOQ'!L9,"")*1.1</f>
         <v>77</v>
       </c>
       <c r="H8" s="11">
@@ -8438,7 +8435,7 @@
         <v>16</v>
       </c>
       <c r="G9" s="10">
-        <f>IF(B9='[2]Breakdown from VHM BOQ'!B10,'[2]Breakdown from VHM BOQ'!L10,"")*1.1</f>
+        <f>IF(B9='[1]Breakdown from VHM BOQ'!B10,'[1]Breakdown from VHM BOQ'!L10,"")*1.1</f>
         <v>77</v>
       </c>
       <c r="H9" s="11">
@@ -8464,7 +8461,7 @@
         <v>16</v>
       </c>
       <c r="G10" s="10">
-        <f>IF(B10='[2]Breakdown from VHM BOQ'!B11,'[2]Breakdown from VHM BOQ'!L11,"")*1.1</f>
+        <f>IF(B10='[1]Breakdown from VHM BOQ'!B11,'[1]Breakdown from VHM BOQ'!L11,"")*1.1</f>
         <v>6212800.0000000009</v>
       </c>
       <c r="H10" s="11">
@@ -8544,7 +8541,7 @@
         <v>16</v>
       </c>
       <c r="G14" s="10">
-        <f>IF(B14='[2]Breakdown from VHM BOQ'!B15,'[2]Breakdown from VHM BOQ'!L15,"")</f>
+        <f>IF(B14='[1]Breakdown from VHM BOQ'!B15,'[1]Breakdown from VHM BOQ'!L15,"")</f>
         <v>138710</v>
       </c>
       <c r="H14" s="11">
@@ -8575,7 +8572,7 @@
         <v>16</v>
       </c>
       <c r="G15" s="10">
-        <f>IF(B15='[2]Breakdown from VHM BOQ'!B18,'[2]Breakdown from VHM BOQ'!L18,"")</f>
+        <f>IF(B15='[1]Breakdown from VHM BOQ'!B18,'[1]Breakdown from VHM BOQ'!L18,"")</f>
         <v>132000</v>
       </c>
       <c r="H15" s="11">
@@ -8604,7 +8601,7 @@
         <v>16</v>
       </c>
       <c r="G16" s="10">
-        <f>IF(B16='[2]Breakdown from VHM BOQ'!B19,'[2]Breakdown from VHM BOQ'!L19,"")</f>
+        <f>IF(B16='[1]Breakdown from VHM BOQ'!B19,'[1]Breakdown from VHM BOQ'!L19,"")</f>
         <v>16005.000000000002</v>
       </c>
       <c r="H16" s="11">
@@ -8635,7 +8632,7 @@
         <v>16</v>
       </c>
       <c r="G17" s="10">
-        <f>IF(B17='[2]Breakdown from VHM BOQ'!B20,'[2]Breakdown from VHM BOQ'!L20,"")</f>
+        <f>IF(B17='[1]Breakdown from VHM BOQ'!B20,'[1]Breakdown from VHM BOQ'!L20,"")</f>
         <v>1333750</v>
       </c>
       <c r="H17" s="11">
@@ -8666,7 +8663,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="10">
-        <f>IF(B18='[2]Breakdown from VHM BOQ'!B21,'[2]Breakdown from VHM BOQ'!L21,"")</f>
+        <f>IF(B18='[1]Breakdown from VHM BOQ'!B21,'[1]Breakdown from VHM BOQ'!L21,"")</f>
         <v>1920600.0000000002</v>
       </c>
       <c r="H18" s="11">
@@ -8697,7 +8694,7 @@
         <v>16</v>
       </c>
       <c r="G19" s="10">
-        <f>IF(B19='[2]Breakdown from VHM BOQ'!B22,'[2]Breakdown from VHM BOQ'!L22,"")</f>
+        <f>IF(B19='[1]Breakdown from VHM BOQ'!B22,'[1]Breakdown from VHM BOQ'!L22,"")</f>
         <v>323400</v>
       </c>
       <c r="H19" s="11">
@@ -8727,7 +8724,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="10">
-        <f>IF(B20='[2]Breakdown from VHM BOQ'!B23,'[2]Breakdown from VHM BOQ'!L23,"")</f>
+        <f>IF(B20='[1]Breakdown from VHM BOQ'!B23,'[1]Breakdown from VHM BOQ'!L23,"")</f>
         <v>332904</v>
       </c>
       <c r="H20" s="11">
@@ -8757,7 +8754,7 @@
         <v>16</v>
       </c>
       <c r="G21" s="10">
-        <f>IF(B21='[2]Breakdown from VHM BOQ'!B24,'[2]Breakdown from VHM BOQ'!L24,"")</f>
+        <f>IF(B21='[1]Breakdown from VHM BOQ'!B24,'[1]Breakdown from VHM BOQ'!L24,"")</f>
         <v>37345</v>
       </c>
       <c r="H21" s="11">
@@ -8788,7 +8785,7 @@
         <v>16</v>
       </c>
       <c r="G22" s="10">
-        <f>IF(B22='[2]Breakdown from VHM BOQ'!B25,'[2]Breakdown from VHM BOQ'!L25,"")</f>
+        <f>IF(B22='[1]Breakdown from VHM BOQ'!B25,'[1]Breakdown from VHM BOQ'!L25,"")</f>
         <v>90695.000000000015</v>
       </c>
       <c r="H22" s="11">
@@ -8819,7 +8816,7 @@
         <v>16</v>
       </c>
       <c r="G23" s="10">
-        <f>IF(B23='[2]Breakdown from VHM BOQ'!B26,'[2]Breakdown from VHM BOQ'!L26,"")</f>
+        <f>IF(B23='[1]Breakdown from VHM BOQ'!B26,'[1]Breakdown from VHM BOQ'!L26,"")</f>
         <v>101200.00000000001</v>
       </c>
       <c r="H23" s="11">
@@ -8868,7 +8865,7 @@
         <v>16</v>
       </c>
       <c r="G25" s="10">
-        <f>IF(B25='[2]Breakdown from VHM BOQ'!B28,'[2]Breakdown from VHM BOQ'!L28,"")</f>
+        <f>IF(B25='[1]Breakdown from VHM BOQ'!B28,'[1]Breakdown from VHM BOQ'!L28,"")</f>
         <v>138710</v>
       </c>
       <c r="H25" s="11">
@@ -8898,7 +8895,7 @@
         <v>16</v>
       </c>
       <c r="G26" s="10">
-        <f>IF(B26='[2]Breakdown from VHM BOQ'!B31,'[2]Breakdown from VHM BOQ'!L31,"")</f>
+        <f>IF(B26='[1]Breakdown from VHM BOQ'!B31,'[1]Breakdown from VHM BOQ'!L31,"")</f>
         <v>132000</v>
       </c>
       <c r="H26" s="11">
@@ -8928,7 +8925,7 @@
         <v>16</v>
       </c>
       <c r="G27" s="10">
-        <f>IF(B27='[2]Breakdown from VHM BOQ'!B32,'[2]Breakdown from VHM BOQ'!L32,"")</f>
+        <f>IF(B27='[1]Breakdown from VHM BOQ'!B32,'[1]Breakdown from VHM BOQ'!L32,"")</f>
         <v>1333750</v>
       </c>
       <c r="H27" s="11">
@@ -8958,7 +8955,7 @@
         <v>16</v>
       </c>
       <c r="G28" s="10">
-        <f>IF(B28='[2]Breakdown from VHM BOQ'!B33,'[2]Breakdown from VHM BOQ'!L33,"")</f>
+        <f>IF(B28='[1]Breakdown from VHM BOQ'!B33,'[1]Breakdown from VHM BOQ'!L33,"")</f>
         <v>1920600.0000000002</v>
       </c>
       <c r="H28" s="11">
@@ -8988,7 +8985,7 @@
         <v>16</v>
       </c>
       <c r="G29" s="10">
-        <f>IF(B29='[2]Breakdown from VHM BOQ'!B34,'[2]Breakdown from VHM BOQ'!L34,"")</f>
+        <f>IF(B29='[1]Breakdown from VHM BOQ'!B34,'[1]Breakdown from VHM BOQ'!L34,"")</f>
         <v>323400</v>
       </c>
       <c r="H29" s="11">
@@ -9018,7 +9015,7 @@
         <v>16</v>
       </c>
       <c r="G30" s="10">
-        <f>IF(B30='[2]Breakdown from VHM BOQ'!B35,'[2]Breakdown from VHM BOQ'!L35,"")</f>
+        <f>IF(B30='[1]Breakdown from VHM BOQ'!B35,'[1]Breakdown from VHM BOQ'!L35,"")</f>
         <v>332904</v>
       </c>
       <c r="H30" s="11">
@@ -9048,7 +9045,7 @@
         <v>16</v>
       </c>
       <c r="G31" s="10">
-        <f>IF(B31='[2]Breakdown from VHM BOQ'!B36,'[2]Breakdown from VHM BOQ'!L36,"")</f>
+        <f>IF(B31='[1]Breakdown from VHM BOQ'!B36,'[1]Breakdown from VHM BOQ'!L36,"")</f>
         <v>37345</v>
       </c>
       <c r="H31" s="11">
@@ -9078,7 +9075,7 @@
         <v>16</v>
       </c>
       <c r="G32" s="10">
-        <f>IF(B32='[2]Breakdown from VHM BOQ'!B37,'[2]Breakdown from VHM BOQ'!L37,"")</f>
+        <f>IF(B32='[1]Breakdown from VHM BOQ'!B37,'[1]Breakdown from VHM BOQ'!L37,"")</f>
         <v>90695.000000000015</v>
       </c>
       <c r="H32" s="11">
@@ -9108,7 +9105,7 @@
         <v>16</v>
       </c>
       <c r="G33" s="10">
-        <f>IF(B33='[2]Breakdown from VHM BOQ'!B38,'[2]Breakdown from VHM BOQ'!L38,"")</f>
+        <f>IF(B33='[1]Breakdown from VHM BOQ'!B38,'[1]Breakdown from VHM BOQ'!L38,"")</f>
         <v>101200.00000000001</v>
       </c>
       <c r="H33" s="11">
@@ -9157,7 +9154,7 @@
         <v>16</v>
       </c>
       <c r="G35" s="10">
-        <f>IF(B35='[2]Breakdown from VHM BOQ'!B40,'[2]Breakdown from VHM BOQ'!L40,"")</f>
+        <f>IF(B35='[1]Breakdown from VHM BOQ'!B40,'[1]Breakdown from VHM BOQ'!L40,"")</f>
         <v>53350.000000000007</v>
       </c>
       <c r="H35" s="11">
@@ -9187,7 +9184,7 @@
         <v>16</v>
       </c>
       <c r="G36" s="10">
-        <f>IF(B36='[2]Breakdown from VHM BOQ'!B41,'[2]Breakdown from VHM BOQ'!L41,"")</f>
+        <f>IF(B36='[1]Breakdown from VHM BOQ'!B41,'[1]Breakdown from VHM BOQ'!L41,"")</f>
         <v>234740.00000000003</v>
       </c>
       <c r="H36" s="11">
@@ -9234,7 +9231,7 @@
         <v>16</v>
       </c>
       <c r="G38" s="10">
-        <f>IF(B38='[2]Breakdown from VHM BOQ'!B43,'[2]Breakdown from VHM BOQ'!L43,"")</f>
+        <f>IF(B38='[1]Breakdown from VHM BOQ'!B43,'[1]Breakdown from VHM BOQ'!L43,"")</f>
         <v>1562000.0000000002</v>
       </c>
       <c r="H38" s="11">
@@ -9264,7 +9261,7 @@
         <v>16</v>
       </c>
       <c r="G39" s="10">
-        <f>IF(B39='[2]Breakdown from VHM BOQ'!B44,'[2]Breakdown from VHM BOQ'!L44,"")</f>
+        <f>IF(B39='[1]Breakdown from VHM BOQ'!B44,'[1]Breakdown from VHM BOQ'!L44,"")</f>
         <v>1004953.95</v>
       </c>
       <c r="H39" s="11">
@@ -9311,7 +9308,7 @@
         <v>64</v>
       </c>
       <c r="G41" s="10">
-        <f>IF(B41='[2]Breakdown from VHM BOQ'!B49,'[2]Breakdown from VHM BOQ'!L49,"")</f>
+        <f>IF(B41='[1]Breakdown from VHM BOQ'!B49,'[1]Breakdown from VHM BOQ'!L49,"")</f>
         <v>11737000.000000002</v>
       </c>
       <c r="H41" s="11">
@@ -9405,7 +9402,7 @@
         <v>16</v>
       </c>
       <c r="G45" s="10">
-        <f>IF(B45='[2]Breakdown from VHM BOQ'!B55,'[2]Breakdown from VHM BOQ'!L55,"")</f>
+        <f>IF(B45='[1]Breakdown from VHM BOQ'!B55,'[1]Breakdown from VHM BOQ'!L55,"")</f>
         <v>6402000.0000000009</v>
       </c>
       <c r="H45" s="11">
@@ -9433,7 +9430,7 @@
         <v>16</v>
       </c>
       <c r="G46" s="10">
-        <f>IF(B46='[2]Breakdown from VHM BOQ'!B58,'[2]Breakdown from VHM BOQ'!L58,"")</f>
+        <f>IF(B46='[1]Breakdown from VHM BOQ'!B58,'[1]Breakdown from VHM BOQ'!L58,"")</f>
         <v>110000.00000000001</v>
       </c>
       <c r="H46" s="11">
@@ -9480,7 +9477,7 @@
         <v>76</v>
       </c>
       <c r="G48" s="10">
-        <f>IF(B48='[2]Breakdown from VHM BOQ'!B66,'[2]Breakdown from VHM BOQ'!L66,"")</f>
+        <f>IF(B48='[1]Breakdown from VHM BOQ'!B66,'[1]Breakdown from VHM BOQ'!L66,"")</f>
         <v>291982.81612500007</v>
       </c>
       <c r="H48" s="11">
@@ -9508,7 +9505,7 @@
         <v>76</v>
       </c>
       <c r="G49" s="10">
-        <f>IF(B49='[2]Breakdown from VHM BOQ'!B67,'[2]Breakdown from VHM BOQ'!L67,"")</f>
+        <f>IF(B49='[1]Breakdown from VHM BOQ'!B67,'[1]Breakdown from VHM BOQ'!L67,"")</f>
         <v>291982.81612500007</v>
       </c>
       <c r="H49" s="11">
@@ -9536,7 +9533,7 @@
         <v>76</v>
       </c>
       <c r="G50" s="10">
-        <f>IF(B50='[2]Breakdown from VHM BOQ'!B68,'[2]Breakdown from VHM BOQ'!L68,"")</f>
+        <f>IF(B50='[1]Breakdown from VHM BOQ'!B68,'[1]Breakdown from VHM BOQ'!L68,"")</f>
         <v>61050.000000000007</v>
       </c>
       <c r="H50" s="11">
@@ -9593,7 +9590,7 @@
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="10">
-        <f>IF(B52='[2]Breakdown from VHM BOQ'!B76,'[2]Breakdown from VHM BOQ'!L76,"")</f>
+        <f>IF(B52='[1]Breakdown from VHM BOQ'!B76,'[1]Breakdown from VHM BOQ'!L76,"")</f>
         <v>128040.00000000001</v>
       </c>
       <c r="H52" s="11">
@@ -9622,7 +9619,7 @@
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="10">
-        <f>IF(B53='[2]Breakdown from VHM BOQ'!B77,'[2]Breakdown from VHM BOQ'!L77,"")</f>
+        <f>IF(B53='[1]Breakdown from VHM BOQ'!B77,'[1]Breakdown from VHM BOQ'!L77,"")</f>
         <v>154715</v>
       </c>
       <c r="H53" s="11">
@@ -9649,7 +9646,7 @@
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="10">
-        <f>IF(B54='[2]Breakdown from VHM BOQ'!B78,'[2]Breakdown from VHM BOQ'!L78,"")</f>
+        <f>IF(B54='[1]Breakdown from VHM BOQ'!B78,'[1]Breakdown from VHM BOQ'!L78,"")</f>
         <v>16005.000000000002</v>
       </c>
       <c r="H54" s="11">
@@ -9677,7 +9674,7 @@
         <v>16</v>
       </c>
       <c r="G55" s="10">
-        <f>IF(B55='[2]Breakdown from VHM BOQ'!B79,'[2]Breakdown from VHM BOQ'!L79,"")</f>
+        <f>IF(B55='[1]Breakdown from VHM BOQ'!B79,'[1]Breakdown from VHM BOQ'!L79,"")</f>
         <v>373450.00000000006</v>
       </c>
       <c r="H55" s="11">
@@ -9701,7 +9698,7 @@
       <c r="E56" s="52"/>
       <c r="F56" s="53"/>
       <c r="G56" s="58">
-        <f>IF(B56='[2]Breakdown from VHM BOQ'!B80,'[2]Breakdown from VHM BOQ'!L80,"")</f>
+        <f>IF(B56='[1]Breakdown from VHM BOQ'!B80,'[1]Breakdown from VHM BOQ'!L80,"")</f>
         <v>1100000</v>
       </c>
       <c r="H56" s="51">
@@ -9763,10 +9760,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="152"/>
+      <c r="B1" s="162"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:9">
@@ -9777,13 +9774,13 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:9" ht="13.15" customHeight="1">
-      <c r="A3" s="153" t="s">
+      <c r="A3" s="163" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="153"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="153"/>
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:9" ht="13.15" customHeight="1">
@@ -9793,10 +9790,10 @@
     <row r="5" spans="1:9" ht="25.5" customHeight="1">
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="G5" s="156" t="s">
+      <c r="G5" s="165" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="155"/>
+      <c r="H5" s="166"/>
     </row>
     <row r="6" spans="1:9" s="47" customFormat="1" ht="16.5" thickBot="1">
       <c r="A6" s="43" t="s">
@@ -9808,10 +9805,10 @@
       <c r="C6" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="154" t="s">
+      <c r="D6" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="154"/>
+      <c r="E6" s="164"/>
       <c r="F6" s="43" t="s">
         <v>7</v>
       </c>
@@ -9823,11 +9820,11 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="151"/>
-      <c r="E7" s="151"/>
+      <c r="A7" s="159"/>
+      <c r="B7" s="160"/>
+      <c r="C7" s="161"/>
+      <c r="D7" s="161"/>
+      <c r="E7" s="161"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:9" s="26" customFormat="1" ht="16">
@@ -9869,7 +9866,7 @@
         <v>16</v>
       </c>
       <c r="G9" s="10">
-        <f>IF(B9='[1]Breakdown from VHM BOQ'!B9,'[1]Breakdown from VHM BOQ'!J9,"")</f>
+        <f>IF(B9='[2]Breakdown from VHM BOQ'!B9,'[2]Breakdown from VHM BOQ'!J9,"")</f>
         <v>86</v>
       </c>
       <c r="H9" s="11">
@@ -9895,7 +9892,7 @@
         <v>16</v>
       </c>
       <c r="G10" s="10">
-        <f>IF(B10='[1]Breakdown from VHM BOQ'!B10,'[1]Breakdown from VHM BOQ'!J10,"")</f>
+        <f>IF(B10='[2]Breakdown from VHM BOQ'!B10,'[2]Breakdown from VHM BOQ'!J10,"")</f>
         <v>86</v>
       </c>
       <c r="H10" s="11">
@@ -9921,7 +9918,7 @@
         <v>16</v>
       </c>
       <c r="G11" s="10">
-        <f>IF(B11='[1]Breakdown from VHM BOQ'!B11,'[1]Breakdown from VHM BOQ'!J11,"")</f>
+        <f>IF(B11='[2]Breakdown from VHM BOQ'!B11,'[2]Breakdown from VHM BOQ'!J11,"")</f>
         <v>3044000</v>
       </c>
       <c r="H11" s="11">
@@ -10002,7 +9999,7 @@
         <v>16</v>
       </c>
       <c r="G15" s="10">
-        <f>IF(B15='[1]Breakdown from VHM BOQ'!B15,'[1]Breakdown from VHM BOQ'!J15,"")</f>
+        <f>IF(B15='[2]Breakdown from VHM BOQ'!B15,'[2]Breakdown from VHM BOQ'!J15,"")</f>
         <v>126100</v>
       </c>
       <c r="H15" s="11">
@@ -10030,7 +10027,7 @@
         <v>16</v>
       </c>
       <c r="G16" s="10">
-        <f>IF(B16='[1]Breakdown from VHM BOQ'!B18,'[1]Breakdown from VHM BOQ'!J18,"")</f>
+        <f>IF(B16='[2]Breakdown from VHM BOQ'!B18,'[2]Breakdown from VHM BOQ'!J18,"")</f>
         <v>120000</v>
       </c>
       <c r="H16" s="11">
@@ -10056,7 +10053,7 @@
         <v>16</v>
       </c>
       <c r="G17" s="10">
-        <f>IF(B17='[1]Breakdown from VHM BOQ'!B19,'[1]Breakdown from VHM BOQ'!J19,"")</f>
+        <f>IF(B17='[2]Breakdown from VHM BOQ'!B19,'[2]Breakdown from VHM BOQ'!J19,"")</f>
         <v>14550</v>
       </c>
       <c r="H17" s="11">
@@ -10085,7 +10082,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="10">
-        <f>IF(B18='[1]Breakdown from VHM BOQ'!B20,'[1]Breakdown from VHM BOQ'!J20,"")</f>
+        <f>IF(B18='[2]Breakdown from VHM BOQ'!B20,'[2]Breakdown from VHM BOQ'!J20,"")</f>
         <v>1212500</v>
       </c>
       <c r="H18" s="11">
@@ -10113,7 +10110,7 @@
         <v>16</v>
       </c>
       <c r="G19" s="10">
-        <f>IF(B19='[1]Breakdown from VHM BOQ'!B21,'[1]Breakdown from VHM BOQ'!J21,"")</f>
+        <f>IF(B19='[2]Breakdown from VHM BOQ'!B21,'[2]Breakdown from VHM BOQ'!J21,"")</f>
         <v>1746000</v>
       </c>
       <c r="H19" s="11">
@@ -10141,7 +10138,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="10">
-        <f>IF(B20='[1]Breakdown from VHM BOQ'!B22,'[1]Breakdown from VHM BOQ'!J22,"")</f>
+        <f>IF(B20='[2]Breakdown from VHM BOQ'!B22,'[2]Breakdown from VHM BOQ'!J22,"")</f>
         <v>294000</v>
       </c>
       <c r="H20" s="11">
@@ -10169,7 +10166,7 @@
         <v>16</v>
       </c>
       <c r="G21" s="10">
-        <f>IF(B21='[1]Breakdown from VHM BOQ'!B23,'[1]Breakdown from VHM BOQ'!J23,"")</f>
+        <f>IF(B21='[2]Breakdown from VHM BOQ'!B23,'[2]Breakdown from VHM BOQ'!J23,"")</f>
         <v>302640</v>
       </c>
       <c r="H21" s="11">
@@ -10197,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="G22" s="10">
-        <f>IF(B22='[1]Breakdown from VHM BOQ'!B24,'[1]Breakdown from VHM BOQ'!J24,"")</f>
+        <f>IF(B22='[2]Breakdown from VHM BOQ'!B24,'[2]Breakdown from VHM BOQ'!J24,"")</f>
         <v>33950</v>
       </c>
       <c r="H22" s="11">
@@ -10225,7 +10222,7 @@
         <v>16</v>
       </c>
       <c r="G23" s="10">
-        <f>IF(B23='[1]Breakdown from VHM BOQ'!B25,'[1]Breakdown from VHM BOQ'!J25,"")</f>
+        <f>IF(B23='[2]Breakdown from VHM BOQ'!B25,'[2]Breakdown from VHM BOQ'!J25,"")</f>
         <v>82450</v>
       </c>
       <c r="H23" s="11">
@@ -10253,7 +10250,7 @@
         <v>16</v>
       </c>
       <c r="G24" s="10">
-        <f>IF(B24='[1]Breakdown from VHM BOQ'!B26,'[1]Breakdown from VHM BOQ'!J26,"")</f>
+        <f>IF(B24='[2]Breakdown from VHM BOQ'!B26,'[2]Breakdown from VHM BOQ'!J26,"")</f>
         <v>92000</v>
       </c>
       <c r="H24" s="11">
@@ -10298,7 +10295,7 @@
         <v>16</v>
       </c>
       <c r="G26" s="10">
-        <f>IF(B26='[1]Breakdown from VHM BOQ'!B28,'[1]Breakdown from VHM BOQ'!J28,"")</f>
+        <f>IF(B26='[2]Breakdown from VHM BOQ'!B28,'[2]Breakdown from VHM BOQ'!J28,"")</f>
         <v>126100</v>
       </c>
       <c r="H26" s="11">
@@ -10326,7 +10323,7 @@
         <v>16</v>
       </c>
       <c r="G27" s="10">
-        <f>IF(B27='[1]Breakdown from VHM BOQ'!B31,'[1]Breakdown from VHM BOQ'!J31,"")</f>
+        <f>IF(B27='[2]Breakdown from VHM BOQ'!B31,'[2]Breakdown from VHM BOQ'!J31,"")</f>
         <v>120000</v>
       </c>
       <c r="H27" s="11">
@@ -10354,7 +10351,7 @@
         <v>16</v>
       </c>
       <c r="G28" s="10">
-        <f>IF(B28='[1]Breakdown from VHM BOQ'!B32,'[1]Breakdown from VHM BOQ'!J32,"")</f>
+        <f>IF(B28='[2]Breakdown from VHM BOQ'!B32,'[2]Breakdown from VHM BOQ'!J32,"")</f>
         <v>1212500</v>
       </c>
       <c r="H28" s="11">
@@ -10382,7 +10379,7 @@
         <v>16</v>
       </c>
       <c r="G29" s="10">
-        <f>IF(B29='[1]Breakdown from VHM BOQ'!B33,'[1]Breakdown from VHM BOQ'!J33,"")</f>
+        <f>IF(B29='[2]Breakdown from VHM BOQ'!B33,'[2]Breakdown from VHM BOQ'!J33,"")</f>
         <v>1746000</v>
       </c>
       <c r="H29" s="11">
@@ -10410,7 +10407,7 @@
         <v>16</v>
       </c>
       <c r="G30" s="10">
-        <f>IF(B30='[1]Breakdown from VHM BOQ'!B34,'[1]Breakdown from VHM BOQ'!J34,"")</f>
+        <f>IF(B30='[2]Breakdown from VHM BOQ'!B34,'[2]Breakdown from VHM BOQ'!J34,"")</f>
         <v>294000</v>
       </c>
       <c r="H30" s="11">
@@ -10438,7 +10435,7 @@
         <v>16</v>
       </c>
       <c r="G31" s="10">
-        <f>IF(B31='[1]Breakdown from VHM BOQ'!B35,'[1]Breakdown from VHM BOQ'!J35,"")</f>
+        <f>IF(B31='[2]Breakdown from VHM BOQ'!B35,'[2]Breakdown from VHM BOQ'!J35,"")</f>
         <v>302640</v>
       </c>
       <c r="H31" s="11">
@@ -10466,7 +10463,7 @@
         <v>16</v>
       </c>
       <c r="G32" s="10">
-        <f>IF(B32='[1]Breakdown from VHM BOQ'!B36,'[1]Breakdown from VHM BOQ'!J36,"")</f>
+        <f>IF(B32='[2]Breakdown from VHM BOQ'!B36,'[2]Breakdown from VHM BOQ'!J36,"")</f>
         <v>33950</v>
       </c>
       <c r="H32" s="11">
@@ -10494,7 +10491,7 @@
         <v>16</v>
       </c>
       <c r="G33" s="10">
-        <f>IF(B33='[1]Breakdown from VHM BOQ'!B37,'[1]Breakdown from VHM BOQ'!J37,"")</f>
+        <f>IF(B33='[2]Breakdown from VHM BOQ'!B37,'[2]Breakdown from VHM BOQ'!J37,"")</f>
         <v>82450</v>
       </c>
       <c r="H33" s="11">
@@ -10522,7 +10519,7 @@
         <v>16</v>
       </c>
       <c r="G34" s="10">
-        <f>IF(B34='[1]Breakdown from VHM BOQ'!B38,'[1]Breakdown from VHM BOQ'!J38,"")</f>
+        <f>IF(B34='[2]Breakdown from VHM BOQ'!B38,'[2]Breakdown from VHM BOQ'!J38,"")</f>
         <v>92000</v>
       </c>
       <c r="H34" s="11">
@@ -10568,7 +10565,7 @@
         <v>16</v>
       </c>
       <c r="G36" s="10">
-        <f>IF(B36='[1]Breakdown from VHM BOQ'!B40,'[1]Breakdown from VHM BOQ'!J40,"")</f>
+        <f>IF(B36='[2]Breakdown from VHM BOQ'!B40,'[2]Breakdown from VHM BOQ'!J40,"")</f>
         <v>48500</v>
       </c>
       <c r="H36" s="11">
@@ -10596,7 +10593,7 @@
         <v>16</v>
       </c>
       <c r="G37" s="10">
-        <f>IF(B37='[1]Breakdown from VHM BOQ'!B41,'[1]Breakdown from VHM BOQ'!J41,"")</f>
+        <f>IF(B37='[2]Breakdown from VHM BOQ'!B41,'[2]Breakdown from VHM BOQ'!J41,"")</f>
         <v>213400</v>
       </c>
       <c r="H37" s="11">
@@ -10639,7 +10636,7 @@
         <v>16</v>
       </c>
       <c r="G39" s="10">
-        <f>IF(B39='[1]Breakdown from VHM BOQ'!B43,'[1]Breakdown from VHM BOQ'!J43,"")</f>
+        <f>IF(B39='[2]Breakdown from VHM BOQ'!B43,'[2]Breakdown from VHM BOQ'!J43,"")</f>
         <v>1420000</v>
       </c>
       <c r="H39" s="11">
@@ -10667,7 +10664,7 @@
         <v>16</v>
       </c>
       <c r="G40" s="10">
-        <f>IF(B40='[1]Breakdown from VHM BOQ'!B44,'[1]Breakdown from VHM BOQ'!J44,"")</f>
+        <f>IF(B40='[2]Breakdown from VHM BOQ'!B44,'[2]Breakdown from VHM BOQ'!J44,"")</f>
         <v>913594.49999999988</v>
       </c>
       <c r="H40" s="11">
@@ -10709,7 +10706,7 @@
         <v>64</v>
       </c>
       <c r="G42" s="10">
-        <f>IF(B42='[1]Breakdown from VHM BOQ'!B47,'[1]Breakdown from VHM BOQ'!J47,"")</f>
+        <f>IF(B42='[2]Breakdown from VHM BOQ'!B47,'[2]Breakdown from VHM BOQ'!J47,"")</f>
         <v>5044000</v>
       </c>
       <c r="H42" s="11">
@@ -10793,7 +10790,7 @@
         <v>16</v>
       </c>
       <c r="G46" s="10">
-        <f>IF(B46='[1]Breakdown from VHM BOQ'!B57,'[1]Breakdown from VHM BOQ'!J57,"")</f>
+        <f>IF(B46='[2]Breakdown from VHM BOQ'!B57,'[2]Breakdown from VHM BOQ'!J57,"")</f>
         <v>2910000</v>
       </c>
       <c r="H46" s="11">
@@ -10819,7 +10816,7 @@
         <v>16</v>
       </c>
       <c r="G47" s="10">
-        <f>IF(B47='[1]Breakdown from VHM BOQ'!B58,'[1]Breakdown from VHM BOQ'!J58,"")</f>
+        <f>IF(B47='[2]Breakdown from VHM BOQ'!B58,'[2]Breakdown from VHM BOQ'!J58,"")</f>
         <v>100000</v>
       </c>
       <c r="H47" s="11">
@@ -10862,7 +10859,7 @@
         <v>76</v>
       </c>
       <c r="G49" s="10">
-        <f>IF(B49='[1]Breakdown from VHM BOQ'!B60,'[1]Breakdown from VHM BOQ'!J60,"")</f>
+        <f>IF(B49='[2]Breakdown from VHM BOQ'!B60,'[2]Breakdown from VHM BOQ'!J60,"")</f>
         <v>78648.569999999992</v>
       </c>
       <c r="H49" s="11">
@@ -10888,7 +10885,7 @@
         <v>76</v>
       </c>
       <c r="G50" s="10">
-        <f>IF(B50='[1]Breakdown from VHM BOQ'!B61,'[1]Breakdown from VHM BOQ'!J61,"")</f>
+        <f>IF(B50='[2]Breakdown from VHM BOQ'!B61,'[2]Breakdown from VHM BOQ'!J61,"")</f>
         <v>78648.569999999992</v>
       </c>
       <c r="H50" s="11">
@@ -10914,7 +10911,7 @@
         <v>76</v>
       </c>
       <c r="G51" s="10">
-        <f>IF(B51='[1]Breakdown from VHM BOQ'!B62,'[1]Breakdown from VHM BOQ'!J62,"")</f>
+        <f>IF(B51='[2]Breakdown from VHM BOQ'!B62,'[2]Breakdown from VHM BOQ'!J62,"")</f>
         <v>18000</v>
       </c>
       <c r="H51" s="11">
@@ -10966,7 +10963,7 @@
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="10">
-        <f>IF(B53='[1]Breakdown from VHM BOQ'!B76,'[1]Breakdown from VHM BOQ'!J76,"")</f>
+        <f>IF(B53='[2]Breakdown from VHM BOQ'!B76,'[2]Breakdown from VHM BOQ'!J76,"")</f>
         <v>116400</v>
       </c>
       <c r="H53" s="11">
@@ -10993,7 +10990,7 @@
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="10">
-        <f>IF(B54='[1]Breakdown from VHM BOQ'!B77,'[1]Breakdown from VHM BOQ'!J77,"")</f>
+        <f>IF(B54='[2]Breakdown from VHM BOQ'!B77,'[2]Breakdown from VHM BOQ'!J77,"")</f>
         <v>140650</v>
       </c>
       <c r="H54" s="11">
@@ -11018,7 +11015,7 @@
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="10">
-        <f>IF(B55='[1]Breakdown from VHM BOQ'!B78,'[1]Breakdown from VHM BOQ'!J78,"")</f>
+        <f>IF(B55='[2]Breakdown from VHM BOQ'!B78,'[2]Breakdown from VHM BOQ'!J78,"")</f>
         <v>14550</v>
       </c>
       <c r="H55" s="11">
@@ -11044,7 +11041,7 @@
         <v>16</v>
       </c>
       <c r="G56" s="10">
-        <f>IF(B56='[1]Breakdown from VHM BOQ'!B79,'[1]Breakdown from VHM BOQ'!J79,"")</f>
+        <f>IF(B56='[2]Breakdown from VHM BOQ'!B79,'[2]Breakdown from VHM BOQ'!J79,"")</f>
         <v>339500</v>
       </c>
       <c r="H56" s="11">
@@ -11066,7 +11063,7 @@
       <c r="E57" s="52"/>
       <c r="F57" s="53"/>
       <c r="G57" s="58">
-        <f>IF(B57='[1]Breakdown from VHM BOQ'!B80,'[1]Breakdown from VHM BOQ'!J80,"")</f>
+        <f>IF(B57='[2]Breakdown from VHM BOQ'!B80,'[2]Breakdown from VHM BOQ'!J80,"")</f>
         <v>1000000</v>
       </c>
       <c r="H57" s="51">
@@ -11125,10 +11122,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="152"/>
+      <c r="B1" s="162"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:8">
@@ -11139,13 +11136,13 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="13.15" customHeight="1">
-      <c r="A3" s="153" t="s">
+      <c r="A3" s="163" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="153"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="153"/>
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:8" ht="13.15" customHeight="1">
@@ -11155,10 +11152,10 @@
     <row r="5" spans="1:8" ht="25.5" customHeight="1">
       <c r="B5" s="29"/>
       <c r="C5" s="4"/>
-      <c r="G5" s="155" t="s">
+      <c r="G5" s="166" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="155"/>
+      <c r="H5" s="166"/>
     </row>
     <row r="6" spans="1:8" s="47" customFormat="1" ht="16.5" thickBot="1">
       <c r="A6" s="43" t="s">
@@ -11170,8 +11167,8 @@
       <c r="C6" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="154"/>
-      <c r="E6" s="154"/>
+      <c r="D6" s="164"/>
+      <c r="E6" s="164"/>
       <c r="F6" s="43" t="s">
         <v>7</v>
       </c>
@@ -11183,11 +11180,11 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="151"/>
-      <c r="E7" s="151"/>
+      <c r="A7" s="159"/>
+      <c r="B7" s="160"/>
+      <c r="C7" s="161"/>
+      <c r="D7" s="161"/>
+      <c r="E7" s="161"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:8" s="26" customFormat="1" ht="32">
@@ -11229,7 +11226,7 @@
         <v>16</v>
       </c>
       <c r="G9" s="10">
-        <f>IF(B9='[1]Breakdown from VHM BOQ'!B9,'[1]Breakdown from VHM BOQ'!K9,"")</f>
+        <f>IF(B9='[2]Breakdown from VHM BOQ'!B9,'[2]Breakdown from VHM BOQ'!K9,"")</f>
         <v>86</v>
       </c>
       <c r="H9" s="11">
@@ -11255,7 +11252,7 @@
         <v>16</v>
       </c>
       <c r="G10" s="10">
-        <f>IF(B10='[1]Breakdown from VHM BOQ'!B10,'[1]Breakdown from VHM BOQ'!K10,"")</f>
+        <f>IF(B10='[2]Breakdown from VHM BOQ'!B10,'[2]Breakdown from VHM BOQ'!K10,"")</f>
         <v>86</v>
       </c>
       <c r="H10" s="11">
@@ -11281,7 +11278,7 @@
         <v>16</v>
       </c>
       <c r="G11" s="10">
-        <f>IF(B11='[1]Breakdown from VHM BOQ'!B11,'[1]Breakdown from VHM BOQ'!K11,"")</f>
+        <f>IF(B11='[2]Breakdown from VHM BOQ'!B11,'[2]Breakdown from VHM BOQ'!K11,"")</f>
         <v>3324000</v>
       </c>
       <c r="H11" s="11">
@@ -11360,7 +11357,7 @@
         <v>16</v>
       </c>
       <c r="G15" s="10">
-        <f>IF(B15='[1]Breakdown from VHM BOQ'!B15,'[1]Breakdown from VHM BOQ'!K15,"")</f>
+        <f>IF(B15='[2]Breakdown from VHM BOQ'!B15,'[2]Breakdown from VHM BOQ'!K15,"")</f>
         <v>126100</v>
       </c>
       <c r="H15" s="11">
@@ -11389,7 +11386,7 @@
         <v>16</v>
       </c>
       <c r="G16" s="10">
-        <f>IF(B16='[1]Breakdown from VHM BOQ'!B18,'[1]Breakdown from VHM BOQ'!K18,"")</f>
+        <f>IF(B16='[2]Breakdown from VHM BOQ'!B18,'[2]Breakdown from VHM BOQ'!K18,"")</f>
         <v>120000</v>
       </c>
       <c r="H16" s="11">
@@ -11416,7 +11413,7 @@
         <v>16</v>
       </c>
       <c r="G17" s="10">
-        <f>IF(B17='[1]Breakdown from VHM BOQ'!B19,'[1]Breakdown from VHM BOQ'!K19,"")</f>
+        <f>IF(B17='[2]Breakdown from VHM BOQ'!B19,'[2]Breakdown from VHM BOQ'!K19,"")</f>
         <v>14550</v>
       </c>
       <c r="H17" s="11">
@@ -11444,7 +11441,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="10">
-        <f>IF(B18='[1]Breakdown from VHM BOQ'!B20,'[1]Breakdown from VHM BOQ'!K20,"")</f>
+        <f>IF(B18='[2]Breakdown from VHM BOQ'!B20,'[2]Breakdown from VHM BOQ'!K20,"")</f>
         <v>1212500</v>
       </c>
       <c r="H18" s="11">
@@ -11472,7 +11469,7 @@
         <v>16</v>
       </c>
       <c r="G19" s="10">
-        <f>IF(B19='[1]Breakdown from VHM BOQ'!B21,'[1]Breakdown from VHM BOQ'!K21,"")</f>
+        <f>IF(B19='[2]Breakdown from VHM BOQ'!B21,'[2]Breakdown from VHM BOQ'!K21,"")</f>
         <v>1746000</v>
       </c>
       <c r="H19" s="11">
@@ -11501,7 +11498,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="10">
-        <f>IF(B20='[1]Breakdown from VHM BOQ'!B22,'[1]Breakdown from VHM BOQ'!K22,"")</f>
+        <f>IF(B20='[2]Breakdown from VHM BOQ'!B22,'[2]Breakdown from VHM BOQ'!K22,"")</f>
         <v>294000</v>
       </c>
       <c r="H20" s="11">
@@ -11529,7 +11526,7 @@
         <v>16</v>
       </c>
       <c r="G21" s="10">
-        <f>IF(B21='[1]Breakdown from VHM BOQ'!B23,'[1]Breakdown from VHM BOQ'!K23,"")</f>
+        <f>IF(B21='[2]Breakdown from VHM BOQ'!B23,'[2]Breakdown from VHM BOQ'!K23,"")</f>
         <v>302640</v>
       </c>
       <c r="H21" s="11">
@@ -11557,7 +11554,7 @@
         <v>16</v>
       </c>
       <c r="G22" s="10">
-        <f>IF(B22='[1]Breakdown from VHM BOQ'!B24,'[1]Breakdown from VHM BOQ'!K24,"")</f>
+        <f>IF(B22='[2]Breakdown from VHM BOQ'!B24,'[2]Breakdown from VHM BOQ'!K24,"")</f>
         <v>33950</v>
       </c>
       <c r="H22" s="11">
@@ -11586,7 +11583,7 @@
         <v>16</v>
       </c>
       <c r="G23" s="10">
-        <f>IF(B23='[1]Breakdown from VHM BOQ'!B25,'[1]Breakdown from VHM BOQ'!K25,"")</f>
+        <f>IF(B23='[2]Breakdown from VHM BOQ'!B25,'[2]Breakdown from VHM BOQ'!K25,"")</f>
         <v>82450</v>
       </c>
       <c r="H23" s="11">
@@ -11615,7 +11612,7 @@
         <v>16</v>
       </c>
       <c r="G24" s="10">
-        <f>IF(B24='[1]Breakdown from VHM BOQ'!B26,'[1]Breakdown from VHM BOQ'!K26,"")</f>
+        <f>IF(B24='[2]Breakdown from VHM BOQ'!B26,'[2]Breakdown from VHM BOQ'!K26,"")</f>
         <v>92000</v>
       </c>
       <c r="H24" s="11">
@@ -11660,7 +11657,7 @@
         <v>16</v>
       </c>
       <c r="G26" s="10">
-        <f>IF(B26='[1]Breakdown from VHM BOQ'!B28,'[1]Breakdown from VHM BOQ'!K28,"")</f>
+        <f>IF(B26='[2]Breakdown from VHM BOQ'!B28,'[2]Breakdown from VHM BOQ'!K28,"")</f>
         <v>126100</v>
       </c>
       <c r="H26" s="11">
@@ -11688,7 +11685,7 @@
         <v>16</v>
       </c>
       <c r="G27" s="10">
-        <f>IF(B27='[1]Breakdown from VHM BOQ'!B31,'[1]Breakdown from VHM BOQ'!K31,"")</f>
+        <f>IF(B27='[2]Breakdown from VHM BOQ'!B31,'[2]Breakdown from VHM BOQ'!K31,"")</f>
         <v>120000</v>
       </c>
       <c r="H27" s="11">
@@ -11716,7 +11713,7 @@
         <v>16</v>
       </c>
       <c r="G28" s="10">
-        <f>IF(B28='[1]Breakdown from VHM BOQ'!B32,'[1]Breakdown from VHM BOQ'!K32,"")</f>
+        <f>IF(B28='[2]Breakdown from VHM BOQ'!B32,'[2]Breakdown from VHM BOQ'!K32,"")</f>
         <v>1212500</v>
       </c>
       <c r="H28" s="11">
@@ -11744,7 +11741,7 @@
         <v>16</v>
       </c>
       <c r="G29" s="10">
-        <f>IF(B29='[1]Breakdown from VHM BOQ'!B33,'[1]Breakdown from VHM BOQ'!K33,"")</f>
+        <f>IF(B29='[2]Breakdown from VHM BOQ'!B33,'[2]Breakdown from VHM BOQ'!K33,"")</f>
         <v>1746000</v>
       </c>
       <c r="H29" s="11">
@@ -11772,7 +11769,7 @@
         <v>16</v>
       </c>
       <c r="G30" s="10">
-        <f>IF(B30='[1]Breakdown from VHM BOQ'!B34,'[1]Breakdown from VHM BOQ'!K34,"")</f>
+        <f>IF(B30='[2]Breakdown from VHM BOQ'!B34,'[2]Breakdown from VHM BOQ'!K34,"")</f>
         <v>294000</v>
       </c>
       <c r="H30" s="11">
@@ -11800,7 +11797,7 @@
         <v>16</v>
       </c>
       <c r="G31" s="10">
-        <f>IF(B31='[1]Breakdown from VHM BOQ'!B35,'[1]Breakdown from VHM BOQ'!K35,"")</f>
+        <f>IF(B31='[2]Breakdown from VHM BOQ'!B35,'[2]Breakdown from VHM BOQ'!K35,"")</f>
         <v>302640</v>
       </c>
       <c r="H31" s="11">
@@ -11828,7 +11825,7 @@
         <v>16</v>
       </c>
       <c r="G32" s="10">
-        <f>IF(B32='[1]Breakdown from VHM BOQ'!B36,'[1]Breakdown from VHM BOQ'!K36,"")</f>
+        <f>IF(B32='[2]Breakdown from VHM BOQ'!B36,'[2]Breakdown from VHM BOQ'!K36,"")</f>
         <v>33950</v>
       </c>
       <c r="H32" s="11">
@@ -11856,7 +11853,7 @@
         <v>16</v>
       </c>
       <c r="G33" s="10">
-        <f>IF(B33='[1]Breakdown from VHM BOQ'!B37,'[1]Breakdown from VHM BOQ'!K37,"")</f>
+        <f>IF(B33='[2]Breakdown from VHM BOQ'!B37,'[2]Breakdown from VHM BOQ'!K37,"")</f>
         <v>82450</v>
       </c>
       <c r="H33" s="11">
@@ -11884,7 +11881,7 @@
         <v>16</v>
       </c>
       <c r="G34" s="10">
-        <f>IF(B34='[1]Breakdown from VHM BOQ'!B38,'[1]Breakdown from VHM BOQ'!K38,"")</f>
+        <f>IF(B34='[2]Breakdown from VHM BOQ'!B38,'[2]Breakdown from VHM BOQ'!K38,"")</f>
         <v>92000</v>
       </c>
       <c r="H34" s="11">
@@ -11929,7 +11926,7 @@
         <v>16</v>
       </c>
       <c r="G36" s="10">
-        <f>IF(B36='[1]Breakdown from VHM BOQ'!B40,'[1]Breakdown from VHM BOQ'!K40,"")</f>
+        <f>IF(B36='[2]Breakdown from VHM BOQ'!B40,'[2]Breakdown from VHM BOQ'!K40,"")</f>
         <v>48500</v>
       </c>
       <c r="H36" s="11">
@@ -11957,7 +11954,7 @@
         <v>16</v>
       </c>
       <c r="G37" s="10">
-        <f>IF(B37='[1]Breakdown from VHM BOQ'!B41,'[1]Breakdown from VHM BOQ'!K41,"")</f>
+        <f>IF(B37='[2]Breakdown from VHM BOQ'!B41,'[2]Breakdown from VHM BOQ'!K41,"")</f>
         <v>213400</v>
       </c>
       <c r="H37" s="11">
@@ -12000,7 +11997,7 @@
         <v>16</v>
       </c>
       <c r="G39" s="10">
-        <f>IF(B39='[1]Breakdown from VHM BOQ'!B43,'[1]Breakdown from VHM BOQ'!K43,"")</f>
+        <f>IF(B39='[2]Breakdown from VHM BOQ'!B43,'[2]Breakdown from VHM BOQ'!K43,"")</f>
         <v>1420000</v>
       </c>
       <c r="H39" s="11">
@@ -12028,7 +12025,7 @@
         <v>16</v>
       </c>
       <c r="G40" s="10">
-        <f>IF(B40='[1]Breakdown from VHM BOQ'!B44,'[1]Breakdown from VHM BOQ'!K44,"")</f>
+        <f>IF(B40='[2]Breakdown from VHM BOQ'!B44,'[2]Breakdown from VHM BOQ'!K44,"")</f>
         <v>913594.49999999988</v>
       </c>
       <c r="H40" s="11">
@@ -12071,7 +12068,7 @@
         <v>64</v>
       </c>
       <c r="G42" s="10">
-        <f>IF(B42='[1]Breakdown from VHM BOQ'!B48,'[1]Breakdown from VHM BOQ'!K48,"")</f>
+        <f>IF(B42='[2]Breakdown from VHM BOQ'!B48,'[2]Breakdown from VHM BOQ'!K48,"")</f>
         <v>6305000</v>
       </c>
       <c r="H42" s="11">
@@ -12156,7 +12153,7 @@
         <v>16</v>
       </c>
       <c r="G46" s="10">
-        <f>IF(B46='[1]Breakdown from VHM BOQ'!B56,'[1]Breakdown from VHM BOQ'!K56,"")</f>
+        <f>IF(B46='[2]Breakdown from VHM BOQ'!B56,'[2]Breakdown from VHM BOQ'!K56,"")</f>
         <v>4365000</v>
       </c>
       <c r="H46" s="11">
@@ -12182,7 +12179,7 @@
         <v>16</v>
       </c>
       <c r="G47" s="10">
-        <f>IF(B47='[1]Breakdown from VHM BOQ'!B58,'[1]Breakdown from VHM BOQ'!K58,"")</f>
+        <f>IF(B47='[2]Breakdown from VHM BOQ'!B58,'[2]Breakdown from VHM BOQ'!K58,"")</f>
         <v>100000</v>
       </c>
       <c r="H47" s="11">
@@ -12225,7 +12222,7 @@
         <v>76</v>
       </c>
       <c r="G49" s="10">
-        <f>IF(B49='[1]Breakdown from VHM BOQ'!B63,'[1]Breakdown from VHM BOQ'!K63,"")</f>
+        <f>IF(B49='[2]Breakdown from VHM BOQ'!B63,'[2]Breakdown from VHM BOQ'!K63,"")</f>
         <v>160667.79299999998</v>
       </c>
       <c r="H49" s="11">
@@ -12251,7 +12248,7 @@
         <v>76</v>
       </c>
       <c r="G50" s="10">
-        <f>IF(B50='[1]Breakdown from VHM BOQ'!B64,'[1]Breakdown from VHM BOQ'!K64,"")</f>
+        <f>IF(B50='[2]Breakdown from VHM BOQ'!B64,'[2]Breakdown from VHM BOQ'!K64,"")</f>
         <v>160667.79299999998</v>
       </c>
       <c r="H50" s="11">
@@ -12277,7 +12274,7 @@
         <v>76</v>
       </c>
       <c r="G51" s="10">
-        <f>IF(B51='[1]Breakdown from VHM BOQ'!B65,'[1]Breakdown from VHM BOQ'!K65,"")</f>
+        <f>IF(B51='[2]Breakdown from VHM BOQ'!B65,'[2]Breakdown from VHM BOQ'!K65,"")</f>
         <v>31000</v>
       </c>
       <c r="H51" s="11">
@@ -12329,7 +12326,7 @@
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="10">
-        <f>IF(B53='[1]Breakdown from VHM BOQ'!B76,'[1]Breakdown from VHM BOQ'!K76,"")</f>
+        <f>IF(B53='[2]Breakdown from VHM BOQ'!B76,'[2]Breakdown from VHM BOQ'!K76,"")</f>
         <v>116400</v>
       </c>
       <c r="H53" s="11">
@@ -12356,7 +12353,7 @@
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="10">
-        <f>IF(B54='[1]Breakdown from VHM BOQ'!B77,'[1]Breakdown from VHM BOQ'!K77,"")</f>
+        <f>IF(B54='[2]Breakdown from VHM BOQ'!B77,'[2]Breakdown from VHM BOQ'!K77,"")</f>
         <v>140650</v>
       </c>
       <c r="H54" s="11">
@@ -12381,7 +12378,7 @@
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="10">
-        <f>IF(B55='[1]Breakdown from VHM BOQ'!B78,'[1]Breakdown from VHM BOQ'!K78,"")</f>
+        <f>IF(B55='[2]Breakdown from VHM BOQ'!B78,'[2]Breakdown from VHM BOQ'!K78,"")</f>
         <v>14550</v>
       </c>
       <c r="H55" s="11">
@@ -12407,7 +12404,7 @@
         <v>16</v>
       </c>
       <c r="G56" s="10">
-        <f>IF(B56='[1]Breakdown from VHM BOQ'!B79,'[1]Breakdown from VHM BOQ'!K79,"")</f>
+        <f>IF(B56='[2]Breakdown from VHM BOQ'!B79,'[2]Breakdown from VHM BOQ'!K79,"")</f>
         <v>339500</v>
       </c>
       <c r="H56" s="11">
@@ -12431,7 +12428,7 @@
       </c>
       <c r="F57" s="53"/>
       <c r="G57" s="58">
-        <f>IF(B57='[1]Breakdown from VHM BOQ'!B80,'[1]Breakdown from VHM BOQ'!K80,"")</f>
+        <f>IF(B57='[2]Breakdown from VHM BOQ'!B80,'[2]Breakdown from VHM BOQ'!K80,"")</f>
         <v>1000000</v>
       </c>
       <c r="H57" s="51">
@@ -12490,10 +12487,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="152"/>
+      <c r="B1" s="162"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:8">
@@ -12504,13 +12501,13 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="13.15" customHeight="1">
-      <c r="A3" s="153" t="s">
+      <c r="A3" s="163" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="153"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="153"/>
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:8" ht="13.15" customHeight="1">
@@ -12520,10 +12517,10 @@
     <row r="5" spans="1:8" ht="25.5" customHeight="1">
       <c r="B5" s="29"/>
       <c r="C5" s="4"/>
-      <c r="G5" s="156" t="s">
+      <c r="G5" s="165" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="157"/>
+      <c r="H5" s="167"/>
     </row>
     <row r="6" spans="1:8" s="47" customFormat="1" ht="16.5" thickBot="1">
       <c r="A6" s="43" t="s">
@@ -12535,8 +12532,8 @@
       <c r="C6" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="154"/>
-      <c r="E6" s="154"/>
+      <c r="D6" s="164"/>
+      <c r="E6" s="164"/>
       <c r="F6" s="43" t="s">
         <v>7</v>
       </c>
@@ -12586,7 +12583,7 @@
         <v>16</v>
       </c>
       <c r="G8" s="10">
-        <f>IF(B8='[1]Breakdown from VHM BOQ'!B9,'[1]Breakdown from VHM BOQ'!L9,"")</f>
+        <f>IF(B8='[2]Breakdown from VHM BOQ'!B9,'[2]Breakdown from VHM BOQ'!L9,"")</f>
         <v>70</v>
       </c>
       <c r="H8" s="11">
@@ -12612,7 +12609,7 @@
         <v>16</v>
       </c>
       <c r="G9" s="10">
-        <f>IF(B9='[1]Breakdown from VHM BOQ'!B10,'[1]Breakdown from VHM BOQ'!L10,"")</f>
+        <f>IF(B9='[2]Breakdown from VHM BOQ'!B10,'[2]Breakdown from VHM BOQ'!L10,"")</f>
         <v>70</v>
       </c>
       <c r="H9" s="11">
@@ -12638,7 +12635,7 @@
         <v>16</v>
       </c>
       <c r="G10" s="10">
-        <f>IF(B10='[1]Breakdown from VHM BOQ'!B11,'[1]Breakdown from VHM BOQ'!L11,"")</f>
+        <f>IF(B10='[2]Breakdown from VHM BOQ'!B11,'[2]Breakdown from VHM BOQ'!L11,"")</f>
         <v>5648000</v>
       </c>
       <c r="H10" s="11">
@@ -12717,7 +12714,7 @@
         <v>16</v>
       </c>
       <c r="G14" s="10">
-        <f>IF(B14='[1]Breakdown from VHM BOQ'!B15,'[1]Breakdown from VHM BOQ'!L15,"")</f>
+        <f>IF(B14='[2]Breakdown from VHM BOQ'!B15,'[2]Breakdown from VHM BOQ'!L15,"")</f>
         <v>126100</v>
       </c>
       <c r="H14" s="11">
@@ -12746,7 +12743,7 @@
         <v>16</v>
       </c>
       <c r="G15" s="10">
-        <f>IF(B15='[1]Breakdown from VHM BOQ'!B18,'[1]Breakdown from VHM BOQ'!L18,"")</f>
+        <f>IF(B15='[2]Breakdown from VHM BOQ'!B18,'[2]Breakdown from VHM BOQ'!L18,"")</f>
         <v>120000</v>
       </c>
       <c r="H15" s="11">
@@ -12773,7 +12770,7 @@
         <v>16</v>
       </c>
       <c r="G16" s="10">
-        <f>IF(B16='[1]Breakdown from VHM BOQ'!B19,'[1]Breakdown from VHM BOQ'!L19,"")</f>
+        <f>IF(B16='[2]Breakdown from VHM BOQ'!B19,'[2]Breakdown from VHM BOQ'!L19,"")</f>
         <v>14550</v>
       </c>
       <c r="H16" s="11">
@@ -12802,7 +12799,7 @@
         <v>16</v>
       </c>
       <c r="G17" s="10">
-        <f>IF(B17='[1]Breakdown from VHM BOQ'!B20,'[1]Breakdown from VHM BOQ'!L20,"")</f>
+        <f>IF(B17='[2]Breakdown from VHM BOQ'!B20,'[2]Breakdown from VHM BOQ'!L20,"")</f>
         <v>1212500</v>
       </c>
       <c r="H17" s="11">
@@ -12831,7 +12828,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="10">
-        <f>IF(B18='[1]Breakdown from VHM BOQ'!B21,'[1]Breakdown from VHM BOQ'!L21,"")</f>
+        <f>IF(B18='[2]Breakdown from VHM BOQ'!B21,'[2]Breakdown from VHM BOQ'!L21,"")</f>
         <v>1746000</v>
       </c>
       <c r="H18" s="11">
@@ -12860,7 +12857,7 @@
         <v>16</v>
       </c>
       <c r="G19" s="10">
-        <f>IF(B19='[1]Breakdown from VHM BOQ'!B22,'[1]Breakdown from VHM BOQ'!L22,"")</f>
+        <f>IF(B19='[2]Breakdown from VHM BOQ'!B22,'[2]Breakdown from VHM BOQ'!L22,"")</f>
         <v>294000</v>
       </c>
       <c r="H19" s="11">
@@ -12888,7 +12885,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="10">
-        <f>IF(B20='[1]Breakdown from VHM BOQ'!B23,'[1]Breakdown from VHM BOQ'!L23,"")</f>
+        <f>IF(B20='[2]Breakdown from VHM BOQ'!B23,'[2]Breakdown from VHM BOQ'!L23,"")</f>
         <v>302640</v>
       </c>
       <c r="H20" s="11">
@@ -12916,7 +12913,7 @@
         <v>16</v>
       </c>
       <c r="G21" s="10">
-        <f>IF(B21='[1]Breakdown from VHM BOQ'!B24,'[1]Breakdown from VHM BOQ'!L24,"")</f>
+        <f>IF(B21='[2]Breakdown from VHM BOQ'!B24,'[2]Breakdown from VHM BOQ'!L24,"")</f>
         <v>33950</v>
       </c>
       <c r="H21" s="11">
@@ -12945,7 +12942,7 @@
         <v>16</v>
       </c>
       <c r="G22" s="10">
-        <f>IF(B22='[1]Breakdown from VHM BOQ'!B25,'[1]Breakdown from VHM BOQ'!L25,"")</f>
+        <f>IF(B22='[2]Breakdown from VHM BOQ'!B25,'[2]Breakdown from VHM BOQ'!L25,"")</f>
         <v>82450</v>
       </c>
       <c r="H22" s="11">
@@ -12974,7 +12971,7 @@
         <v>16</v>
       </c>
       <c r="G23" s="10">
-        <f>IF(B23='[1]Breakdown from VHM BOQ'!B26,'[1]Breakdown from VHM BOQ'!L26,"")</f>
+        <f>IF(B23='[2]Breakdown from VHM BOQ'!B26,'[2]Breakdown from VHM BOQ'!L26,"")</f>
         <v>92000</v>
       </c>
       <c r="H23" s="11">
@@ -13019,7 +13016,7 @@
         <v>16</v>
       </c>
       <c r="G25" s="10">
-        <f>IF(B25='[1]Breakdown from VHM BOQ'!B28,'[1]Breakdown from VHM BOQ'!L28,"")</f>
+        <f>IF(B25='[2]Breakdown from VHM BOQ'!B28,'[2]Breakdown from VHM BOQ'!L28,"")</f>
         <v>126100</v>
       </c>
       <c r="H25" s="11">
@@ -13047,7 +13044,7 @@
         <v>16</v>
       </c>
       <c r="G26" s="10">
-        <f>IF(B26='[1]Breakdown from VHM BOQ'!B31,'[1]Breakdown from VHM BOQ'!L31,"")</f>
+        <f>IF(B26='[2]Breakdown from VHM BOQ'!B31,'[2]Breakdown from VHM BOQ'!L31,"")</f>
         <v>120000</v>
       </c>
       <c r="H26" s="11">
@@ -13075,7 +13072,7 @@
         <v>16</v>
       </c>
       <c r="G27" s="10">
-        <f>IF(B27='[1]Breakdown from VHM BOQ'!B32,'[1]Breakdown from VHM BOQ'!L32,"")</f>
+        <f>IF(B27='[2]Breakdown from VHM BOQ'!B32,'[2]Breakdown from VHM BOQ'!L32,"")</f>
         <v>1212500</v>
       </c>
       <c r="H27" s="11">
@@ -13103,7 +13100,7 @@
         <v>16</v>
       </c>
       <c r="G28" s="10">
-        <f>IF(B28='[1]Breakdown from VHM BOQ'!B33,'[1]Breakdown from VHM BOQ'!L33,"")</f>
+        <f>IF(B28='[2]Breakdown from VHM BOQ'!B33,'[2]Breakdown from VHM BOQ'!L33,"")</f>
         <v>1746000</v>
       </c>
       <c r="H28" s="11">
@@ -13131,7 +13128,7 @@
         <v>16</v>
       </c>
       <c r="G29" s="10">
-        <f>IF(B29='[1]Breakdown from VHM BOQ'!B34,'[1]Breakdown from VHM BOQ'!L34,"")</f>
+        <f>IF(B29='[2]Breakdown from VHM BOQ'!B34,'[2]Breakdown from VHM BOQ'!L34,"")</f>
         <v>294000</v>
       </c>
       <c r="H29" s="11">
@@ -13159,7 +13156,7 @@
         <v>16</v>
       </c>
       <c r="G30" s="10">
-        <f>IF(B30='[1]Breakdown from VHM BOQ'!B35,'[1]Breakdown from VHM BOQ'!L35,"")</f>
+        <f>IF(B30='[2]Breakdown from VHM BOQ'!B35,'[2]Breakdown from VHM BOQ'!L35,"")</f>
         <v>302640</v>
       </c>
       <c r="H30" s="11">
@@ -13187,7 +13184,7 @@
         <v>16</v>
       </c>
       <c r="G31" s="10">
-        <f>IF(B31='[1]Breakdown from VHM BOQ'!B36,'[1]Breakdown from VHM BOQ'!L36,"")</f>
+        <f>IF(B31='[2]Breakdown from VHM BOQ'!B36,'[2]Breakdown from VHM BOQ'!L36,"")</f>
         <v>33950</v>
       </c>
       <c r="H31" s="11">
@@ -13215,7 +13212,7 @@
         <v>16</v>
       </c>
       <c r="G32" s="10">
-        <f>IF(B32='[1]Breakdown from VHM BOQ'!B37,'[1]Breakdown from VHM BOQ'!L37,"")</f>
+        <f>IF(B32='[2]Breakdown from VHM BOQ'!B37,'[2]Breakdown from VHM BOQ'!L37,"")</f>
         <v>82450</v>
       </c>
       <c r="H32" s="11">
@@ -13243,7 +13240,7 @@
         <v>16</v>
       </c>
       <c r="G33" s="10">
-        <f>IF(B33='[1]Breakdown from VHM BOQ'!B38,'[1]Breakdown from VHM BOQ'!L38,"")</f>
+        <f>IF(B33='[2]Breakdown from VHM BOQ'!B38,'[2]Breakdown from VHM BOQ'!L38,"")</f>
         <v>92000</v>
       </c>
       <c r="H33" s="11">
@@ -13288,7 +13285,7 @@
         <v>16</v>
       </c>
       <c r="G35" s="10">
-        <f>IF(B35='[1]Breakdown from VHM BOQ'!B40,'[1]Breakdown from VHM BOQ'!L40,"")</f>
+        <f>IF(B35='[2]Breakdown from VHM BOQ'!B40,'[2]Breakdown from VHM BOQ'!L40,"")</f>
         <v>48500</v>
       </c>
       <c r="H35" s="11">
@@ -13316,7 +13313,7 @@
         <v>16</v>
       </c>
       <c r="G36" s="10">
-        <f>IF(B36='[1]Breakdown from VHM BOQ'!B41,'[1]Breakdown from VHM BOQ'!L41,"")</f>
+        <f>IF(B36='[2]Breakdown from VHM BOQ'!B41,'[2]Breakdown from VHM BOQ'!L41,"")</f>
         <v>213400</v>
       </c>
       <c r="H36" s="11">
@@ -13359,7 +13356,7 @@
         <v>16</v>
       </c>
       <c r="G38" s="10">
-        <f>IF(B38='[1]Breakdown from VHM BOQ'!B43,'[1]Breakdown from VHM BOQ'!L43,"")</f>
+        <f>IF(B38='[2]Breakdown from VHM BOQ'!B43,'[2]Breakdown from VHM BOQ'!L43,"")</f>
         <v>1420000</v>
       </c>
       <c r="H38" s="11">
@@ -13387,7 +13384,7 @@
         <v>16</v>
       </c>
       <c r="G39" s="10">
-        <f>IF(B39='[1]Breakdown from VHM BOQ'!B44,'[1]Breakdown from VHM BOQ'!L44,"")</f>
+        <f>IF(B39='[2]Breakdown from VHM BOQ'!B44,'[2]Breakdown from VHM BOQ'!L44,"")</f>
         <v>913594.49999999988</v>
       </c>
       <c r="H39" s="11">
@@ -13430,7 +13427,7 @@
         <v>64</v>
       </c>
       <c r="G41" s="10">
-        <f>IF(B41='[1]Breakdown from VHM BOQ'!B49,'[1]Breakdown from VHM BOQ'!L49,"")</f>
+        <f>IF(B41='[2]Breakdown from VHM BOQ'!B49,'[2]Breakdown from VHM BOQ'!L49,"")</f>
         <v>10670000</v>
       </c>
       <c r="H41" s="11">
@@ -13515,7 +13512,7 @@
         <v>16</v>
       </c>
       <c r="G45" s="10">
-        <f>IF(B45='[1]Breakdown from VHM BOQ'!B55,'[1]Breakdown from VHM BOQ'!L55,"")</f>
+        <f>IF(B45='[2]Breakdown from VHM BOQ'!B55,'[2]Breakdown from VHM BOQ'!L55,"")</f>
         <v>5820000</v>
       </c>
       <c r="H45" s="11">
@@ -13541,7 +13538,7 @@
         <v>16</v>
       </c>
       <c r="G46" s="10">
-        <f>IF(B46='[1]Breakdown from VHM BOQ'!B58,'[1]Breakdown from VHM BOQ'!L58,"")</f>
+        <f>IF(B46='[2]Breakdown from VHM BOQ'!B58,'[2]Breakdown from VHM BOQ'!L58,"")</f>
         <v>100000</v>
       </c>
       <c r="H46" s="11">
@@ -13584,7 +13581,7 @@
         <v>76</v>
       </c>
       <c r="G48" s="10">
-        <f>IF(B48='[1]Breakdown from VHM BOQ'!B66,'[1]Breakdown from VHM BOQ'!L66,"")</f>
+        <f>IF(B48='[2]Breakdown from VHM BOQ'!B66,'[2]Breakdown from VHM BOQ'!L66,"")</f>
         <v>265438.92375000002</v>
       </c>
       <c r="H48" s="11">
@@ -13610,7 +13607,7 @@
         <v>76</v>
       </c>
       <c r="G49" s="10">
-        <f>IF(B49='[1]Breakdown from VHM BOQ'!B67,'[1]Breakdown from VHM BOQ'!L67,"")</f>
+        <f>IF(B49='[2]Breakdown from VHM BOQ'!B67,'[2]Breakdown from VHM BOQ'!L67,"")</f>
         <v>265438.92375000002</v>
       </c>
       <c r="H49" s="11">
@@ -13636,7 +13633,7 @@
         <v>76</v>
       </c>
       <c r="G50" s="10">
-        <f>IF(B50='[1]Breakdown from VHM BOQ'!B68,'[1]Breakdown from VHM BOQ'!L68,"")</f>
+        <f>IF(B50='[2]Breakdown from VHM BOQ'!B68,'[2]Breakdown from VHM BOQ'!L68,"")</f>
         <v>55500</v>
       </c>
       <c r="H50" s="11">
@@ -13688,7 +13685,7 @@
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="10">
-        <f>IF(B52='[1]Breakdown from VHM BOQ'!B76,'[1]Breakdown from VHM BOQ'!L76,"")</f>
+        <f>IF(B52='[2]Breakdown from VHM BOQ'!B76,'[2]Breakdown from VHM BOQ'!L76,"")</f>
         <v>116400</v>
       </c>
       <c r="H52" s="11">
@@ -13715,7 +13712,7 @@
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="10">
-        <f>IF(B53='[1]Breakdown from VHM BOQ'!B77,'[1]Breakdown from VHM BOQ'!L77,"")</f>
+        <f>IF(B53='[2]Breakdown from VHM BOQ'!B77,'[2]Breakdown from VHM BOQ'!L77,"")</f>
         <v>140650</v>
       </c>
       <c r="H53" s="11">
@@ -13740,7 +13737,7 @@
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="10">
-        <f>IF(B54='[1]Breakdown from VHM BOQ'!B78,'[1]Breakdown from VHM BOQ'!L78,"")</f>
+        <f>IF(B54='[2]Breakdown from VHM BOQ'!B78,'[2]Breakdown from VHM BOQ'!L78,"")</f>
         <v>14550</v>
       </c>
       <c r="H54" s="11">
@@ -13766,7 +13763,7 @@
         <v>16</v>
       </c>
       <c r="G55" s="10">
-        <f>IF(B55='[1]Breakdown from VHM BOQ'!B79,'[1]Breakdown from VHM BOQ'!L79,"")</f>
+        <f>IF(B55='[2]Breakdown from VHM BOQ'!B79,'[2]Breakdown from VHM BOQ'!L79,"")</f>
         <v>339500</v>
       </c>
       <c r="H55" s="11">
@@ -13788,7 +13785,7 @@
       <c r="E56" s="52"/>
       <c r="F56" s="53"/>
       <c r="G56" s="58">
-        <f>IF(B56='[1]Breakdown from VHM BOQ'!B80,'[1]Breakdown from VHM BOQ'!L80,"")</f>
+        <f>IF(B56='[2]Breakdown from VHM BOQ'!B80,'[2]Breakdown from VHM BOQ'!L80,"")</f>
         <v>1000000</v>
       </c>
       <c r="H56" s="51">
@@ -13846,630 +13843,636 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="18.5">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="162"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
     </row>
     <row r="3" spans="1:7" ht="14.5">
-      <c r="A3" s="109" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
+      <c r="A3" s="108" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
     </row>
     <row r="4" spans="1:7" ht="14.5">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="162"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
+      <c r="B4" s="152"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
     </row>
     <row r="5" spans="1:7" ht="14.5">
-      <c r="A5" s="111"/>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
+      <c r="A5" s="110"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A6" s="110"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="164" t="s">
+      <c r="A6" s="109"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="154" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="165"/>
-      <c r="G6" s="166"/>
+      <c r="F6" s="155"/>
+      <c r="G6" s="156"/>
     </row>
     <row r="7" spans="1:7" ht="14.5">
-      <c r="A7" s="107" t="s">
+      <c r="A7" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="107" t="s">
+      <c r="B7" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="167" t="s">
+      <c r="C7" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="168"/>
-      <c r="E7" s="107" t="s">
+      <c r="D7" s="158"/>
+      <c r="E7" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="106" t="s">
+      <c r="F7" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="106" t="s">
+      <c r="G7" s="105" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.5">
-      <c r="A8" s="100" t="s">
+      <c r="A8" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="99" t="s">
+      <c r="B8" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="100">
-        <v>1</v>
-      </c>
-      <c r="D8" s="100" t="s">
+      <c r="C8" s="99">
+        <v>1</v>
+      </c>
+      <c r="D8" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="100"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96">
+      <c r="E8" s="99"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95">
         <f>SUM(G9:G12)</f>
         <v>3300000</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.5">
-      <c r="A9" s="76">
-        <v>1</v>
-      </c>
-      <c r="B9" s="79" t="s">
+      <c r="A9" s="75">
+        <v>1</v>
+      </c>
+      <c r="B9" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="76">
+      <c r="C9" s="75">
         <v>7700</v>
       </c>
-      <c r="D9" s="76" t="s">
+      <c r="D9" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="76"/>
-      <c r="F9" s="72">
+      <c r="E9" s="75"/>
+      <c r="F9" s="71">
         <v>86</v>
       </c>
-      <c r="G9" s="72">
+      <c r="G9" s="71">
         <f>C9*F9</f>
         <v>662200</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.5">
-      <c r="A10" s="76">
+      <c r="A10" s="75">
         <v>2</v>
       </c>
-      <c r="B10" s="79" t="s">
+      <c r="B10" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="76">
+      <c r="C10" s="75">
         <v>7700</v>
       </c>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="76"/>
-      <c r="F10" s="72">
+      <c r="E10" s="75"/>
+      <c r="F10" s="71">
         <v>86</v>
       </c>
-      <c r="G10" s="72">
+      <c r="G10" s="71">
         <f>C10*F10</f>
         <v>662200</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.5">
-      <c r="A11" s="76">
+      <c r="A11" s="75">
         <v>3</v>
       </c>
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="76">
-        <v>1</v>
-      </c>
-      <c r="D11" s="76" t="s">
+      <c r="C11" s="75">
+        <v>1</v>
+      </c>
+      <c r="D11" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="76"/>
-      <c r="F11" s="72">
+      <c r="E11" s="75"/>
+      <c r="F11" s="71">
         <v>2300000</v>
       </c>
-      <c r="G11" s="72">
+      <c r="G11" s="71">
         <f>C11*F11</f>
         <v>2300000</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.5">
-      <c r="A12" s="76"/>
-      <c r="B12" s="105" t="s">
+      <c r="A12" s="75"/>
+      <c r="B12" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="104">
-        <v>1</v>
-      </c>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="103">
+      <c r="C12" s="103">
+        <v>1</v>
+      </c>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="102">
         <v>-324400</v>
       </c>
-      <c r="G12" s="103">
+      <c r="G12" s="102">
         <f>F12*C12</f>
         <v>-324400</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.5">
-      <c r="A13" s="100" t="s">
+      <c r="A13" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="99" t="s">
+      <c r="B13" s="98" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="98">
-        <v>1</v>
-      </c>
-      <c r="D13" s="98" t="s">
+      <c r="C13" s="97">
+        <v>1</v>
+      </c>
+      <c r="D13" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="98"/>
-      <c r="F13" s="97"/>
-      <c r="G13" s="96">
+      <c r="E13" s="97"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="95">
         <f>SUM(G14:G15)</f>
         <v>1050000</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.5">
-      <c r="A14" s="76">
-        <v>1</v>
-      </c>
-      <c r="B14" s="77" t="s">
+      <c r="A14" s="75">
+        <v>1</v>
+      </c>
+      <c r="B14" s="76" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="76">
-        <v>1</v>
-      </c>
-      <c r="D14" s="76" t="s">
+      <c r="C14" s="75">
+        <v>1</v>
+      </c>
+      <c r="D14" s="75" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="76" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="72">
+      <c r="E14" s="75" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="71">
         <v>250000</v>
       </c>
-      <c r="G14" s="72">
+      <c r="G14" s="71">
         <f>C14*F14</f>
         <v>250000</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.5">
-      <c r="A15" s="76">
+      <c r="A15" s="75">
         <v>2</v>
       </c>
-      <c r="B15" s="79" t="s">
+      <c r="B15" s="78" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="76">
-        <v>1</v>
-      </c>
-      <c r="D15" s="76" t="s">
+      <c r="C15" s="75">
+        <v>1</v>
+      </c>
+      <c r="D15" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="76" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="72">
+      <c r="E15" s="75" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="71">
         <v>800000</v>
       </c>
-      <c r="G15" s="72">
+      <c r="G15" s="71">
         <f>C15*F15</f>
         <v>800000</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.5">
-      <c r="A16" s="76"/>
-      <c r="B16" s="79"/>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="72"/>
+      <c r="A16" s="75"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
     </row>
     <row r="17" spans="1:8" ht="14.5">
-      <c r="A17" s="100" t="s">
+      <c r="A17" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="99" t="s">
+      <c r="B17" s="98" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="97"/>
-      <c r="G17" s="96">
+      <c r="C17" s="97"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="97"/>
+      <c r="F17" s="96"/>
+      <c r="G17" s="95">
         <f>SUM(G18)</f>
         <v>1500000</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="14.5">
-      <c r="A18" s="76">
-        <v>1</v>
-      </c>
-      <c r="B18" s="79" t="s">
+      <c r="A18" s="75">
+        <v>1</v>
+      </c>
+      <c r="B18" s="78" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="76">
-        <v>1</v>
-      </c>
-      <c r="D18" s="76" t="s">
+      <c r="C18" s="75">
+        <v>1</v>
+      </c>
+      <c r="D18" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="F18" s="72">
+      <c r="F18" s="71">
         <v>1500000</v>
       </c>
-      <c r="G18" s="72">
+      <c r="G18" s="71">
         <f>C18*F18</f>
         <v>1500000</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="102"/>
-      <c r="B19" s="101"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="99" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="99" t="s">
+      <c r="B20" s="98" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="98"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="96">
+      <c r="C20" s="97"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="95">
         <f>SUM(G21:G25)</f>
         <v>4475000</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" s="76">
-        <v>1</v>
-      </c>
-      <c r="B21" s="81" t="s">
+      <c r="A21" s="75">
+        <v>1</v>
+      </c>
+      <c r="B21" s="80" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="76">
+      <c r="C21" s="75">
         <v>15</v>
       </c>
-      <c r="D21" s="76" t="s">
+      <c r="D21" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="94" t="s">
+      <c r="E21" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="94">
         <v>150000</v>
       </c>
-      <c r="G21" s="72">
+      <c r="G21" s="71">
         <f>C21*F21</f>
         <v>2250000</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="76">
+      <c r="A22" s="75">
         <v>2</v>
       </c>
-      <c r="B22" s="79" t="s">
+      <c r="B22" s="78" t="s">
         <v>126</v>
       </c>
-      <c r="C22" s="76">
+      <c r="C22" s="75">
         <v>5</v>
       </c>
-      <c r="D22" s="76" t="s">
+      <c r="D22" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="E22" s="94" t="s">
+      <c r="E22" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="94">
         <v>50000</v>
       </c>
-      <c r="G22" s="72">
+      <c r="G22" s="71">
         <f>C22*F22</f>
         <v>250000</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="76">
+      <c r="A23" s="75">
         <v>3</v>
       </c>
-      <c r="B23" s="79" t="s">
+      <c r="B23" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="76">
+      <c r="C23" s="75">
         <v>15</v>
       </c>
-      <c r="D23" s="76" t="s">
+      <c r="D23" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="94" t="s">
+      <c r="E23" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="F23" s="72">
+      <c r="F23" s="71">
         <v>35000</v>
       </c>
-      <c r="G23" s="72">
+      <c r="G23" s="71">
         <f>C23*F23</f>
         <v>525000</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A24" s="76">
+      <c r="A24" s="75">
         <v>4</v>
       </c>
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="76">
-        <v>1</v>
-      </c>
-      <c r="D24" s="76" t="s">
+      <c r="C24" s="75">
+        <v>1</v>
+      </c>
+      <c r="D24" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="76"/>
-      <c r="F24" s="72">
+      <c r="E24" s="75"/>
+      <c r="F24" s="71">
         <v>1000000</v>
       </c>
-      <c r="G24" s="72">
+      <c r="G24" s="71">
         <f>C24*F24</f>
         <v>1000000</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" s="76">
+      <c r="A25" s="75">
         <v>5</v>
       </c>
-      <c r="B25" s="79" t="s">
+      <c r="B25" s="78" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="76">
+      <c r="C25" s="75">
         <v>15</v>
       </c>
-      <c r="D25" s="76" t="s">
+      <c r="D25" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="76" t="s">
+      <c r="E25" s="75" t="s">
         <v>129</v>
       </c>
-      <c r="F25" s="72">
+      <c r="F25" s="71">
         <v>30000</v>
       </c>
-      <c r="G25" s="72">
+      <c r="G25" s="71">
         <f>C25*F25</f>
         <v>450000</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A26" s="79"/>
-      <c r="B26" s="93"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="72"/>
+      <c r="A26" s="78"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="71"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="90" t="s">
+      <c r="B27" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="86">
-        <v>1</v>
-      </c>
-      <c r="D27" s="86" t="s">
+      <c r="C27" s="85">
+        <v>1</v>
+      </c>
+      <c r="D27" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="86"/>
-      <c r="F27" s="89">
+      <c r="E27" s="85"/>
+      <c r="F27" s="88">
         <v>500000</v>
       </c>
-      <c r="G27" s="83">
+      <c r="G27" s="82">
         <f>C27*F27</f>
         <v>500000</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A28" s="88" t="s">
+      <c r="A28" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="87" t="s">
+      <c r="B28" s="86" t="s">
         <v>130</v>
       </c>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="83">
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="82">
         <f>SUM(G29:G34)</f>
-        <v>472750</v>
+        <v>472528</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A29" s="76">
-        <v>1</v>
-      </c>
-      <c r="B29" s="82" t="s">
+      <c r="A29" s="75">
+        <v>1</v>
+      </c>
+      <c r="B29" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="C29" s="81">
+      <c r="C29" s="80">
         <v>0.62</v>
       </c>
-      <c r="D29" s="80" t="s">
+      <c r="D29" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="E29" s="80" t="s">
+      <c r="E29" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="F29" s="72">
+      <c r="F29" s="71">
         <v>69500</v>
       </c>
-      <c r="G29" s="72">
-        <v>43750</v>
+      <c r="G29" s="71">
+        <f>C29*F29</f>
+        <v>43090</v>
       </c>
       <c r="H29" s="68"/>
     </row>
     <row r="30" spans="1:8" ht="37.5" customHeight="1">
-      <c r="A30" s="76">
+      <c r="A30" s="75">
         <v>2</v>
       </c>
-      <c r="B30" s="77" t="s">
+      <c r="B30" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="D30" s="76" t="s">
+      <c r="D30" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="76" t="s">
+      <c r="E30" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="72">
+      <c r="F30" s="71">
         <v>1700000</v>
       </c>
-      <c r="G30" s="72">
+      <c r="G30" s="71">
+        <f t="shared" ref="G30:G34" si="0">C30*F30</f>
         <v>136000</v>
       </c>
       <c r="H30" s="68"/>
     </row>
     <row r="31" spans="1:8" ht="41.5" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="75">
         <v>3</v>
       </c>
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="D31" s="76" t="s">
+      <c r="D31" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="E31" s="76" t="s">
+      <c r="E31" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F31" s="72">
+      <c r="F31" s="71">
         <v>292100</v>
       </c>
-      <c r="G31" s="72">
-        <v>111000</v>
+      <c r="G31" s="71">
+        <f t="shared" si="0"/>
+        <v>110998</v>
       </c>
       <c r="H31" s="68"/>
     </row>
     <row r="32" spans="1:8" ht="40.5" customHeight="1">
-      <c r="A32" s="76">
+      <c r="A32" s="75">
         <v>4</v>
       </c>
-      <c r="B32" s="77" t="s">
+      <c r="B32" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="C32" s="79" t="s">
-        <v>139</v>
-      </c>
-      <c r="D32" s="78" t="s">
+      <c r="C32" s="78">
+        <v>1.6</v>
+      </c>
+      <c r="D32" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="78" t="s">
+      <c r="E32" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="F32" s="72">
+      <c r="F32" s="71">
         <v>23400</v>
       </c>
-      <c r="G32" s="72">
-        <v>37000</v>
+      <c r="G32" s="71">
+        <f t="shared" si="0"/>
+        <v>37440</v>
       </c>
       <c r="H32" s="68"/>
     </row>
     <row r="33" spans="1:8" ht="21" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="75">
         <v>5</v>
       </c>
-      <c r="B33" s="77" t="s">
+      <c r="B33" s="76" t="s">
         <v>140</v>
       </c>
-      <c r="C33" s="76">
-        <v>1</v>
-      </c>
-      <c r="D33" s="76" t="s">
+      <c r="C33" s="75">
+        <v>1</v>
+      </c>
+      <c r="D33" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="76" t="s">
+      <c r="E33" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F33" s="72">
+      <c r="F33" s="71">
         <v>63000</v>
       </c>
-      <c r="G33" s="72">
+      <c r="G33" s="71">
+        <f t="shared" si="0"/>
         <v>63000</v>
       </c>
       <c r="H33" s="68"/>
     </row>
     <row r="34" spans="1:8" ht="35.5" customHeight="1">
-      <c r="A34" s="75">
+      <c r="A34" s="74">
         <v>6</v>
       </c>
-      <c r="B34" s="74" t="s">
+      <c r="B34" s="73" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="73">
-        <v>1</v>
-      </c>
-      <c r="D34" s="73" t="s">
+      <c r="C34" s="72">
+        <v>1</v>
+      </c>
+      <c r="D34" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="73" t="s">
+      <c r="E34" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="F34" s="72">
+      <c r="F34" s="71">
         <v>82000</v>
       </c>
       <c r="G34" s="71">
+        <f t="shared" si="0"/>
         <v>82000</v>
       </c>
       <c r="H34" s="68"/>
@@ -14478,14 +14481,14 @@
       <c r="A35" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="158"/>
-      <c r="C35" s="159"/>
-      <c r="D35" s="159"/>
-      <c r="E35" s="159"/>
-      <c r="F35" s="160"/>
+      <c r="B35" s="148"/>
+      <c r="C35" s="149"/>
+      <c r="D35" s="149"/>
+      <c r="E35" s="149"/>
+      <c r="F35" s="150"/>
       <c r="G35" s="69">
         <f>SUM(G8,G13,G17,G20,G27,G28)</f>
-        <v>11297750</v>
+        <v>11297528</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1">
@@ -14569,647 +14572,647 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="14.5">
-      <c r="A1" s="140"/>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
+      <c r="A1" s="139"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
     </row>
     <row r="2" spans="1:13" ht="18.5">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="151" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="162"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1">
-      <c r="A3" s="109" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
+      <c r="A3" s="108" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="162"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
+      <c r="B4" s="152"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
     </row>
     <row r="5" spans="1:13" ht="14.5">
-      <c r="A5" s="111"/>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
+      <c r="A5" s="110"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
     </row>
     <row r="6" spans="1:13" ht="16.5" thickBot="1">
-      <c r="A6" s="110"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="169" t="s">
+      <c r="A6" s="109"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="168" t="s">
         <v>155</v>
       </c>
-      <c r="F6" s="162"/>
-      <c r="G6" s="170"/>
+      <c r="F6" s="152"/>
+      <c r="G6" s="169"/>
     </row>
     <row r="7" spans="1:13" ht="14.5">
-      <c r="A7" s="139" t="s">
+      <c r="A7" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="138" t="s">
+      <c r="B7" s="137" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="171" t="s">
+      <c r="C7" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="172"/>
-      <c r="E7" s="137" t="s">
+      <c r="D7" s="171"/>
+      <c r="E7" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="136" t="s">
+      <c r="F7" s="135" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="135" t="s">
+      <c r="G7" s="134" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="14.5">
-      <c r="A8" s="133" t="s">
+      <c r="A8" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="134" t="s">
+      <c r="B8" s="133" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="133">
-        <v>1</v>
-      </c>
-      <c r="D8" s="133" t="s">
+      <c r="C8" s="132">
+        <v>1</v>
+      </c>
+      <c r="D8" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="133"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132">
+      <c r="E8" s="132"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="131">
         <f>SUM(G9:G12)</f>
         <v>3300000</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="14.5">
-      <c r="A9" s="80">
-        <v>1</v>
-      </c>
-      <c r="B9" s="81" t="s">
+      <c r="A9" s="79">
+        <v>1</v>
+      </c>
+      <c r="B9" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="80">
+      <c r="C9" s="79">
         <v>11000</v>
       </c>
-      <c r="D9" s="80" t="s">
+      <c r="D9" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="80"/>
-      <c r="F9" s="95">
+      <c r="E9" s="79"/>
+      <c r="F9" s="94">
         <v>73</v>
       </c>
-      <c r="G9" s="95">
+      <c r="G9" s="94">
         <f>C9*F9</f>
         <v>803000</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="14.5">
-      <c r="A10" s="80">
+      <c r="A10" s="79">
         <v>2</v>
       </c>
-      <c r="B10" s="81" t="s">
+      <c r="B10" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="80">
+      <c r="C10" s="79">
         <v>11000</v>
       </c>
-      <c r="D10" s="80" t="s">
+      <c r="D10" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="80"/>
-      <c r="F10" s="95">
+      <c r="E10" s="79"/>
+      <c r="F10" s="94">
         <v>73</v>
       </c>
-      <c r="G10" s="95">
+      <c r="G10" s="94">
         <f>C10*F10</f>
         <v>803000</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="14.5">
-      <c r="A11" s="80">
+      <c r="A11" s="79">
         <v>3</v>
       </c>
-      <c r="B11" s="81" t="s">
+      <c r="B11" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="80">
-        <v>1</v>
-      </c>
-      <c r="D11" s="80" t="s">
+      <c r="C11" s="79">
+        <v>1</v>
+      </c>
+      <c r="D11" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="95">
+      <c r="E11" s="79"/>
+      <c r="F11" s="94">
         <v>2300000</v>
       </c>
-      <c r="G11" s="95">
+      <c r="G11" s="94">
         <f>C11*F11</f>
         <v>2300000</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="14.5">
-      <c r="A12" s="80"/>
-      <c r="B12" s="105" t="s">
+      <c r="A12" s="79"/>
+      <c r="B12" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="104">
-        <v>1</v>
-      </c>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="103">
+      <c r="C12" s="103">
+        <v>1</v>
+      </c>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="102">
         <v>-606000</v>
       </c>
-      <c r="G12" s="103">
+      <c r="G12" s="102">
         <f>F12*C12</f>
         <v>-606000</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="14.5">
-      <c r="A13" s="127" t="s">
+      <c r="A13" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="130" t="s">
+      <c r="B13" s="129" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="125">
-        <v>1</v>
-      </c>
-      <c r="D13" s="125" t="s">
+      <c r="C13" s="124">
+        <v>1</v>
+      </c>
+      <c r="D13" s="124" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="125"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="123">
+      <c r="E13" s="124"/>
+      <c r="F13" s="123"/>
+      <c r="G13" s="122">
         <f>SUM(G14:G15)</f>
         <v>1150000</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="14.5">
-      <c r="A14" s="80">
-        <v>1</v>
-      </c>
-      <c r="B14" s="82" t="s">
+      <c r="A14" s="79">
+        <v>1</v>
+      </c>
+      <c r="B14" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="80">
-        <v>1</v>
-      </c>
-      <c r="D14" s="80" t="s">
+      <c r="C14" s="79">
+        <v>1</v>
+      </c>
+      <c r="D14" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="80" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="95">
+      <c r="E14" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="94">
         <v>250000</v>
       </c>
-      <c r="G14" s="95">
+      <c r="G14" s="94">
         <f>C14*F14</f>
         <v>250000</v>
       </c>
-      <c r="M14" s="131"/>
+      <c r="M14" s="130"/>
     </row>
     <row r="15" spans="1:13" ht="14.5">
-      <c r="A15" s="80">
+      <c r="A15" s="79">
         <v>2</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="80">
-        <v>1</v>
-      </c>
-      <c r="D15" s="80" t="s">
+      <c r="C15" s="79">
+        <v>1</v>
+      </c>
+      <c r="D15" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="80" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="95">
+      <c r="E15" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="94">
         <v>900000</v>
       </c>
-      <c r="G15" s="95">
+      <c r="G15" s="94">
         <f>C15*F15</f>
         <v>900000</v>
       </c>
-      <c r="M15" s="131"/>
+      <c r="M15" s="130"/>
     </row>
     <row r="16" spans="1:13" ht="14.5">
-      <c r="A16" s="80"/>
-      <c r="B16" s="81"/>
-      <c r="C16" s="80" t="s">
+      <c r="A16" s="79"/>
+      <c r="B16" s="80"/>
+      <c r="C16" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="M16" s="131"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="94"/>
+      <c r="M16" s="130"/>
     </row>
     <row r="17" spans="1:7" ht="14.5">
-      <c r="A17" s="127" t="s">
+      <c r="A17" s="126" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="130" t="s">
+      <c r="B17" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="125" t="s">
+      <c r="C17" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="125"/>
-      <c r="E17" s="125"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="123">
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="123"/>
+      <c r="G17" s="122">
         <f>SUM(G18)</f>
         <v>1700000</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="14.5">
-      <c r="A18" s="80">
-        <v>1</v>
-      </c>
-      <c r="B18" s="81" t="s">
+      <c r="A18" s="79">
+        <v>1</v>
+      </c>
+      <c r="B18" s="80" t="s">
         <v>145</v>
       </c>
-      <c r="C18" s="80">
-        <v>1</v>
-      </c>
-      <c r="D18" s="80" t="s">
+      <c r="C18" s="79">
+        <v>1</v>
+      </c>
+      <c r="D18" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="80" t="s">
+      <c r="E18" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="94">
         <v>1700000</v>
       </c>
-      <c r="G18" s="95">
+      <c r="G18" s="94">
         <f>C18*F18</f>
         <v>1700000</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A19" s="129"/>
-      <c r="B19" s="128"/>
-      <c r="C19" s="80" t="s">
+      <c r="A19" s="128"/>
+      <c r="B19" s="127"/>
+      <c r="C19" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A20" s="127" t="s">
+      <c r="A20" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="126" t="s">
+      <c r="B20" s="125" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="125" t="s">
+      <c r="C20" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="124"/>
-      <c r="G20" s="123">
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="122">
         <f>SUM(G21:G25)</f>
         <v>4875000</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A21" s="80">
-        <v>1</v>
-      </c>
-      <c r="B21" s="81" t="s">
+      <c r="A21" s="79">
+        <v>1</v>
+      </c>
+      <c r="B21" s="80" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="80">
+      <c r="C21" s="79">
         <v>15</v>
       </c>
-      <c r="D21" s="80" t="s">
+      <c r="D21" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="122" t="s">
+      <c r="E21" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="94">
         <v>175000</v>
       </c>
-      <c r="G21" s="95">
+      <c r="G21" s="94">
         <f>C21*F21</f>
         <v>2625000</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A22" s="80">
+      <c r="A22" s="79">
         <v>2</v>
       </c>
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="80">
+      <c r="C22" s="79">
         <v>5</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E22" s="122" t="s">
+      <c r="E22" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="94">
         <v>55000</v>
       </c>
-      <c r="G22" s="95">
+      <c r="G22" s="94">
         <f>C22*F22</f>
         <v>275000</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A23" s="80">
+      <c r="A23" s="79">
         <v>3</v>
       </c>
-      <c r="B23" s="79" t="s">
+      <c r="B23" s="78" t="s">
         <v>148</v>
       </c>
-      <c r="C23" s="76">
+      <c r="C23" s="75">
         <v>15</v>
       </c>
-      <c r="D23" s="76" t="s">
+      <c r="D23" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="94" t="s">
+      <c r="E23" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="F23" s="72">
+      <c r="F23" s="71">
         <v>35000</v>
       </c>
-      <c r="G23" s="95">
+      <c r="G23" s="94">
         <f>C23*F23</f>
         <v>525000</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A24" s="80">
+      <c r="A24" s="79">
         <v>4</v>
       </c>
-      <c r="B24" s="81" t="s">
+      <c r="B24" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="76">
-        <v>1</v>
-      </c>
-      <c r="D24" s="76" t="s">
+      <c r="C24" s="75">
+        <v>1</v>
+      </c>
+      <c r="D24" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="76"/>
-      <c r="F24" s="72">
+      <c r="E24" s="75"/>
+      <c r="F24" s="71">
         <v>1000000</v>
       </c>
-      <c r="G24" s="95">
+      <c r="G24" s="94">
         <f>C24*F24</f>
         <v>1000000</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A25" s="80">
+      <c r="A25" s="79">
         <v>5</v>
       </c>
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="80" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="80">
+      <c r="C25" s="79">
         <v>15</v>
       </c>
-      <c r="D25" s="80" t="s">
+      <c r="D25" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="80" t="s">
+      <c r="E25" s="79" t="s">
         <v>129</v>
       </c>
-      <c r="F25" s="95">
+      <c r="F25" s="94">
         <v>30000</v>
       </c>
-      <c r="G25" s="95">
+      <c r="G25" s="94">
         <f>C25*F25</f>
         <v>450000</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A26" s="110"/>
-      <c r="B26" s="121"/>
-      <c r="C26" s="120" t="s">
+      <c r="A26" s="109"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="119" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="120"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="118"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A27" s="118" t="s">
+      <c r="A27" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="117" t="s">
+      <c r="B27" s="116" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="116">
-        <v>1</v>
-      </c>
-      <c r="D27" s="116" t="s">
+      <c r="C27" s="115">
+        <v>1</v>
+      </c>
+      <c r="D27" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="116"/>
-      <c r="F27" s="115">
+      <c r="E27" s="115"/>
+      <c r="F27" s="114">
         <v>500000</v>
       </c>
-      <c r="G27" s="114">
+      <c r="G27" s="113">
         <f>C27*F27</f>
         <v>500000</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A28" s="88" t="s">
+      <c r="A28" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="87" t="s">
+      <c r="B28" s="86" t="s">
         <v>130</v>
       </c>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="83">
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="82">
         <f>SUM(G29:G34)</f>
         <v>472750</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A29" s="76">
-        <v>1</v>
-      </c>
-      <c r="B29" s="82" t="s">
+      <c r="A29" s="75">
+        <v>1</v>
+      </c>
+      <c r="B29" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="C29" s="81" t="s">
+      <c r="C29" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="D29" s="81" t="s">
+      <c r="D29" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="E29" s="80" t="s">
+      <c r="E29" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="F29" s="72">
+      <c r="F29" s="71">
         <v>69500</v>
       </c>
-      <c r="G29" s="72">
+      <c r="G29" s="71">
         <v>43750</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="25.5" customHeight="1">
-      <c r="A30" s="76">
+      <c r="A30" s="75">
         <v>2</v>
       </c>
-      <c r="B30" s="77" t="s">
+      <c r="B30" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="D30" s="79" t="s">
+      <c r="D30" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="76" t="s">
+      <c r="E30" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="72">
+      <c r="F30" s="71">
         <v>1700000</v>
       </c>
-      <c r="G30" s="72">
+      <c r="G30" s="71">
         <v>136000</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="75">
         <v>3</v>
       </c>
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="D31" s="79" t="s">
+      <c r="D31" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="E31" s="76" t="s">
+      <c r="E31" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F31" s="72">
+      <c r="F31" s="71">
         <v>292100</v>
       </c>
-      <c r="G31" s="72">
+      <c r="G31" s="71">
         <v>111000</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="26.5" customHeight="1">
-      <c r="A32" s="76">
+      <c r="A32" s="75">
         <v>4</v>
       </c>
-      <c r="B32" s="77" t="s">
+      <c r="B32" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="C32" s="79" t="s">
+      <c r="C32" s="78" t="s">
         <v>139</v>
       </c>
-      <c r="D32" s="113" t="s">
+      <c r="D32" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="78" t="s">
+      <c r="E32" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="F32" s="72">
+      <c r="F32" s="71">
         <v>23400</v>
       </c>
-      <c r="G32" s="72">
+      <c r="G32" s="71">
         <v>37000</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="32.5" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="75">
         <v>5</v>
       </c>
-      <c r="B33" s="77" t="s">
+      <c r="B33" s="76" t="s">
         <v>140</v>
       </c>
-      <c r="C33" s="76">
-        <v>1</v>
-      </c>
-      <c r="D33" s="79" t="s">
+      <c r="C33" s="75">
+        <v>1</v>
+      </c>
+      <c r="D33" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="76" t="s">
+      <c r="E33" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F33" s="72">
+      <c r="F33" s="71">
         <v>63000</v>
       </c>
-      <c r="G33" s="72">
+      <c r="G33" s="71">
         <v>63000</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="36" customHeight="1">
-      <c r="A34" s="76">
+      <c r="A34" s="75">
         <v>6</v>
       </c>
-      <c r="B34" s="77" t="s">
+      <c r="B34" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="76">
-        <v>1</v>
-      </c>
-      <c r="D34" s="79" t="s">
+      <c r="C34" s="75">
+        <v>1</v>
+      </c>
+      <c r="D34" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="76" t="s">
+      <c r="E34" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F34" s="72">
+      <c r="F34" s="71">
         <v>82000</v>
       </c>
-      <c r="G34" s="72">
+      <c r="G34" s="71">
         <v>82000</v>
       </c>
     </row>
@@ -15217,11 +15220,11 @@
       <c r="A35" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="158"/>
-      <c r="C35" s="159"/>
-      <c r="D35" s="159"/>
-      <c r="E35" s="159"/>
-      <c r="F35" s="160"/>
+      <c r="B35" s="148"/>
+      <c r="C35" s="149"/>
+      <c r="D35" s="149"/>
+      <c r="E35" s="149"/>
+      <c r="F35" s="150"/>
       <c r="G35" s="69">
         <f>SUM(G8,G13,G17,G20,G27,G28)</f>
         <v>11997750</v>
@@ -15312,656 +15315,656 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.5">
-      <c r="A1" s="140"/>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
+      <c r="A1" s="139"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
     </row>
     <row r="2" spans="1:7" ht="18.5">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="162"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1">
-      <c r="A3" s="109" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
+      <c r="A3" s="108" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="162"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
+      <c r="B4" s="152"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
     </row>
     <row r="5" spans="1:7" ht="14.5">
-      <c r="A5" s="111"/>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
+      <c r="A5" s="110"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
     </row>
     <row r="6" spans="1:7" ht="16.5" thickBot="1">
-      <c r="A6" s="110"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="169" t="s">
+      <c r="A6" s="109"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="168" t="s">
         <v>156</v>
       </c>
-      <c r="F6" s="162"/>
-      <c r="G6" s="170"/>
+      <c r="F6" s="152"/>
+      <c r="G6" s="169"/>
     </row>
     <row r="7" spans="1:7" ht="14.5">
-      <c r="A7" s="139" t="s">
+      <c r="A7" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="138" t="s">
+      <c r="B7" s="137" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="171" t="s">
+      <c r="C7" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="172"/>
-      <c r="E7" s="137" t="s">
+      <c r="D7" s="171"/>
+      <c r="E7" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="136" t="s">
+      <c r="F7" s="135" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="135" t="s">
+      <c r="G7" s="134" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.5">
-      <c r="A8" s="133" t="s">
+      <c r="A8" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="134" t="s">
+      <c r="B8" s="133" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="133">
-        <v>1</v>
-      </c>
-      <c r="D8" s="133" t="s">
+      <c r="C8" s="132">
+        <v>1</v>
+      </c>
+      <c r="D8" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="133"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132">
+      <c r="E8" s="132"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="131">
         <f>SUM(G9:G12)</f>
         <v>4000000</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.5">
-      <c r="A9" s="80">
-        <v>1</v>
-      </c>
-      <c r="B9" s="81" t="s">
+      <c r="A9" s="79">
+        <v>1</v>
+      </c>
+      <c r="B9" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="80">
+      <c r="C9" s="79">
         <v>13200</v>
       </c>
-      <c r="D9" s="80" t="s">
+      <c r="D9" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="80"/>
-      <c r="F9" s="95">
+      <c r="E9" s="79"/>
+      <c r="F9" s="94">
         <v>73</v>
       </c>
-      <c r="G9" s="95">
+      <c r="G9" s="94">
         <f>F9*C9</f>
         <v>963600</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.5">
-      <c r="A10" s="80">
+      <c r="A10" s="79">
         <v>2</v>
       </c>
-      <c r="B10" s="81" t="s">
+      <c r="B10" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="80">
+      <c r="C10" s="79">
         <v>13200</v>
       </c>
-      <c r="D10" s="80" t="s">
+      <c r="D10" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="80"/>
-      <c r="F10" s="95">
+      <c r="E10" s="79"/>
+      <c r="F10" s="94">
         <v>73</v>
       </c>
-      <c r="G10" s="95">
+      <c r="G10" s="94">
         <f>F10*C10</f>
         <v>963600</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.5">
-      <c r="A11" s="80">
+      <c r="A11" s="79">
         <v>3</v>
       </c>
-      <c r="B11" s="81" t="s">
+      <c r="B11" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="80">
-        <v>1</v>
-      </c>
-      <c r="D11" s="80" t="s">
+      <c r="C11" s="79">
+        <v>1</v>
+      </c>
+      <c r="D11" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="95">
+      <c r="E11" s="79"/>
+      <c r="F11" s="94">
         <v>2500000</v>
       </c>
-      <c r="G11" s="95">
+      <c r="G11" s="94">
         <f>F11*C11</f>
         <v>2500000</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.5">
-      <c r="A12" s="80"/>
-      <c r="B12" s="105" t="s">
+      <c r="A12" s="79"/>
+      <c r="B12" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="104">
-        <v>1</v>
-      </c>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="103">
+      <c r="C12" s="103">
+        <v>1</v>
+      </c>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="102">
         <v>-427200</v>
       </c>
-      <c r="G12" s="103">
+      <c r="G12" s="102">
         <f>F12*C12</f>
         <v>-427200</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.5">
-      <c r="A13" s="127" t="s">
+      <c r="A13" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="130" t="s">
+      <c r="B13" s="129" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="125">
-        <v>1</v>
-      </c>
-      <c r="D13" s="125" t="s">
+      <c r="C13" s="124">
+        <v>1</v>
+      </c>
+      <c r="D13" s="124" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="125"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="123">
+      <c r="E13" s="124"/>
+      <c r="F13" s="123"/>
+      <c r="G13" s="122">
         <f>SUM(G14:G15)</f>
         <v>1150000</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.5">
-      <c r="A14" s="80">
-        <v>1</v>
-      </c>
-      <c r="B14" s="82" t="s">
+      <c r="A14" s="79">
+        <v>1</v>
+      </c>
+      <c r="B14" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="80">
-        <v>1</v>
-      </c>
-      <c r="D14" s="80" t="s">
+      <c r="C14" s="79">
+        <v>1</v>
+      </c>
+      <c r="D14" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="80" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="95">
+      <c r="E14" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="94">
         <v>250000</v>
       </c>
-      <c r="G14" s="95">
+      <c r="G14" s="94">
         <f>F14*C14</f>
         <v>250000</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.5">
-      <c r="A15" s="80">
+      <c r="A15" s="79">
         <v>2</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="80">
-        <v>1</v>
-      </c>
-      <c r="D15" s="80" t="s">
+      <c r="C15" s="79">
+        <v>1</v>
+      </c>
+      <c r="D15" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="80" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="95">
+      <c r="E15" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="94">
         <v>900000</v>
       </c>
-      <c r="G15" s="95">
+      <c r="G15" s="94">
         <f>F15*C15</f>
         <v>900000</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.5">
-      <c r="A16" s="80"/>
-      <c r="B16" s="81"/>
-      <c r="C16" s="80" t="s">
+      <c r="A16" s="79"/>
+      <c r="B16" s="80"/>
+      <c r="C16" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="94"/>
     </row>
     <row r="17" spans="1:8" ht="14.5">
-      <c r="A17" s="127" t="s">
+      <c r="A17" s="126" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="130" t="s">
+      <c r="B17" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="125" t="s">
+      <c r="C17" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="125"/>
-      <c r="E17" s="125"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="123">
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="123"/>
+      <c r="G17" s="122">
         <f>SUM(G18)</f>
         <v>2000000</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="14.5">
-      <c r="A18" s="80">
-        <v>1</v>
-      </c>
-      <c r="B18" s="81" t="s">
+      <c r="A18" s="79">
+        <v>1</v>
+      </c>
+      <c r="B18" s="80" t="s">
         <v>151</v>
       </c>
-      <c r="C18" s="80">
-        <v>1</v>
-      </c>
-      <c r="D18" s="80" t="s">
+      <c r="C18" s="79">
+        <v>1</v>
+      </c>
+      <c r="D18" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="80" t="s">
+      <c r="E18" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="94">
         <v>2000000</v>
       </c>
-      <c r="G18" s="95">
+      <c r="G18" s="94">
         <f>F18*C18</f>
         <v>2000000</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="129"/>
-      <c r="B19" s="128"/>
-      <c r="C19" s="80" t="s">
+      <c r="A19" s="128"/>
+      <c r="B19" s="127"/>
+      <c r="C19" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A20" s="127" t="s">
+      <c r="A20" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="126" t="s">
+      <c r="B20" s="125" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="125" t="s">
+      <c r="C20" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="124"/>
-      <c r="G20" s="123">
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="122">
         <f>SUM(G21:G25)</f>
         <v>4277500</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="14.5">
-      <c r="A21" s="80">
-        <v>1</v>
-      </c>
-      <c r="B21" s="81" t="s">
+      <c r="A21" s="79">
+        <v>1</v>
+      </c>
+      <c r="B21" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="C21" s="80">
+      <c r="C21" s="79">
         <v>15</v>
       </c>
-      <c r="D21" s="80" t="s">
+      <c r="D21" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="122" t="s">
+      <c r="E21" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="94">
         <v>130000</v>
       </c>
-      <c r="G21" s="95">
+      <c r="G21" s="94">
         <f>F21*C21</f>
         <v>1950000</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="23.5" customHeight="1">
-      <c r="A22" s="80">
+      <c r="A22" s="79">
         <v>2</v>
       </c>
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="80">
+      <c r="C22" s="79">
         <v>5</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E22" s="122" t="s">
+      <c r="E22" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="94">
         <v>61500</v>
       </c>
-      <c r="G22" s="95">
+      <c r="G22" s="94">
         <f>F22*C22</f>
         <v>307500</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="34.5" customHeight="1">
-      <c r="A23" s="80">
+      <c r="A23" s="79">
         <v>3</v>
       </c>
-      <c r="B23" s="79" t="s">
+      <c r="B23" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="80">
+      <c r="C23" s="79">
         <v>15</v>
       </c>
-      <c r="D23" s="80" t="s">
+      <c r="D23" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="122" t="s">
+      <c r="E23" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="F23" s="72">
+      <c r="F23" s="71">
         <v>38000</v>
       </c>
-      <c r="G23" s="95">
+      <c r="G23" s="94">
         <f>F23*C23</f>
         <v>570000</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A24" s="80">
+      <c r="A24" s="79">
         <v>4</v>
       </c>
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="76">
-        <v>1</v>
-      </c>
-      <c r="D24" s="76" t="s">
+      <c r="C24" s="75">
+        <v>1</v>
+      </c>
+      <c r="D24" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="76"/>
-      <c r="F24" s="72">
+      <c r="E24" s="75"/>
+      <c r="F24" s="71">
         <v>1000000</v>
       </c>
-      <c r="G24" s="95">
+      <c r="G24" s="94">
         <f>F24*C24</f>
         <v>1000000</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" s="80">
+      <c r="A25" s="79">
         <v>5</v>
       </c>
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="80" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="80">
+      <c r="C25" s="79">
         <v>15</v>
       </c>
-      <c r="D25" s="80" t="s">
+      <c r="D25" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="80" t="s">
+      <c r="E25" s="79" t="s">
         <v>129</v>
       </c>
-      <c r="F25" s="95">
+      <c r="F25" s="94">
         <v>30000</v>
       </c>
-      <c r="G25" s="95">
+      <c r="G25" s="94">
         <f>F25*C25</f>
         <v>450000</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A26" s="110"/>
-      <c r="B26" s="121"/>
-      <c r="C26" s="120" t="s">
+      <c r="A26" s="109"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="119" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="120"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="118"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="148" t="s">
+      <c r="A27" s="147" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="147" t="s">
+      <c r="B27" s="146" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="146">
-        <v>1</v>
-      </c>
-      <c r="D27" s="146" t="s">
+      <c r="C27" s="145">
+        <v>1</v>
+      </c>
+      <c r="D27" s="145" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="146"/>
-      <c r="F27" s="145">
+      <c r="E27" s="145"/>
+      <c r="F27" s="144">
         <v>500000</v>
       </c>
-      <c r="G27" s="144">
+      <c r="G27" s="143">
         <f>F27*C27</f>
         <v>500000</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A28" s="143"/>
-      <c r="B28" s="142"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
+      <c r="A28" s="142"/>
+      <c r="B28" s="141"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A29" s="88" t="s">
+      <c r="A29" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="87" t="s">
+      <c r="B29" s="86" t="s">
         <v>130</v>
       </c>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="84"/>
-      <c r="G29" s="83">
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="82">
         <f>SUM(G30:G35)</f>
         <v>472750</v>
       </c>
-      <c r="H29" s="110"/>
+      <c r="H29" s="109"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A30" s="76">
-        <v>1</v>
-      </c>
-      <c r="B30" s="82" t="s">
+      <c r="A30" s="75">
+        <v>1</v>
+      </c>
+      <c r="B30" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="80" t="s">
+      <c r="C30" s="79" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="80" t="s">
+      <c r="D30" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="E30" s="80" t="s">
+      <c r="E30" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="72">
+      <c r="F30" s="71">
         <v>69500</v>
       </c>
-      <c r="G30" s="72">
+      <c r="G30" s="71">
         <v>43750</v>
       </c>
-      <c r="H30" s="110"/>
+      <c r="H30" s="109"/>
     </row>
     <row r="31" spans="1:8" ht="33.75" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="75">
         <v>2</v>
       </c>
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="C31" s="76" t="s">
+      <c r="C31" s="75" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="76" t="s">
+      <c r="D31" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="76" t="s">
+      <c r="E31" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F31" s="72">
+      <c r="F31" s="71">
         <v>1700000</v>
       </c>
-      <c r="G31" s="72">
+      <c r="G31" s="71">
         <v>136000</v>
       </c>
-      <c r="H31" s="110"/>
+      <c r="H31" s="109"/>
     </row>
     <row r="32" spans="1:8" ht="46.75" customHeight="1">
-      <c r="A32" s="76">
+      <c r="A32" s="75">
         <v>3</v>
       </c>
-      <c r="B32" s="77" t="s">
+      <c r="B32" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="C32" s="76" t="s">
+      <c r="C32" s="75" t="s">
         <v>137</v>
       </c>
-      <c r="D32" s="76" t="s">
+      <c r="D32" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="76" t="s">
+      <c r="E32" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F32" s="72">
+      <c r="F32" s="71">
         <v>292100</v>
       </c>
-      <c r="G32" s="72">
+      <c r="G32" s="71">
         <v>111000</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="43.75" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="75">
         <v>4</v>
       </c>
-      <c r="B33" s="77" t="s">
+      <c r="B33" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="C33" s="76" t="s">
+      <c r="C33" s="75" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="78" t="s">
+      <c r="D33" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="78" t="s">
+      <c r="E33" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="F33" s="72">
+      <c r="F33" s="71">
         <v>23400</v>
       </c>
-      <c r="G33" s="72">
+      <c r="G33" s="71">
         <v>37000</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A34" s="76">
+      <c r="A34" s="75">
         <v>5</v>
       </c>
-      <c r="B34" s="77" t="s">
+      <c r="B34" s="76" t="s">
         <v>140</v>
       </c>
-      <c r="C34" s="76">
-        <v>1</v>
-      </c>
-      <c r="D34" s="76" t="s">
+      <c r="C34" s="75">
+        <v>1</v>
+      </c>
+      <c r="D34" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="76" t="s">
+      <c r="E34" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F34" s="72">
+      <c r="F34" s="71">
         <v>63000</v>
       </c>
-      <c r="G34" s="72">
+      <c r="G34" s="71">
         <v>63000</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
-      <c r="A35" s="76">
+      <c r="A35" s="75">
         <v>6</v>
       </c>
-      <c r="B35" s="77" t="s">
+      <c r="B35" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="C35" s="76">
-        <v>1</v>
-      </c>
-      <c r="D35" s="76" t="s">
+      <c r="C35" s="75">
+        <v>1</v>
+      </c>
+      <c r="D35" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="76" t="s">
+      <c r="E35" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="F35" s="72">
+      <c r="F35" s="71">
         <v>82000</v>
       </c>
-      <c r="G35" s="72">
+      <c r="G35" s="71">
         <v>82000</v>
       </c>
     </row>
@@ -15969,21 +15972,21 @@
       <c r="A36" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="158"/>
-      <c r="C36" s="159"/>
-      <c r="D36" s="159"/>
-      <c r="E36" s="159"/>
-      <c r="F36" s="160"/>
+      <c r="B36" s="148"/>
+      <c r="C36" s="149"/>
+      <c r="D36" s="149"/>
+      <c r="E36" s="149"/>
+      <c r="F36" s="150"/>
       <c r="G36" s="69">
         <f>SUM(G8,G13,G17,G20,G27,G29)</f>
         <v>12400250</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1">
-      <c r="G37" s="141"/>
+      <c r="G37" s="140"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1">
-      <c r="G38" s="141"/>
+      <c r="G38" s="140"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1"/>
     <row r="40" spans="1:7" ht="15.75" customHeight="1"/>
